--- a/成本核算平台需求跟踪矩阵.xlsx
+++ b/成本核算平台需求跟踪矩阵.xlsx
@@ -2281,7 +2281,6 @@
     <xf numFmtId="14" fontId="27" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="1" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2307,6 +2306,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2516,13 +2516,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.6235185185" refreshedBy="26242" recordCount="70">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
   <cacheFields count="14">
     <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="60">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="一、底座与设计基线"/>
         <s v="【若依底座接入与品牌裁剪】"/>
@@ -2548,45 +2548,10 @@
         <s v="【结果台账与追溯】"/>
         <s v="【百万级性能优化】"/>
         <s v="【监控告警与通知】"/>
-        <s v="【协力队派工】生成作业指令"/>
-        <s v="【船舶动态(小程序)】"/>
-        <s v="【工作台】"/>
-        <s v="【大机对舱】"/>
-        <s v="【清场确认】"/>
-        <s v="【对垛确认-库管员】"/>
-        <s v="【对垛确认-堆取料司机】"/>
-        <s v="【清舱设备申请】"/>
-        <s v="【车辆抽磅】"/>
-        <s v="【车辆抽磅接口】"/>
-        <s v="【车辆过磅记录】"/>
-        <s v="【人员清舱】"/>
-        <s v="【设备清舱台时】"/>
-        <s v="【成垛确认】"/>
-        <s v="【苫盖】"/>
-        <s v="【货垛巡更】"/>
-        <s v="【设备请假】"/>
-        <s v="【设备报修】"/>
-        <s v="【请假报修审核】"/>
-        <s v="【中控流程确认】"/>
-        <s v="【堆取料机运行记录】"/>
-        <s v="【皮带运行记录】启停"/>
-        <s v="【卸船机运行记录】"/>
-        <s v="【门机运行记录】"/>
-        <s v="【提醒】清舱、采样"/>
-        <s v="【运行记录交接班自动处理job】"/>
-        <s v="六、库场管理"/>
-        <s v="【入库理货票确认】"/>
-        <s v="【出入库记录】"/>
-        <s v="【库存查询】"/>
-        <s v="【库存调整】"/>
-        <s v="【每日库存】"/>
-        <s v="【货垛牌管理】"/>
-        <s v="七、接口开发"/>
-        <s v="【卸船合同】"/>
       </sharedItems>
     </cacheField>
     <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="28">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="建立产品重构新基线"/>
         <s v="完成独立仓库、品牌文案、导航精简"/>
@@ -2612,26 +2577,12 @@
         <s v="恢复独立结果台账、规则命中与阶梯解释"/>
         <s v="批量分片、异步执行、索引与缓存优化"/>
         <s v="恢复任务告警、失败订阅和通知治理"/>
-        <s v="redis数据"/>
-        <s v="xxl-job"/>
-        <s v="跟踪网厅调用"/>
       </sharedItems>
     </cacheField>
     <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="13">
+      <sharedItems containsBlank="1" count="2">
         <m/>
         <s v="GitFhw"/>
-        <s v="吴秀晗"/>
-        <s v="高杰"/>
-        <s v="王昌泽"/>
-        <s v="胡兆稳"/>
-        <s v="宁文龙"/>
-        <s v="矫淑宏"/>
-        <s v="苏浩南"/>
-        <s v="林凤晟"/>
-        <s v="刘瀚远"/>
-        <s v="孙启明"/>
-        <s v="张永菲"/>
       </sharedItems>
     </cacheField>
     <cacheField name="状态" numFmtId="0">
@@ -2640,9 +2591,9 @@
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
         <s v="未开始 ⏳"/>
-        <s v="开发完成👌"/>
-        <s v="已延期 💥"/>
-        <s v="进行中 🔛"/>
+        <s v="开发完成👌" u="1"/>
+        <s v="已延期 💥" u="1"/>
+        <s v="进行中 🔛" u="1"/>
         <s v="使用下拉列表显示任务状态" u="1"/>
         <s v="待启动 💡" u="1"/>
         <s v="李光军" u="1"/>
@@ -2663,7 +2614,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="27">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-03-31T00:00:00"/>
@@ -2680,21 +2631,10 @@
         <d v="2026-05-15T00:00:00"/>
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-25T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-28T00:00:00"/>
-        <d v="2024-09-30T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-28T00:00:00"/>
-        <n v="45576"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-09-19T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="29">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-04-21T00:00:00"/>
@@ -2711,36 +2651,15 @@
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-23T00:00:00"/>
         <d v="2026-05-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
-        <d v="2024-09-29T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-10-23T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-31T00:00:00"/>
-        <n v="45596"/>
-        <n v="45607"/>
-        <d v="2024-09-30T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="23" count="9">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <n v="2"/>
-        <n v="7"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="3"/>
-        <n v="20"/>
-        <n v="11"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="120" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -2749,17 +2668,10 @@
         <n v="12"/>
         <n v="31"/>
         <n v="11"/>
-        <n v="2"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="120"/>
-        <n v="20"/>
-        <n v="112"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="35" count="14">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -2768,68 +2680,31 @@
         <n v="10"/>
         <n v="23"/>
         <n v="9"/>
-        <n v="6"/>
-        <n v="4"/>
-        <n v="8"/>
-        <n v="18"/>
-        <n v="15"/>
-        <n v="35"/>
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
         <m/>
         <n v="1"/>
         <n v="0.15"/>
         <n v="0"/>
-        <n v="0.868131868131868"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-18T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-10-09T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-09-20T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-22T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-16T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-11-28T00:00:00"/>
-        <d v="2024-11-07T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <s v="田华"/>
-        <s v="孙启明"/>
-        <s v="孙佳明"/>
-        <s v="赵添志"/>
       </sharedItems>
     </cacheField>
     <cacheField name="开始时间" numFmtId="0">
@@ -2842,13 +2717,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.6235185185" refreshedBy="26242" recordCount="70">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
   <cacheFields count="14">
     <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="60">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="一、底座与设计基线"/>
         <s v="【若依底座接入与品牌裁剪】"/>
@@ -2874,45 +2749,10 @@
         <s v="【结果台账与追溯】"/>
         <s v="【百万级性能优化】"/>
         <s v="【监控告警与通知】"/>
-        <s v="【协力队派工】生成作业指令"/>
-        <s v="【船舶动态(小程序)】"/>
-        <s v="【工作台】"/>
-        <s v="【大机对舱】"/>
-        <s v="【清场确认】"/>
-        <s v="【对垛确认-库管员】"/>
-        <s v="【对垛确认-堆取料司机】"/>
-        <s v="【清舱设备申请】"/>
-        <s v="【车辆抽磅】"/>
-        <s v="【车辆抽磅接口】"/>
-        <s v="【车辆过磅记录】"/>
-        <s v="【人员清舱】"/>
-        <s v="【设备清舱台时】"/>
-        <s v="【成垛确认】"/>
-        <s v="【苫盖】"/>
-        <s v="【货垛巡更】"/>
-        <s v="【设备请假】"/>
-        <s v="【设备报修】"/>
-        <s v="【请假报修审核】"/>
-        <s v="【中控流程确认】"/>
-        <s v="【堆取料机运行记录】"/>
-        <s v="【皮带运行记录】启停"/>
-        <s v="【卸船机运行记录】"/>
-        <s v="【门机运行记录】"/>
-        <s v="【提醒】清舱、采样"/>
-        <s v="【运行记录交接班自动处理job】"/>
-        <s v="六、库场管理"/>
-        <s v="【入库理货票确认】"/>
-        <s v="【出入库记录】"/>
-        <s v="【库存查询】"/>
-        <s v="【库存调整】"/>
-        <s v="【每日库存】"/>
-        <s v="【货垛牌管理】"/>
-        <s v="七、接口开发"/>
-        <s v="【卸船合同】"/>
       </sharedItems>
     </cacheField>
     <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="28">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="建立产品重构新基线"/>
         <s v="完成独立仓库、品牌文案、导航精简"/>
@@ -2938,41 +2778,24 @@
         <s v="恢复独立结果台账、规则命中与阶梯解释"/>
         <s v="批量分片、异步执行、索引与缓存优化"/>
         <s v="恢复任务告警、失败订阅和通知治理"/>
-        <s v="redis数据"/>
-        <s v="xxl-job"/>
-        <s v="跟踪网厅调用"/>
       </sharedItems>
     </cacheField>
     <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="13">
+      <sharedItems containsBlank="1" count="2">
         <m/>
         <s v="GitFhw"/>
-        <s v="吴秀晗"/>
-        <s v="高杰"/>
-        <s v="王昌泽"/>
-        <s v="胡兆稳"/>
-        <s v="宁文龙"/>
-        <s v="矫淑宏"/>
-        <s v="苏浩南"/>
-        <s v="林凤晟"/>
-        <s v="刘瀚远"/>
-        <s v="孙启明"/>
-        <s v="张永菲"/>
       </sharedItems>
     </cacheField>
     <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="7">
+      <sharedItems containsBlank="1" count="4">
         <m/>
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
         <s v="未开始 ⏳"/>
-        <s v="开发完成👌"/>
-        <s v="已延期 💥"/>
-        <s v="进行中 🔛"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="27">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-03-31T00:00:00"/>
@@ -2989,21 +2812,10 @@
         <d v="2026-05-15T00:00:00"/>
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-25T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-28T00:00:00"/>
-        <d v="2024-09-30T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-28T00:00:00"/>
-        <n v="45576"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-09-19T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="29">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-04-21T00:00:00"/>
@@ -3020,36 +2832,15 @@
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-23T00:00:00"/>
         <d v="2026-05-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
-        <d v="2024-09-29T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-10-23T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-31T00:00:00"/>
-        <n v="45596"/>
-        <n v="45607"/>
-        <d v="2024-09-30T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="23" count="9">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <n v="2"/>
-        <n v="7"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="3"/>
-        <n v="20"/>
-        <n v="11"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="120" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -3058,17 +2849,10 @@
         <n v="12"/>
         <n v="31"/>
         <n v="11"/>
-        <n v="2"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="120"/>
-        <n v="20"/>
-        <n v="112"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="35" count="14">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -3077,68 +2861,31 @@
         <n v="10"/>
         <n v="23"/>
         <n v="9"/>
-        <n v="6"/>
-        <n v="4"/>
-        <n v="8"/>
-        <n v="18"/>
-        <n v="15"/>
-        <n v="35"/>
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
         <m/>
         <n v="1"/>
         <n v="0.15"/>
         <n v="0"/>
-        <n v="0.868131868131868"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-18T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-10-09T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-09-20T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-22T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-16T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-11-28T00:00:00"/>
-        <d v="2024-11-07T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <s v="田华"/>
-        <s v="孙启明"/>
-        <s v="孙佳明"/>
-        <s v="赵添志"/>
       </sharedItems>
     </cacheField>
     <cacheField name="开始时间" numFmtId="0">
@@ -3151,13 +2898,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.6235185185" refreshedBy="26242" recordCount="70">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
   <cacheFields count="14">
     <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="60">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="一、底座与设计基线"/>
         <s v="【若依底座接入与品牌裁剪】"/>
@@ -3183,45 +2930,10 @@
         <s v="【结果台账与追溯】"/>
         <s v="【百万级性能优化】"/>
         <s v="【监控告警与通知】"/>
-        <s v="【协力队派工】生成作业指令"/>
-        <s v="【船舶动态(小程序)】"/>
-        <s v="【工作台】"/>
-        <s v="【大机对舱】"/>
-        <s v="【清场确认】"/>
-        <s v="【对垛确认-库管员】"/>
-        <s v="【对垛确认-堆取料司机】"/>
-        <s v="【清舱设备申请】"/>
-        <s v="【车辆抽磅】"/>
-        <s v="【车辆抽磅接口】"/>
-        <s v="【车辆过磅记录】"/>
-        <s v="【人员清舱】"/>
-        <s v="【设备清舱台时】"/>
-        <s v="【成垛确认】"/>
-        <s v="【苫盖】"/>
-        <s v="【货垛巡更】"/>
-        <s v="【设备请假】"/>
-        <s v="【设备报修】"/>
-        <s v="【请假报修审核】"/>
-        <s v="【中控流程确认】"/>
-        <s v="【堆取料机运行记录】"/>
-        <s v="【皮带运行记录】启停"/>
-        <s v="【卸船机运行记录】"/>
-        <s v="【门机运行记录】"/>
-        <s v="【提醒】清舱、采样"/>
-        <s v="【运行记录交接班自动处理job】"/>
-        <s v="六、库场管理"/>
-        <s v="【入库理货票确认】"/>
-        <s v="【出入库记录】"/>
-        <s v="【库存查询】"/>
-        <s v="【库存调整】"/>
-        <s v="【每日库存】"/>
-        <s v="【货垛牌管理】"/>
-        <s v="七、接口开发"/>
-        <s v="【卸船合同】"/>
       </sharedItems>
     </cacheField>
     <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="28">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="建立产品重构新基线"/>
         <s v="完成独立仓库、品牌文案、导航精简"/>
@@ -3247,26 +2959,12 @@
         <s v="恢复独立结果台账、规则命中与阶梯解释"/>
         <s v="批量分片、异步执行、索引与缓存优化"/>
         <s v="恢复任务告警、失败订阅和通知治理"/>
-        <s v="redis数据"/>
-        <s v="xxl-job"/>
-        <s v="跟踪网厅调用"/>
       </sharedItems>
     </cacheField>
     <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="13">
+      <sharedItems containsBlank="1" count="2">
         <m/>
         <s v="GitFhw"/>
-        <s v="吴秀晗"/>
-        <s v="高杰"/>
-        <s v="王昌泽"/>
-        <s v="胡兆稳"/>
-        <s v="宁文龙"/>
-        <s v="矫淑宏"/>
-        <s v="苏浩南"/>
-        <s v="林凤晟"/>
-        <s v="刘瀚远"/>
-        <s v="孙启明"/>
-        <s v="张永菲"/>
       </sharedItems>
     </cacheField>
     <cacheField name="状态" numFmtId="0">
@@ -3275,9 +2973,9 @@
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
         <s v="未开始 ⏳"/>
-        <s v="开发完成👌"/>
-        <s v="已延期 💥"/>
-        <s v="进行中 🔛"/>
+        <s v="开发完成👌" u="1"/>
+        <s v="已延期 💥" u="1"/>
+        <s v="进行中 🔛" u="1"/>
         <s v="使用下拉列表显示任务状态" u="1"/>
         <s v="待启动 💡" u="1"/>
         <s v="李光军" u="1"/>
@@ -3298,7 +2996,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="27">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-03-31T00:00:00"/>
@@ -3315,21 +3013,10 @@
         <d v="2026-05-15T00:00:00"/>
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-25T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-28T00:00:00"/>
-        <d v="2024-09-30T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-28T00:00:00"/>
-        <n v="45576"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-09-19T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="29">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-04-21T00:00:00"/>
@@ -3346,36 +3033,15 @@
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-23T00:00:00"/>
         <d v="2026-05-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
-        <d v="2024-09-29T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-10-23T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-31T00:00:00"/>
-        <n v="45596"/>
-        <n v="45607"/>
-        <d v="2024-09-30T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="23" count="9">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <n v="2"/>
-        <n v="7"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="3"/>
-        <n v="20"/>
-        <n v="11"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="120" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -3384,17 +3050,10 @@
         <n v="12"/>
         <n v="31"/>
         <n v="11"/>
-        <n v="2"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="120"/>
-        <n v="20"/>
-        <n v="112"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="35" count="14">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -3403,68 +3062,31 @@
         <n v="10"/>
         <n v="23"/>
         <n v="9"/>
-        <n v="6"/>
-        <n v="4"/>
-        <n v="8"/>
-        <n v="18"/>
-        <n v="15"/>
-        <n v="35"/>
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
         <m/>
         <n v="1"/>
         <n v="0.15"/>
         <n v="0"/>
-        <n v="0.868131868131868"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-18T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-10-09T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-09-20T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-22T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-16T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-11-28T00:00:00"/>
-        <d v="2024-11-07T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <s v="田华"/>
-        <s v="孙启明"/>
-        <s v="孙佳明"/>
-        <s v="赵添志"/>
       </sharedItems>
     </cacheField>
     <cacheField name="开始时间" numFmtId="0">
@@ -3477,13 +3099,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.6235185185" refreshedBy="26242" recordCount="70">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
   <cacheFields count="14">
     <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="60">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="一、底座与设计基线"/>
         <s v="【若依底座接入与品牌裁剪】"/>
@@ -3509,45 +3131,10 @@
         <s v="【结果台账与追溯】"/>
         <s v="【百万级性能优化】"/>
         <s v="【监控告警与通知】"/>
-        <s v="【协力队派工】生成作业指令"/>
-        <s v="【船舶动态(小程序)】"/>
-        <s v="【工作台】"/>
-        <s v="【大机对舱】"/>
-        <s v="【清场确认】"/>
-        <s v="【对垛确认-库管员】"/>
-        <s v="【对垛确认-堆取料司机】"/>
-        <s v="【清舱设备申请】"/>
-        <s v="【车辆抽磅】"/>
-        <s v="【车辆抽磅接口】"/>
-        <s v="【车辆过磅记录】"/>
-        <s v="【人员清舱】"/>
-        <s v="【设备清舱台时】"/>
-        <s v="【成垛确认】"/>
-        <s v="【苫盖】"/>
-        <s v="【货垛巡更】"/>
-        <s v="【设备请假】"/>
-        <s v="【设备报修】"/>
-        <s v="【请假报修审核】"/>
-        <s v="【中控流程确认】"/>
-        <s v="【堆取料机运行记录】"/>
-        <s v="【皮带运行记录】启停"/>
-        <s v="【卸船机运行记录】"/>
-        <s v="【门机运行记录】"/>
-        <s v="【提醒】清舱、采样"/>
-        <s v="【运行记录交接班自动处理job】"/>
-        <s v="六、库场管理"/>
-        <s v="【入库理货票确认】"/>
-        <s v="【出入库记录】"/>
-        <s v="【库存查询】"/>
-        <s v="【库存调整】"/>
-        <s v="【每日库存】"/>
-        <s v="【货垛牌管理】"/>
-        <s v="七、接口开发"/>
-        <s v="【卸船合同】"/>
       </sharedItems>
     </cacheField>
     <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="28">
+      <sharedItems containsBlank="1" count="25">
         <m/>
         <s v="建立产品重构新基线"/>
         <s v="完成独立仓库、品牌文案、导航精简"/>
@@ -3573,41 +3160,24 @@
         <s v="恢复独立结果台账、规则命中与阶梯解释"/>
         <s v="批量分片、异步执行、索引与缓存优化"/>
         <s v="恢复任务告警、失败订阅和通知治理"/>
-        <s v="redis数据"/>
-        <s v="xxl-job"/>
-        <s v="跟踪网厅调用"/>
       </sharedItems>
     </cacheField>
     <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="13">
+      <sharedItems containsBlank="1" count="2">
         <m/>
         <s v="GitFhw"/>
-        <s v="吴秀晗"/>
-        <s v="高杰"/>
-        <s v="王昌泽"/>
-        <s v="胡兆稳"/>
-        <s v="宁文龙"/>
-        <s v="矫淑宏"/>
-        <s v="苏浩南"/>
-        <s v="林凤晟"/>
-        <s v="刘瀚远"/>
-        <s v="孙启明"/>
-        <s v="张永菲"/>
       </sharedItems>
     </cacheField>
     <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="7">
+      <sharedItems containsBlank="1" count="4">
         <m/>
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
         <s v="未开始 ⏳"/>
-        <s v="开发完成👌"/>
-        <s v="已延期 💥"/>
-        <s v="进行中 🔛"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="27">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-03-31T00:00:00"/>
@@ -3624,21 +3194,10 @@
         <d v="2026-05-15T00:00:00"/>
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-25T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-28T00:00:00"/>
-        <d v="2024-09-30T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-28T00:00:00"/>
-        <n v="45576"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-09-19T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsDate="1" containsMixedTypes="1" count="29">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
         <m/>
         <d v="2026-03-30T00:00:00"/>
         <d v="2026-04-21T00:00:00"/>
@@ -3655,36 +3214,15 @@
         <d v="2026-05-20T00:00:00"/>
         <d v="2026-05-23T00:00:00"/>
         <d v="2026-05-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
-        <d v="2024-09-29T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-10-23T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-31T00:00:00"/>
-        <n v="45596"/>
-        <n v="45607"/>
-        <d v="2024-09-30T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="23" count="9">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <n v="2"/>
-        <n v="7"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="3"/>
-        <n v="20"/>
-        <n v="11"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="120" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -3693,17 +3231,10 @@
         <n v="12"/>
         <n v="31"/>
         <n v="11"/>
-        <n v="2"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="23"/>
-        <n v="120"/>
-        <n v="20"/>
-        <n v="112"/>
       </sharedItems>
     </cacheField>
     <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="35" count="14">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
         <m/>
         <n v="1"/>
         <n v="3"/>
@@ -3712,68 +3243,31 @@
         <n v="10"/>
         <n v="23"/>
         <n v="9"/>
-        <n v="6"/>
-        <n v="4"/>
-        <n v="8"/>
-        <n v="18"/>
-        <n v="15"/>
-        <n v="35"/>
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
         <m/>
         <n v="1"/>
         <n v="0.15"/>
         <n v="0"/>
-        <n v="0.868131868131868"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-18T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-09-24T00:00:00"/>
-        <d v="2024-09-18T00:00:00"/>
-        <d v="2024-10-08T00:00:00"/>
-        <d v="2024-10-09T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-14T00:00:00"/>
-        <d v="2024-10-21T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-09-20T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2024-09-22T00:00:00" maxDate="2026-03-30T00:00:00" count="15">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
         <m/>
         <d v="2026-03-30T00:00:00"/>
-        <d v="2024-10-10T00:00:00"/>
-        <d v="2024-09-22T00:00:00"/>
-        <d v="2024-10-12T00:00:00"/>
-        <d v="2024-10-15T00:00:00"/>
-        <d v="2024-10-16T00:00:00"/>
-        <d v="2024-10-11T00:00:00"/>
-        <d v="2024-10-22T00:00:00"/>
-        <d v="2024-10-25T00:00:00"/>
-        <d v="2024-10-18T00:00:00"/>
-        <d v="2024-11-28T00:00:00"/>
-        <d v="2024-11-07T00:00:00"/>
-        <d v="2024-10-17T00:00:00"/>
-        <d v="2024-09-23T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
         <m/>
-        <s v="田华"/>
-        <s v="孙启明"/>
-        <s v="孙佳明"/>
-        <s v="赵添志"/>
       </sharedItems>
     </cacheField>
     <cacheField name="开始时间" numFmtId="0">
@@ -3790,43 +3284,8 @@
   <location ref="B24:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="61">
+      <items count="26">
         <item x="0"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -3876,10 +3335,10 @@
         <item h="1" m="1" x="23"/>
         <item h="1" m="1" x="7"/>
         <item h="1" x="1"/>
-        <item h="1" x="4"/>
+        <item h="1" m="1" x="4"/>
         <item h="1" m="1" x="8"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
+        <item h="1" m="1" x="5"/>
+        <item h="1" m="1" x="6"/>
         <item h="1" x="2"/>
         <item h="1" x="3"/>
         <item t="default"/>
@@ -3924,43 +3383,8 @@
   <location ref="B12:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="61">
+      <items count="26">
         <item x="0"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -4019,43 +3443,8 @@
   <location ref="E24:F26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="61">
+      <items count="26">
         <item x="0"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -4105,10 +3494,10 @@
         <item h="1" m="1" x="23"/>
         <item h="1" m="1" x="7"/>
         <item h="1" x="1"/>
-        <item h="1" x="4"/>
+        <item h="1" m="1" x="4"/>
         <item h="1" m="1" x="8"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
+        <item h="1" m="1" x="5"/>
+        <item h="1" m="1" x="6"/>
         <item h="1" x="2"/>
         <item h="1" x="3"/>
         <item t="default"/>
@@ -4153,43 +3542,8 @@
   <location ref="E12:F13" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="61">
+      <items count="26">
         <item x="0"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
@@ -4223,16 +3577,8 @@
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="10">
+      <items count="2">
         <item x="0"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="8"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -6410,7 +5756,7 @@
       <c r="I9" s="115">
         <v>1</v>
       </c>
-      <c r="J9" s="117">
+      <c r="J9" s="107">
         <v>1</v>
       </c>
       <c r="K9" s="116">
@@ -6423,126 +5769,126 @@
       <c r="N9" s="115"/>
       <c r="O9" s="115"/>
       <c r="P9" s="104"/>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="119"/>
-      <c r="S9" s="119"/>
-      <c r="T9" s="119"/>
-      <c r="U9" s="119"/>
-      <c r="V9" s="119"/>
-      <c r="W9" s="119"/>
-      <c r="X9" s="119"/>
-      <c r="Y9" s="119"/>
-      <c r="Z9" s="119"/>
-      <c r="AA9" s="119"/>
-      <c r="AB9" s="119"/>
-      <c r="AC9" s="119"/>
-      <c r="AD9" s="119"/>
-      <c r="AE9" s="119"/>
-      <c r="AF9" s="119"/>
-      <c r="AG9" s="119"/>
-      <c r="AH9" s="119"/>
-      <c r="AI9" s="119"/>
-      <c r="AJ9" s="119"/>
-      <c r="AK9" s="119"/>
-      <c r="AL9" s="119"/>
-      <c r="AM9" s="119"/>
-      <c r="AN9" s="119"/>
-      <c r="AO9" s="119"/>
-      <c r="AP9" s="119"/>
-      <c r="AQ9" s="119"/>
-      <c r="AR9" s="119"/>
-      <c r="AS9" s="119"/>
-      <c r="AT9" s="119"/>
-      <c r="AU9" s="119"/>
-      <c r="AV9" s="119"/>
-      <c r="AW9" s="119"/>
-      <c r="AX9" s="119"/>
-      <c r="AY9" s="119"/>
-      <c r="AZ9" s="119"/>
-      <c r="BA9" s="119"/>
-      <c r="BB9" s="119"/>
-      <c r="BC9" s="119"/>
-      <c r="BD9" s="119"/>
-      <c r="BE9" s="119"/>
-      <c r="BF9" s="119"/>
-      <c r="BG9" s="119"/>
-      <c r="BH9" s="119"/>
-      <c r="BI9" s="119"/>
-      <c r="BJ9" s="119"/>
-      <c r="BK9" s="119"/>
-      <c r="BL9" s="119"/>
-      <c r="BM9" s="119"/>
-      <c r="BN9" s="119"/>
-      <c r="BO9" s="119"/>
-      <c r="BP9" s="119"/>
-      <c r="BQ9" s="119"/>
-      <c r="BR9" s="119"/>
-      <c r="BS9" s="119"/>
-      <c r="BT9" s="119"/>
-      <c r="BU9" s="119"/>
-      <c r="BV9" s="119"/>
-      <c r="BW9" s="119"/>
-      <c r="BX9" s="119"/>
-      <c r="BY9" s="119"/>
-      <c r="BZ9" s="119"/>
-      <c r="CA9" s="119"/>
-      <c r="CB9" s="119"/>
-      <c r="CC9" s="119"/>
-      <c r="CD9" s="119"/>
-      <c r="CE9" s="119"/>
-      <c r="CF9" s="119"/>
-      <c r="CG9" s="119"/>
-      <c r="CH9" s="119"/>
-      <c r="CI9" s="119"/>
-      <c r="CJ9" s="119"/>
-      <c r="CK9" s="119"/>
-      <c r="CL9" s="119"/>
-      <c r="CM9" s="119"/>
-      <c r="CN9" s="119"/>
-      <c r="CO9" s="119"/>
-      <c r="CP9" s="119"/>
-      <c r="CQ9" s="119"/>
-      <c r="CR9" s="119"/>
-      <c r="CS9" s="119"/>
-      <c r="CT9" s="119"/>
-      <c r="CU9" s="119"/>
-      <c r="CV9" s="119"/>
-      <c r="CW9" s="119"/>
-      <c r="CX9" s="119"/>
-      <c r="CY9" s="119"/>
-      <c r="CZ9" s="119"/>
-      <c r="DA9" s="119"/>
-      <c r="DB9" s="119"/>
-      <c r="DC9" s="119"/>
-      <c r="DD9" s="119"/>
-      <c r="DE9" s="119"/>
-      <c r="DF9" s="119"/>
-      <c r="DG9" s="119"/>
-      <c r="DH9" s="119"/>
-      <c r="DI9" s="119"/>
-      <c r="DJ9" s="119"/>
-      <c r="DK9" s="119"/>
-      <c r="DL9" s="119"/>
-      <c r="DM9" s="119"/>
-      <c r="DN9" s="119"/>
-      <c r="DO9" s="119"/>
-      <c r="DP9" s="119"/>
-      <c r="DQ9" s="119"/>
-      <c r="DR9" s="119"/>
-      <c r="DS9" s="119"/>
-      <c r="DT9" s="119"/>
-      <c r="DU9" s="119"/>
-      <c r="DV9" s="119"/>
-      <c r="DW9" s="119"/>
-      <c r="DX9" s="119"/>
-      <c r="DY9" s="119"/>
-      <c r="DZ9" s="119"/>
-      <c r="EA9" s="119"/>
-      <c r="EB9" s="119"/>
-      <c r="EC9" s="119"/>
-      <c r="ED9" s="119"/>
-      <c r="EE9" s="119"/>
-      <c r="EF9" s="119"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118"/>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118"/>
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118"/>
+      <c r="AA9" s="118"/>
+      <c r="AB9" s="118"/>
+      <c r="AC9" s="118"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="118"/>
+      <c r="AF9" s="118"/>
+      <c r="AG9" s="118"/>
+      <c r="AH9" s="118"/>
+      <c r="AI9" s="118"/>
+      <c r="AJ9" s="118"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="118"/>
+      <c r="AM9" s="118"/>
+      <c r="AN9" s="118"/>
+      <c r="AO9" s="118"/>
+      <c r="AP9" s="118"/>
+      <c r="AQ9" s="118"/>
+      <c r="AR9" s="118"/>
+      <c r="AS9" s="118"/>
+      <c r="AT9" s="118"/>
+      <c r="AU9" s="118"/>
+      <c r="AV9" s="118"/>
+      <c r="AW9" s="118"/>
+      <c r="AX9" s="118"/>
+      <c r="AY9" s="118"/>
+      <c r="AZ9" s="118"/>
+      <c r="BA9" s="118"/>
+      <c r="BB9" s="118"/>
+      <c r="BC9" s="118"/>
+      <c r="BD9" s="118"/>
+      <c r="BE9" s="118"/>
+      <c r="BF9" s="118"/>
+      <c r="BG9" s="118"/>
+      <c r="BH9" s="118"/>
+      <c r="BI9" s="118"/>
+      <c r="BJ9" s="118"/>
+      <c r="BK9" s="118"/>
+      <c r="BL9" s="118"/>
+      <c r="BM9" s="118"/>
+      <c r="BN9" s="118"/>
+      <c r="BO9" s="118"/>
+      <c r="BP9" s="118"/>
+      <c r="BQ9" s="118"/>
+      <c r="BR9" s="118"/>
+      <c r="BS9" s="118"/>
+      <c r="BT9" s="118"/>
+      <c r="BU9" s="118"/>
+      <c r="BV9" s="118"/>
+      <c r="BW9" s="118"/>
+      <c r="BX9" s="118"/>
+      <c r="BY9" s="118"/>
+      <c r="BZ9" s="118"/>
+      <c r="CA9" s="118"/>
+      <c r="CB9" s="118"/>
+      <c r="CC9" s="118"/>
+      <c r="CD9" s="118"/>
+      <c r="CE9" s="118"/>
+      <c r="CF9" s="118"/>
+      <c r="CG9" s="118"/>
+      <c r="CH9" s="118"/>
+      <c r="CI9" s="118"/>
+      <c r="CJ9" s="118"/>
+      <c r="CK9" s="118"/>
+      <c r="CL9" s="118"/>
+      <c r="CM9" s="118"/>
+      <c r="CN9" s="118"/>
+      <c r="CO9" s="118"/>
+      <c r="CP9" s="118"/>
+      <c r="CQ9" s="118"/>
+      <c r="CR9" s="118"/>
+      <c r="CS9" s="118"/>
+      <c r="CT9" s="118"/>
+      <c r="CU9" s="118"/>
+      <c r="CV9" s="118"/>
+      <c r="CW9" s="118"/>
+      <c r="CX9" s="118"/>
+      <c r="CY9" s="118"/>
+      <c r="CZ9" s="118"/>
+      <c r="DA9" s="118"/>
+      <c r="DB9" s="118"/>
+      <c r="DC9" s="118"/>
+      <c r="DD9" s="118"/>
+      <c r="DE9" s="118"/>
+      <c r="DF9" s="118"/>
+      <c r="DG9" s="118"/>
+      <c r="DH9" s="118"/>
+      <c r="DI9" s="118"/>
+      <c r="DJ9" s="118"/>
+      <c r="DK9" s="118"/>
+      <c r="DL9" s="118"/>
+      <c r="DM9" s="118"/>
+      <c r="DN9" s="118"/>
+      <c r="DO9" s="118"/>
+      <c r="DP9" s="118"/>
+      <c r="DQ9" s="118"/>
+      <c r="DR9" s="118"/>
+      <c r="DS9" s="118"/>
+      <c r="DT9" s="118"/>
+      <c r="DU9" s="118"/>
+      <c r="DV9" s="118"/>
+      <c r="DW9" s="118"/>
+      <c r="DX9" s="118"/>
+      <c r="DY9" s="118"/>
+      <c r="DZ9" s="118"/>
+      <c r="EA9" s="118"/>
+      <c r="EB9" s="118"/>
+      <c r="EC9" s="118"/>
+      <c r="ED9" s="118"/>
+      <c r="EE9" s="118"/>
+      <c r="EF9" s="118"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:136">
       <c r="A10" s="102" t="s">
@@ -6554,7 +5900,7 @@
       <c r="C10" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="120" t="s">
+      <c r="D10" s="119" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="104">
@@ -6580,55 +5926,55 @@
         <v>46111</v>
       </c>
       <c r="M10" s="104"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="120"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
       <c r="P10" s="104"/>
       <c r="Q10" s="108"/>
       <c r="R10" s="35"/>
       <c r="S10" s="111"/>
-      <c r="T10" s="121"/>
+      <c r="T10" s="120"/>
       <c r="U10" s="111"/>
       <c r="V10" s="109"/>
       <c r="W10" s="109"/>
       <c r="X10" s="109"/>
       <c r="Y10" s="111"/>
       <c r="Z10" s="111"/>
-      <c r="AA10" s="121"/>
+      <c r="AA10" s="120"/>
       <c r="AB10" s="111"/>
       <c r="AC10" s="109"/>
       <c r="AD10" s="109"/>
       <c r="AE10" s="109"/>
       <c r="AF10" s="111"/>
       <c r="AG10" s="111"/>
-      <c r="AH10" s="121"/>
+      <c r="AH10" s="120"/>
       <c r="AI10" s="111"/>
       <c r="AJ10" s="109"/>
       <c r="AK10" s="109"/>
       <c r="AL10" s="109"/>
       <c r="AM10" s="111"/>
       <c r="AN10" s="111"/>
-      <c r="AO10" s="121"/>
+      <c r="AO10" s="120"/>
       <c r="AP10" s="111"/>
       <c r="AQ10" s="109"/>
       <c r="AR10" s="109"/>
       <c r="AS10" s="109"/>
       <c r="AT10" s="111"/>
       <c r="AU10" s="111"/>
-      <c r="AV10" s="121"/>
+      <c r="AV10" s="120"/>
       <c r="AW10" s="111"/>
       <c r="AX10" s="109"/>
       <c r="AY10" s="109"/>
       <c r="AZ10" s="109"/>
       <c r="BA10" s="111"/>
       <c r="BB10" s="111"/>
-      <c r="BC10" s="121"/>
+      <c r="BC10" s="120"/>
       <c r="BD10" s="111"/>
       <c r="BE10" s="109"/>
       <c r="BF10" s="109"/>
       <c r="BG10" s="109"/>
       <c r="BH10" s="111"/>
       <c r="BI10" s="111"/>
-      <c r="BJ10" s="121"/>
+      <c r="BJ10" s="120"/>
       <c r="BK10" s="111"/>
       <c r="BL10" s="109"/>
       <c r="BM10" s="109"/>
@@ -6660,7 +6006,7 @@
       <c r="C11" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="120" t="s">
+      <c r="D11" s="119" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="104">
@@ -6686,55 +6032,55 @@
         <v>46111</v>
       </c>
       <c r="M11" s="104"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="120"/>
+      <c r="N11" s="119"/>
+      <c r="O11" s="119"/>
       <c r="P11" s="104"/>
       <c r="Q11" s="108"/>
       <c r="R11" s="35"/>
       <c r="S11" s="111"/>
-      <c r="T11" s="121"/>
+      <c r="T11" s="120"/>
       <c r="U11" s="111"/>
       <c r="V11" s="109"/>
       <c r="W11" s="109"/>
       <c r="X11" s="109"/>
       <c r="Y11" s="111"/>
       <c r="Z11" s="111"/>
-      <c r="AA11" s="121"/>
+      <c r="AA11" s="120"/>
       <c r="AB11" s="111"/>
       <c r="AC11" s="109"/>
       <c r="AD11" s="109"/>
       <c r="AE11" s="109"/>
       <c r="AF11" s="111"/>
       <c r="AG11" s="111"/>
-      <c r="AH11" s="121"/>
+      <c r="AH11" s="120"/>
       <c r="AI11" s="111"/>
       <c r="AJ11" s="109"/>
       <c r="AK11" s="109"/>
       <c r="AL11" s="109"/>
       <c r="AM11" s="111"/>
       <c r="AN11" s="111"/>
-      <c r="AO11" s="121"/>
+      <c r="AO11" s="120"/>
       <c r="AP11" s="111"/>
       <c r="AQ11" s="109"/>
       <c r="AR11" s="109"/>
       <c r="AS11" s="109"/>
       <c r="AT11" s="111"/>
       <c r="AU11" s="111"/>
-      <c r="AV11" s="121"/>
+      <c r="AV11" s="120"/>
       <c r="AW11" s="111"/>
       <c r="AX11" s="109"/>
       <c r="AY11" s="109"/>
       <c r="AZ11" s="109"/>
       <c r="BA11" s="111"/>
       <c r="BB11" s="111"/>
-      <c r="BC11" s="121"/>
+      <c r="BC11" s="120"/>
       <c r="BD11" s="111"/>
       <c r="BE11" s="109"/>
       <c r="BF11" s="109"/>
       <c r="BG11" s="109"/>
       <c r="BH11" s="111"/>
       <c r="BI11" s="111"/>
-      <c r="BJ11" s="121"/>
+      <c r="BJ11" s="120"/>
       <c r="BK11" s="111"/>
       <c r="BL11" s="109"/>
       <c r="BM11" s="109"/>
@@ -6766,7 +6112,7 @@
       <c r="C12" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="120" t="s">
+      <c r="D12" s="119" t="s">
         <v>42</v>
       </c>
       <c r="E12" s="104">
@@ -6784,55 +6130,55 @@
       <c r="K12" s="104"/>
       <c r="L12" s="104"/>
       <c r="M12" s="104"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="120"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
       <c r="P12" s="104"/>
       <c r="Q12" s="108"/>
       <c r="R12" s="35"/>
       <c r="S12" s="111"/>
-      <c r="T12" s="121"/>
+      <c r="T12" s="120"/>
       <c r="U12" s="111"/>
       <c r="V12" s="109"/>
       <c r="W12" s="109"/>
       <c r="X12" s="109"/>
       <c r="Y12" s="111"/>
       <c r="Z12" s="111"/>
-      <c r="AA12" s="121"/>
+      <c r="AA12" s="120"/>
       <c r="AB12" s="111"/>
       <c r="AC12" s="109"/>
       <c r="AD12" s="109"/>
       <c r="AE12" s="109"/>
       <c r="AF12" s="111"/>
       <c r="AG12" s="111"/>
-      <c r="AH12" s="121"/>
+      <c r="AH12" s="120"/>
       <c r="AI12" s="111"/>
       <c r="AJ12" s="109"/>
       <c r="AK12" s="109"/>
       <c r="AL12" s="109"/>
       <c r="AM12" s="111"/>
       <c r="AN12" s="111"/>
-      <c r="AO12" s="121"/>
+      <c r="AO12" s="120"/>
       <c r="AP12" s="111"/>
       <c r="AQ12" s="109"/>
       <c r="AR12" s="109"/>
       <c r="AS12" s="109"/>
       <c r="AT12" s="111"/>
       <c r="AU12" s="111"/>
-      <c r="AV12" s="121"/>
+      <c r="AV12" s="120"/>
       <c r="AW12" s="111"/>
       <c r="AX12" s="109"/>
       <c r="AY12" s="109"/>
       <c r="AZ12" s="109"/>
       <c r="BA12" s="111"/>
       <c r="BB12" s="111"/>
-      <c r="BC12" s="121"/>
+      <c r="BC12" s="120"/>
       <c r="BD12" s="111"/>
       <c r="BE12" s="109"/>
       <c r="BF12" s="109"/>
       <c r="BG12" s="109"/>
       <c r="BH12" s="111"/>
       <c r="BI12" s="111"/>
-      <c r="BJ12" s="121"/>
+      <c r="BJ12" s="120"/>
       <c r="BK12" s="111"/>
       <c r="BL12" s="109"/>
       <c r="BM12" s="109"/>
@@ -6864,7 +6210,7 @@
       <c r="C13" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="120" t="s">
+      <c r="D13" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="104">
@@ -6886,55 +6232,55 @@
       <c r="K13" s="104"/>
       <c r="L13" s="104"/>
       <c r="M13" s="104"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
       <c r="P13" s="104"/>
       <c r="Q13" s="108"/>
       <c r="R13" s="35"/>
       <c r="S13" s="111"/>
-      <c r="T13" s="121"/>
+      <c r="T13" s="120"/>
       <c r="U13" s="111"/>
       <c r="V13" s="109"/>
       <c r="W13" s="109"/>
       <c r="X13" s="109"/>
       <c r="Y13" s="111"/>
       <c r="Z13" s="111"/>
-      <c r="AA13" s="121"/>
+      <c r="AA13" s="120"/>
       <c r="AB13" s="111"/>
       <c r="AC13" s="109"/>
       <c r="AD13" s="109"/>
       <c r="AE13" s="109"/>
       <c r="AF13" s="111"/>
       <c r="AG13" s="111"/>
-      <c r="AH13" s="121"/>
+      <c r="AH13" s="120"/>
       <c r="AI13" s="111"/>
       <c r="AJ13" s="109"/>
       <c r="AK13" s="109"/>
       <c r="AL13" s="109"/>
       <c r="AM13" s="111"/>
       <c r="AN13" s="111"/>
-      <c r="AO13" s="121"/>
+      <c r="AO13" s="120"/>
       <c r="AP13" s="111"/>
       <c r="AQ13" s="109"/>
       <c r="AR13" s="109"/>
       <c r="AS13" s="109"/>
       <c r="AT13" s="111"/>
       <c r="AU13" s="111"/>
-      <c r="AV13" s="121"/>
+      <c r="AV13" s="120"/>
       <c r="AW13" s="111"/>
       <c r="AX13" s="109"/>
       <c r="AY13" s="109"/>
       <c r="AZ13" s="109"/>
       <c r="BA13" s="111"/>
       <c r="BB13" s="111"/>
-      <c r="BC13" s="121"/>
+      <c r="BC13" s="120"/>
       <c r="BD13" s="111"/>
       <c r="BE13" s="109"/>
       <c r="BF13" s="109"/>
       <c r="BG13" s="109"/>
       <c r="BH13" s="111"/>
       <c r="BI13" s="111"/>
-      <c r="BJ13" s="121"/>
+      <c r="BJ13" s="120"/>
       <c r="BK13" s="111"/>
       <c r="BL13" s="109"/>
       <c r="BM13" s="109"/>
@@ -6957,7 +6303,7 @@
       <c r="CD13" s="111"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:136">
-      <c r="A14" s="122" t="s">
+      <c r="A14" s="121" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="102" t="s">
@@ -6966,7 +6312,7 @@
       <c r="C14" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="120" t="s">
+      <c r="D14" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="104">
@@ -6988,55 +6334,55 @@
       <c r="K14" s="104"/>
       <c r="L14" s="104"/>
       <c r="M14" s="104"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="120"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="119"/>
       <c r="P14" s="104"/>
       <c r="Q14" s="108"/>
       <c r="R14" s="35"/>
       <c r="S14" s="111"/>
-      <c r="T14" s="121"/>
+      <c r="T14" s="120"/>
       <c r="U14" s="111"/>
       <c r="V14" s="109"/>
       <c r="W14" s="109"/>
       <c r="X14" s="109"/>
       <c r="Y14" s="111"/>
       <c r="Z14" s="111"/>
-      <c r="AA14" s="121"/>
+      <c r="AA14" s="120"/>
       <c r="AB14" s="111"/>
       <c r="AC14" s="109"/>
       <c r="AD14" s="109"/>
       <c r="AE14" s="109"/>
       <c r="AF14" s="111"/>
       <c r="AG14" s="111"/>
-      <c r="AH14" s="121"/>
+      <c r="AH14" s="120"/>
       <c r="AI14" s="111"/>
       <c r="AJ14" s="109"/>
       <c r="AK14" s="109"/>
       <c r="AL14" s="109"/>
       <c r="AM14" s="111"/>
       <c r="AN14" s="111"/>
-      <c r="AO14" s="121"/>
+      <c r="AO14" s="120"/>
       <c r="AP14" s="111"/>
       <c r="AQ14" s="109"/>
       <c r="AR14" s="109"/>
       <c r="AS14" s="109"/>
       <c r="AT14" s="111"/>
       <c r="AU14" s="111"/>
-      <c r="AV14" s="121"/>
+      <c r="AV14" s="120"/>
       <c r="AW14" s="111"/>
       <c r="AX14" s="109"/>
       <c r="AY14" s="109"/>
       <c r="AZ14" s="109"/>
       <c r="BA14" s="111"/>
       <c r="BB14" s="111"/>
-      <c r="BC14" s="121"/>
+      <c r="BC14" s="120"/>
       <c r="BD14" s="111"/>
       <c r="BE14" s="109"/>
       <c r="BF14" s="109"/>
       <c r="BG14" s="109"/>
       <c r="BH14" s="111"/>
       <c r="BI14" s="111"/>
-      <c r="BJ14" s="121"/>
+      <c r="BJ14" s="120"/>
       <c r="BK14" s="111"/>
       <c r="BL14" s="109"/>
       <c r="BM14" s="109"/>
@@ -7059,7 +6405,7 @@
       <c r="CD14" s="111"/>
     </row>
     <row r="15" ht="27" customHeight="1" spans="1:136">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="121" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="102" t="s">
@@ -7068,7 +6414,7 @@
       <c r="C15" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="120" t="s">
+      <c r="D15" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E15" s="104">
@@ -7090,55 +6436,55 @@
       <c r="K15" s="104"/>
       <c r="L15" s="104"/>
       <c r="M15" s="104"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="119"/>
       <c r="P15" s="104"/>
       <c r="Q15" s="108"/>
       <c r="R15" s="35"/>
       <c r="S15" s="111"/>
-      <c r="T15" s="121"/>
+      <c r="T15" s="120"/>
       <c r="U15" s="111"/>
       <c r="V15" s="109"/>
       <c r="W15" s="109"/>
       <c r="X15" s="109"/>
       <c r="Y15" s="111"/>
       <c r="Z15" s="111"/>
-      <c r="AA15" s="121"/>
+      <c r="AA15" s="120"/>
       <c r="AB15" s="111"/>
       <c r="AC15" s="109"/>
       <c r="AD15" s="109"/>
       <c r="AE15" s="109"/>
       <c r="AF15" s="111"/>
       <c r="AG15" s="111"/>
-      <c r="AH15" s="121"/>
+      <c r="AH15" s="120"/>
       <c r="AI15" s="111"/>
       <c r="AJ15" s="109"/>
       <c r="AK15" s="109"/>
       <c r="AL15" s="109"/>
       <c r="AM15" s="111"/>
       <c r="AN15" s="111"/>
-      <c r="AO15" s="121"/>
+      <c r="AO15" s="120"/>
       <c r="AP15" s="111"/>
       <c r="AQ15" s="109"/>
       <c r="AR15" s="109"/>
       <c r="AS15" s="109"/>
       <c r="AT15" s="111"/>
       <c r="AU15" s="111"/>
-      <c r="AV15" s="121"/>
+      <c r="AV15" s="120"/>
       <c r="AW15" s="111"/>
       <c r="AX15" s="109"/>
       <c r="AY15" s="109"/>
       <c r="AZ15" s="109"/>
       <c r="BA15" s="111"/>
       <c r="BB15" s="111"/>
-      <c r="BC15" s="121"/>
+      <c r="BC15" s="120"/>
       <c r="BD15" s="111"/>
       <c r="BE15" s="109"/>
       <c r="BF15" s="109"/>
       <c r="BG15" s="109"/>
       <c r="BH15" s="111"/>
       <c r="BI15" s="111"/>
-      <c r="BJ15" s="121"/>
+      <c r="BJ15" s="120"/>
       <c r="BK15" s="111"/>
       <c r="BL15" s="109"/>
       <c r="BM15" s="109"/>
@@ -7170,7 +6516,7 @@
       <c r="C16" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="119" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="104">
@@ -7192,55 +6538,55 @@
       <c r="K16" s="104"/>
       <c r="L16" s="104"/>
       <c r="M16" s="104"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="120"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
       <c r="P16" s="104"/>
       <c r="Q16" s="108"/>
       <c r="R16" s="35"/>
       <c r="S16" s="111"/>
-      <c r="T16" s="121"/>
+      <c r="T16" s="120"/>
       <c r="U16" s="111"/>
       <c r="V16" s="109"/>
       <c r="W16" s="109"/>
       <c r="X16" s="109"/>
       <c r="Y16" s="111"/>
       <c r="Z16" s="111"/>
-      <c r="AA16" s="121"/>
+      <c r="AA16" s="120"/>
       <c r="AB16" s="111"/>
       <c r="AC16" s="109"/>
       <c r="AD16" s="109"/>
       <c r="AE16" s="109"/>
       <c r="AF16" s="111"/>
       <c r="AG16" s="111"/>
-      <c r="AH16" s="121"/>
+      <c r="AH16" s="120"/>
       <c r="AI16" s="111"/>
       <c r="AJ16" s="109"/>
       <c r="AK16" s="109"/>
       <c r="AL16" s="109"/>
       <c r="AM16" s="111"/>
       <c r="AN16" s="111"/>
-      <c r="AO16" s="121"/>
+      <c r="AO16" s="120"/>
       <c r="AP16" s="111"/>
       <c r="AQ16" s="109"/>
       <c r="AR16" s="109"/>
       <c r="AS16" s="109"/>
       <c r="AT16" s="111"/>
       <c r="AU16" s="111"/>
-      <c r="AV16" s="121"/>
+      <c r="AV16" s="120"/>
       <c r="AW16" s="111"/>
       <c r="AX16" s="109"/>
       <c r="AY16" s="109"/>
       <c r="AZ16" s="109"/>
       <c r="BA16" s="111"/>
       <c r="BB16" s="111"/>
-      <c r="BC16" s="121"/>
+      <c r="BC16" s="120"/>
       <c r="BD16" s="111"/>
       <c r="BE16" s="109"/>
       <c r="BF16" s="109"/>
       <c r="BG16" s="109"/>
       <c r="BH16" s="111"/>
       <c r="BI16" s="111"/>
-      <c r="BJ16" s="121"/>
+      <c r="BJ16" s="120"/>
       <c r="BK16" s="111"/>
       <c r="BL16" s="109"/>
       <c r="BM16" s="109"/>
@@ -7272,7 +6618,7 @@
       <c r="C17" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="120" t="s">
+      <c r="D17" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="104">
@@ -7294,55 +6640,55 @@
       <c r="K17" s="104"/>
       <c r="L17" s="104"/>
       <c r="M17" s="104"/>
-      <c r="N17" s="120"/>
-      <c r="O17" s="120"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
       <c r="P17" s="104"/>
       <c r="Q17" s="108"/>
       <c r="R17" s="35"/>
       <c r="S17" s="111"/>
-      <c r="T17" s="121"/>
+      <c r="T17" s="120"/>
       <c r="U17" s="111"/>
       <c r="V17" s="109"/>
       <c r="W17" s="109"/>
       <c r="X17" s="109"/>
       <c r="Y17" s="111"/>
       <c r="Z17" s="111"/>
-      <c r="AA17" s="121"/>
+      <c r="AA17" s="120"/>
       <c r="AB17" s="111"/>
       <c r="AC17" s="109"/>
       <c r="AD17" s="109"/>
       <c r="AE17" s="109"/>
       <c r="AF17" s="111"/>
       <c r="AG17" s="111"/>
-      <c r="AH17" s="121"/>
+      <c r="AH17" s="120"/>
       <c r="AI17" s="111"/>
       <c r="AJ17" s="109"/>
       <c r="AK17" s="109"/>
       <c r="AL17" s="109"/>
       <c r="AM17" s="111"/>
       <c r="AN17" s="111"/>
-      <c r="AO17" s="121"/>
+      <c r="AO17" s="120"/>
       <c r="AP17" s="111"/>
       <c r="AQ17" s="109"/>
       <c r="AR17" s="109"/>
       <c r="AS17" s="109"/>
       <c r="AT17" s="111"/>
       <c r="AU17" s="111"/>
-      <c r="AV17" s="121"/>
+      <c r="AV17" s="120"/>
       <c r="AW17" s="111"/>
       <c r="AX17" s="109"/>
       <c r="AY17" s="109"/>
       <c r="AZ17" s="109"/>
       <c r="BA17" s="111"/>
       <c r="BB17" s="111"/>
-      <c r="BC17" s="121"/>
+      <c r="BC17" s="120"/>
       <c r="BD17" s="111"/>
       <c r="BE17" s="109"/>
       <c r="BF17" s="109"/>
       <c r="BG17" s="109"/>
       <c r="BH17" s="111"/>
       <c r="BI17" s="111"/>
-      <c r="BJ17" s="121"/>
+      <c r="BJ17" s="120"/>
       <c r="BK17" s="111"/>
       <c r="BL17" s="109"/>
       <c r="BM17" s="109"/>
@@ -7374,7 +6720,7 @@
       <c r="C18" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="120" t="s">
+      <c r="D18" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="104">
@@ -7396,55 +6742,55 @@
       <c r="K18" s="104"/>
       <c r="L18" s="104"/>
       <c r="M18" s="104"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
+      <c r="N18" s="119"/>
+      <c r="O18" s="119"/>
       <c r="P18" s="104"/>
       <c r="Q18" s="108"/>
       <c r="R18" s="35"/>
       <c r="S18" s="111"/>
-      <c r="T18" s="121"/>
+      <c r="T18" s="120"/>
       <c r="U18" s="111"/>
       <c r="V18" s="109"/>
       <c r="W18" s="109"/>
       <c r="X18" s="109"/>
       <c r="Y18" s="111"/>
       <c r="Z18" s="111"/>
-      <c r="AA18" s="121"/>
+      <c r="AA18" s="120"/>
       <c r="AB18" s="111"/>
       <c r="AC18" s="109"/>
       <c r="AD18" s="109"/>
       <c r="AE18" s="109"/>
       <c r="AF18" s="111"/>
       <c r="AG18" s="111"/>
-      <c r="AH18" s="121"/>
+      <c r="AH18" s="120"/>
       <c r="AI18" s="111"/>
       <c r="AJ18" s="109"/>
       <c r="AK18" s="109"/>
       <c r="AL18" s="109"/>
       <c r="AM18" s="111"/>
       <c r="AN18" s="111"/>
-      <c r="AO18" s="121"/>
+      <c r="AO18" s="120"/>
       <c r="AP18" s="111"/>
       <c r="AQ18" s="109"/>
       <c r="AR18" s="109"/>
       <c r="AS18" s="109"/>
       <c r="AT18" s="111"/>
       <c r="AU18" s="111"/>
-      <c r="AV18" s="121"/>
+      <c r="AV18" s="120"/>
       <c r="AW18" s="111"/>
       <c r="AX18" s="109"/>
       <c r="AY18" s="109"/>
       <c r="AZ18" s="109"/>
       <c r="BA18" s="111"/>
       <c r="BB18" s="111"/>
-      <c r="BC18" s="121"/>
+      <c r="BC18" s="120"/>
       <c r="BD18" s="111"/>
       <c r="BE18" s="109"/>
       <c r="BF18" s="109"/>
       <c r="BG18" s="109"/>
       <c r="BH18" s="111"/>
       <c r="BI18" s="111"/>
-      <c r="BJ18" s="121"/>
+      <c r="BJ18" s="120"/>
       <c r="BK18" s="111"/>
       <c r="BL18" s="109"/>
       <c r="BM18" s="109"/>
@@ -7476,7 +6822,7 @@
       <c r="C19" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="120" t="s">
+      <c r="D19" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E19" s="104">
@@ -7494,55 +6840,55 @@
       <c r="K19" s="104"/>
       <c r="L19" s="104"/>
       <c r="M19" s="104"/>
-      <c r="N19" s="120"/>
-      <c r="O19" s="120"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
       <c r="P19" s="104"/>
       <c r="Q19" s="108"/>
       <c r="R19" s="35"/>
       <c r="S19" s="111"/>
-      <c r="T19" s="121"/>
+      <c r="T19" s="120"/>
       <c r="U19" s="111"/>
       <c r="V19" s="109"/>
       <c r="W19" s="109"/>
       <c r="X19" s="109"/>
       <c r="Y19" s="111"/>
       <c r="Z19" s="111"/>
-      <c r="AA19" s="121"/>
+      <c r="AA19" s="120"/>
       <c r="AB19" s="111"/>
       <c r="AC19" s="109"/>
       <c r="AD19" s="109"/>
       <c r="AE19" s="109"/>
       <c r="AF19" s="111"/>
       <c r="AG19" s="111"/>
-      <c r="AH19" s="121"/>
+      <c r="AH19" s="120"/>
       <c r="AI19" s="111"/>
       <c r="AJ19" s="109"/>
       <c r="AK19" s="109"/>
       <c r="AL19" s="109"/>
       <c r="AM19" s="111"/>
       <c r="AN19" s="111"/>
-      <c r="AO19" s="121"/>
+      <c r="AO19" s="120"/>
       <c r="AP19" s="111"/>
       <c r="AQ19" s="109"/>
       <c r="AR19" s="109"/>
       <c r="AS19" s="109"/>
       <c r="AT19" s="111"/>
       <c r="AU19" s="111"/>
-      <c r="AV19" s="121"/>
+      <c r="AV19" s="120"/>
       <c r="AW19" s="111"/>
       <c r="AX19" s="109"/>
       <c r="AY19" s="109"/>
       <c r="AZ19" s="109"/>
       <c r="BA19" s="111"/>
       <c r="BB19" s="111"/>
-      <c r="BC19" s="121"/>
+      <c r="BC19" s="120"/>
       <c r="BD19" s="111"/>
       <c r="BE19" s="109"/>
       <c r="BF19" s="109"/>
       <c r="BG19" s="109"/>
       <c r="BH19" s="111"/>
       <c r="BI19" s="111"/>
-      <c r="BJ19" s="121"/>
+      <c r="BJ19" s="120"/>
       <c r="BK19" s="111"/>
       <c r="BL19" s="109"/>
       <c r="BM19" s="109"/>
@@ -7574,7 +6920,7 @@
       <c r="C20" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="120" t="s">
+      <c r="D20" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="104">
@@ -7596,55 +6942,55 @@
       <c r="K20" s="104"/>
       <c r="L20" s="104"/>
       <c r="M20" s="104"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="120"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
       <c r="P20" s="104"/>
       <c r="Q20" s="108"/>
       <c r="R20" s="35"/>
       <c r="S20" s="111"/>
-      <c r="T20" s="121"/>
+      <c r="T20" s="120"/>
       <c r="U20" s="111"/>
       <c r="V20" s="109"/>
       <c r="W20" s="109"/>
       <c r="X20" s="109"/>
       <c r="Y20" s="111"/>
       <c r="Z20" s="111"/>
-      <c r="AA20" s="121"/>
+      <c r="AA20" s="120"/>
       <c r="AB20" s="111"/>
       <c r="AC20" s="109"/>
       <c r="AD20" s="109"/>
       <c r="AE20" s="109"/>
       <c r="AF20" s="111"/>
       <c r="AG20" s="111"/>
-      <c r="AH20" s="121"/>
+      <c r="AH20" s="120"/>
       <c r="AI20" s="111"/>
       <c r="AJ20" s="109"/>
       <c r="AK20" s="109"/>
       <c r="AL20" s="109"/>
       <c r="AM20" s="111"/>
       <c r="AN20" s="111"/>
-      <c r="AO20" s="121"/>
+      <c r="AO20" s="120"/>
       <c r="AP20" s="111"/>
       <c r="AQ20" s="109"/>
       <c r="AR20" s="109"/>
       <c r="AS20" s="109"/>
       <c r="AT20" s="111"/>
       <c r="AU20" s="111"/>
-      <c r="AV20" s="121"/>
+      <c r="AV20" s="120"/>
       <c r="AW20" s="111"/>
       <c r="AX20" s="109"/>
       <c r="AY20" s="109"/>
       <c r="AZ20" s="109"/>
       <c r="BA20" s="111"/>
       <c r="BB20" s="111"/>
-      <c r="BC20" s="121"/>
+      <c r="BC20" s="120"/>
       <c r="BD20" s="111"/>
       <c r="BE20" s="109"/>
       <c r="BF20" s="109"/>
       <c r="BG20" s="109"/>
       <c r="BH20" s="111"/>
       <c r="BI20" s="111"/>
-      <c r="BJ20" s="121"/>
+      <c r="BJ20" s="120"/>
       <c r="BK20" s="111"/>
       <c r="BL20" s="109"/>
       <c r="BM20" s="109"/>
@@ -7676,7 +7022,7 @@
       <c r="C21" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="104">
@@ -7698,55 +7044,55 @@
       <c r="K21" s="104"/>
       <c r="L21" s="104"/>
       <c r="M21" s="104"/>
-      <c r="N21" s="120"/>
-      <c r="O21" s="120"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
       <c r="P21" s="104"/>
       <c r="Q21" s="108"/>
       <c r="R21" s="35"/>
       <c r="S21" s="111"/>
-      <c r="T21" s="121"/>
+      <c r="T21" s="120"/>
       <c r="U21" s="111"/>
       <c r="V21" s="109"/>
       <c r="W21" s="109"/>
       <c r="X21" s="109"/>
       <c r="Y21" s="111"/>
       <c r="Z21" s="111"/>
-      <c r="AA21" s="121"/>
+      <c r="AA21" s="120"/>
       <c r="AB21" s="111"/>
       <c r="AC21" s="109"/>
       <c r="AD21" s="109"/>
       <c r="AE21" s="109"/>
       <c r="AF21" s="111"/>
       <c r="AG21" s="111"/>
-      <c r="AH21" s="121"/>
+      <c r="AH21" s="120"/>
       <c r="AI21" s="111"/>
       <c r="AJ21" s="109"/>
       <c r="AK21" s="109"/>
       <c r="AL21" s="109"/>
       <c r="AM21" s="111"/>
       <c r="AN21" s="111"/>
-      <c r="AO21" s="121"/>
+      <c r="AO21" s="120"/>
       <c r="AP21" s="111"/>
       <c r="AQ21" s="109"/>
       <c r="AR21" s="109"/>
       <c r="AS21" s="109"/>
       <c r="AT21" s="111"/>
       <c r="AU21" s="111"/>
-      <c r="AV21" s="121"/>
+      <c r="AV21" s="120"/>
       <c r="AW21" s="111"/>
       <c r="AX21" s="109"/>
       <c r="AY21" s="109"/>
       <c r="AZ21" s="109"/>
       <c r="BA21" s="111"/>
       <c r="BB21" s="111"/>
-      <c r="BC21" s="121"/>
+      <c r="BC21" s="120"/>
       <c r="BD21" s="111"/>
       <c r="BE21" s="109"/>
       <c r="BF21" s="109"/>
       <c r="BG21" s="109"/>
       <c r="BH21" s="111"/>
       <c r="BI21" s="111"/>
-      <c r="BJ21" s="121"/>
+      <c r="BJ21" s="120"/>
       <c r="BK21" s="111"/>
       <c r="BL21" s="109"/>
       <c r="BM21" s="109"/>
@@ -7778,7 +7124,7 @@
       <c r="C22" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="120" t="s">
+      <c r="D22" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="104">
@@ -7800,55 +7146,55 @@
       <c r="K22" s="104"/>
       <c r="L22" s="104"/>
       <c r="M22" s="104"/>
-      <c r="N22" s="120"/>
-      <c r="O22" s="120"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
       <c r="P22" s="104"/>
       <c r="Q22" s="108"/>
       <c r="R22" s="35"/>
       <c r="S22" s="111"/>
-      <c r="T22" s="121"/>
+      <c r="T22" s="120"/>
       <c r="U22" s="111"/>
       <c r="V22" s="109"/>
       <c r="W22" s="109"/>
       <c r="X22" s="109"/>
       <c r="Y22" s="111"/>
       <c r="Z22" s="111"/>
-      <c r="AA22" s="121"/>
+      <c r="AA22" s="120"/>
       <c r="AB22" s="111"/>
       <c r="AC22" s="109"/>
       <c r="AD22" s="109"/>
       <c r="AE22" s="109"/>
       <c r="AF22" s="111"/>
       <c r="AG22" s="111"/>
-      <c r="AH22" s="121"/>
+      <c r="AH22" s="120"/>
       <c r="AI22" s="111"/>
       <c r="AJ22" s="109"/>
       <c r="AK22" s="109"/>
       <c r="AL22" s="109"/>
       <c r="AM22" s="111"/>
       <c r="AN22" s="111"/>
-      <c r="AO22" s="121"/>
+      <c r="AO22" s="120"/>
       <c r="AP22" s="111"/>
       <c r="AQ22" s="109"/>
       <c r="AR22" s="109"/>
       <c r="AS22" s="109"/>
       <c r="AT22" s="111"/>
       <c r="AU22" s="111"/>
-      <c r="AV22" s="121"/>
+      <c r="AV22" s="120"/>
       <c r="AW22" s="111"/>
       <c r="AX22" s="109"/>
       <c r="AY22" s="109"/>
       <c r="AZ22" s="109"/>
       <c r="BA22" s="111"/>
       <c r="BB22" s="111"/>
-      <c r="BC22" s="121"/>
+      <c r="BC22" s="120"/>
       <c r="BD22" s="111"/>
       <c r="BE22" s="109"/>
       <c r="BF22" s="109"/>
       <c r="BG22" s="109"/>
       <c r="BH22" s="111"/>
       <c r="BI22" s="111"/>
-      <c r="BJ22" s="121"/>
+      <c r="BJ22" s="120"/>
       <c r="BK22" s="111"/>
       <c r="BL22" s="109"/>
       <c r="BM22" s="109"/>
@@ -7880,7 +7226,7 @@
       <c r="C23" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="120" t="s">
+      <c r="D23" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="104">
@@ -7902,55 +7248,55 @@
       <c r="K23" s="104"/>
       <c r="L23" s="104"/>
       <c r="M23" s="104"/>
-      <c r="N23" s="120"/>
-      <c r="O23" s="120"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
       <c r="P23" s="104"/>
       <c r="Q23" s="108"/>
       <c r="R23" s="35"/>
       <c r="S23" s="111"/>
-      <c r="T23" s="121"/>
+      <c r="T23" s="120"/>
       <c r="U23" s="111"/>
       <c r="V23" s="109"/>
       <c r="W23" s="109"/>
       <c r="X23" s="109"/>
       <c r="Y23" s="111"/>
       <c r="Z23" s="111"/>
-      <c r="AA23" s="121"/>
+      <c r="AA23" s="120"/>
       <c r="AB23" s="111"/>
       <c r="AC23" s="109"/>
       <c r="AD23" s="109"/>
       <c r="AE23" s="109"/>
       <c r="AF23" s="111"/>
       <c r="AG23" s="111"/>
-      <c r="AH23" s="121"/>
+      <c r="AH23" s="120"/>
       <c r="AI23" s="111"/>
       <c r="AJ23" s="109"/>
       <c r="AK23" s="109"/>
       <c r="AL23" s="109"/>
       <c r="AM23" s="111"/>
       <c r="AN23" s="111"/>
-      <c r="AO23" s="121"/>
+      <c r="AO23" s="120"/>
       <c r="AP23" s="111"/>
       <c r="AQ23" s="109"/>
       <c r="AR23" s="109"/>
       <c r="AS23" s="109"/>
       <c r="AT23" s="111"/>
       <c r="AU23" s="111"/>
-      <c r="AV23" s="121"/>
+      <c r="AV23" s="120"/>
       <c r="AW23" s="111"/>
       <c r="AX23" s="109"/>
       <c r="AY23" s="109"/>
       <c r="AZ23" s="109"/>
       <c r="BA23" s="111"/>
       <c r="BB23" s="111"/>
-      <c r="BC23" s="121"/>
+      <c r="BC23" s="120"/>
       <c r="BD23" s="111"/>
       <c r="BE23" s="109"/>
       <c r="BF23" s="109"/>
       <c r="BG23" s="109"/>
       <c r="BH23" s="111"/>
       <c r="BI23" s="111"/>
-      <c r="BJ23" s="121"/>
+      <c r="BJ23" s="120"/>
       <c r="BK23" s="111"/>
       <c r="BL23" s="109"/>
       <c r="BM23" s="109"/>
@@ -7982,7 +7328,7 @@
       <c r="C24" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="120" t="s">
+      <c r="D24" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="104">
@@ -8004,55 +7350,55 @@
       <c r="K24" s="104"/>
       <c r="L24" s="104"/>
       <c r="M24" s="104"/>
-      <c r="N24" s="120"/>
-      <c r="O24" s="120"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
       <c r="P24" s="104"/>
       <c r="Q24" s="108"/>
       <c r="R24" s="35"/>
       <c r="S24" s="111"/>
-      <c r="T24" s="121"/>
+      <c r="T24" s="120"/>
       <c r="U24" s="111"/>
       <c r="V24" s="109"/>
       <c r="W24" s="109"/>
       <c r="X24" s="109"/>
       <c r="Y24" s="111"/>
       <c r="Z24" s="111"/>
-      <c r="AA24" s="121"/>
+      <c r="AA24" s="120"/>
       <c r="AB24" s="111"/>
       <c r="AC24" s="109"/>
       <c r="AD24" s="109"/>
       <c r="AE24" s="109"/>
       <c r="AF24" s="111"/>
       <c r="AG24" s="111"/>
-      <c r="AH24" s="121"/>
+      <c r="AH24" s="120"/>
       <c r="AI24" s="111"/>
       <c r="AJ24" s="109"/>
       <c r="AK24" s="109"/>
       <c r="AL24" s="109"/>
       <c r="AM24" s="111"/>
       <c r="AN24" s="111"/>
-      <c r="AO24" s="121"/>
+      <c r="AO24" s="120"/>
       <c r="AP24" s="111"/>
       <c r="AQ24" s="109"/>
       <c r="AR24" s="109"/>
       <c r="AS24" s="109"/>
       <c r="AT24" s="111"/>
       <c r="AU24" s="111"/>
-      <c r="AV24" s="121"/>
+      <c r="AV24" s="120"/>
       <c r="AW24" s="111"/>
       <c r="AX24" s="109"/>
       <c r="AY24" s="109"/>
       <c r="AZ24" s="109"/>
       <c r="BA24" s="111"/>
       <c r="BB24" s="111"/>
-      <c r="BC24" s="121"/>
+      <c r="BC24" s="120"/>
       <c r="BD24" s="111"/>
       <c r="BE24" s="109"/>
       <c r="BF24" s="109"/>
       <c r="BG24" s="109"/>
       <c r="BH24" s="111"/>
       <c r="BI24" s="111"/>
-      <c r="BJ24" s="121"/>
+      <c r="BJ24" s="120"/>
       <c r="BK24" s="111"/>
       <c r="BL24" s="109"/>
       <c r="BM24" s="109"/>
@@ -8075,7 +7421,7 @@
       <c r="CD24" s="111"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:136">
-      <c r="A25" s="122" t="s">
+      <c r="A25" s="121" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="102" t="s">
@@ -8084,7 +7430,7 @@
       <c r="C25" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="120" t="s">
+      <c r="D25" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E25" s="104">
@@ -8106,71 +7452,71 @@
       <c r="K25" s="104"/>
       <c r="L25" s="104"/>
       <c r="M25" s="104"/>
-      <c r="N25" s="120"/>
-      <c r="O25" s="120"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="119"/>
       <c r="P25" s="104"/>
-      <c r="Q25" s="123"/>
-      <c r="R25" s="124"/>
-      <c r="S25" s="124"/>
-      <c r="T25" s="124"/>
-      <c r="U25" s="124"/>
-      <c r="V25" s="125"/>
-      <c r="W25" s="123"/>
-      <c r="X25" s="123"/>
-      <c r="Y25" s="124"/>
-      <c r="Z25" s="124"/>
-      <c r="AA25" s="124"/>
-      <c r="AB25" s="124"/>
-      <c r="AC25" s="124"/>
-      <c r="AD25" s="123"/>
-      <c r="AE25" s="123"/>
-      <c r="AF25" s="124"/>
-      <c r="AG25" s="124"/>
-      <c r="AH25" s="124"/>
-      <c r="AI25" s="124"/>
-      <c r="AJ25" s="124"/>
-      <c r="AK25" s="123"/>
-      <c r="AL25" s="123"/>
-      <c r="AM25" s="124"/>
-      <c r="AN25" s="124"/>
-      <c r="AO25" s="124"/>
-      <c r="AP25" s="124"/>
-      <c r="AQ25" s="124"/>
-      <c r="AR25" s="123"/>
-      <c r="AS25" s="123"/>
-      <c r="AT25" s="124"/>
-      <c r="AU25" s="124"/>
-      <c r="AV25" s="124"/>
-      <c r="AW25" s="124"/>
-      <c r="AX25" s="124"/>
-      <c r="AY25" s="123"/>
-      <c r="AZ25" s="123"/>
-      <c r="BA25" s="124"/>
-      <c r="BB25" s="124"/>
-      <c r="BC25" s="124"/>
-      <c r="BD25" s="124"/>
-      <c r="BE25" s="124"/>
-      <c r="BF25" s="123"/>
-      <c r="BG25" s="123"/>
-      <c r="BH25" s="124"/>
-      <c r="BI25" s="124"/>
-      <c r="BJ25" s="124"/>
-      <c r="BK25" s="124"/>
-      <c r="BL25" s="124"/>
-      <c r="BM25" s="123"/>
-      <c r="BN25" s="123"/>
-      <c r="BO25" s="124"/>
-      <c r="BP25" s="124"/>
-      <c r="BQ25" s="124"/>
-      <c r="BR25" s="124"/>
-      <c r="BS25" s="124"/>
-      <c r="BT25" s="124"/>
-      <c r="BU25" s="124"/>
-      <c r="BV25" s="124"/>
-      <c r="BW25" s="124"/>
-      <c r="BX25" s="124"/>
-      <c r="BY25" s="124"/>
-      <c r="BZ25" s="124"/>
+      <c r="Q25" s="122"/>
+      <c r="R25" s="123"/>
+      <c r="S25" s="123"/>
+      <c r="T25" s="123"/>
+      <c r="U25" s="123"/>
+      <c r="V25" s="124"/>
+      <c r="W25" s="122"/>
+      <c r="X25" s="122"/>
+      <c r="Y25" s="123"/>
+      <c r="Z25" s="123"/>
+      <c r="AA25" s="123"/>
+      <c r="AB25" s="123"/>
+      <c r="AC25" s="123"/>
+      <c r="AD25" s="122"/>
+      <c r="AE25" s="122"/>
+      <c r="AF25" s="123"/>
+      <c r="AG25" s="123"/>
+      <c r="AH25" s="123"/>
+      <c r="AI25" s="123"/>
+      <c r="AJ25" s="123"/>
+      <c r="AK25" s="122"/>
+      <c r="AL25" s="122"/>
+      <c r="AM25" s="123"/>
+      <c r="AN25" s="123"/>
+      <c r="AO25" s="123"/>
+      <c r="AP25" s="123"/>
+      <c r="AQ25" s="123"/>
+      <c r="AR25" s="122"/>
+      <c r="AS25" s="122"/>
+      <c r="AT25" s="123"/>
+      <c r="AU25" s="123"/>
+      <c r="AV25" s="123"/>
+      <c r="AW25" s="123"/>
+      <c r="AX25" s="123"/>
+      <c r="AY25" s="122"/>
+      <c r="AZ25" s="122"/>
+      <c r="BA25" s="123"/>
+      <c r="BB25" s="123"/>
+      <c r="BC25" s="123"/>
+      <c r="BD25" s="123"/>
+      <c r="BE25" s="123"/>
+      <c r="BF25" s="122"/>
+      <c r="BG25" s="122"/>
+      <c r="BH25" s="123"/>
+      <c r="BI25" s="123"/>
+      <c r="BJ25" s="123"/>
+      <c r="BK25" s="123"/>
+      <c r="BL25" s="123"/>
+      <c r="BM25" s="122"/>
+      <c r="BN25" s="122"/>
+      <c r="BO25" s="123"/>
+      <c r="BP25" s="123"/>
+      <c r="BQ25" s="123"/>
+      <c r="BR25" s="123"/>
+      <c r="BS25" s="123"/>
+      <c r="BT25" s="123"/>
+      <c r="BU25" s="123"/>
+      <c r="BV25" s="123"/>
+      <c r="BW25" s="123"/>
+      <c r="BX25" s="123"/>
+      <c r="BY25" s="123"/>
+      <c r="BZ25" s="123"/>
       <c r="CA25" s="15"/>
       <c r="CB25" s="15"/>
       <c r="CC25" s="15"/>
@@ -8186,13 +7532,13 @@
       <c r="C26" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="120" t="s">
+      <c r="D26" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="104">
         <v>46152</v>
       </c>
-      <c r="F26" s="126">
+      <c r="F26" s="125">
         <v>46162</v>
       </c>
       <c r="G26" s="105"/>
@@ -8208,59 +7554,59 @@
       <c r="K26" s="104"/>
       <c r="L26" s="104"/>
       <c r="M26" s="104"/>
-      <c r="N26" s="120"/>
-      <c r="O26" s="120"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="119"/>
       <c r="P26" s="104"/>
-      <c r="Q26" s="123"/>
+      <c r="Q26" s="122"/>
       <c r="R26" s="111"/>
       <c r="S26" s="15"/>
       <c r="T26" s="15"/>
       <c r="U26" s="111"/>
       <c r="V26" s="111"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="124"/>
+      <c r="W26" s="123"/>
+      <c r="X26" s="123"/>
       <c r="Y26" s="15"/>
       <c r="Z26" s="15"/>
       <c r="AA26" s="15"/>
       <c r="AB26" s="111"/>
       <c r="AC26" s="111"/>
-      <c r="AD26" s="124"/>
-      <c r="AE26" s="124"/>
+      <c r="AD26" s="123"/>
+      <c r="AE26" s="123"/>
       <c r="AF26" s="111"/>
       <c r="AG26" s="111"/>
       <c r="AH26" s="110"/>
       <c r="AI26" s="111"/>
       <c r="AJ26" s="111"/>
-      <c r="AK26" s="124"/>
-      <c r="AL26" s="124"/>
+      <c r="AK26" s="123"/>
+      <c r="AL26" s="123"/>
       <c r="AM26" s="110"/>
       <c r="AN26" s="110"/>
       <c r="AO26" s="110"/>
       <c r="AP26" s="111"/>
       <c r="AQ26" s="111"/>
-      <c r="AR26" s="124"/>
-      <c r="AS26" s="124"/>
+      <c r="AR26" s="123"/>
+      <c r="AS26" s="123"/>
       <c r="AT26" s="111"/>
       <c r="AU26" s="111"/>
       <c r="AV26" s="111"/>
       <c r="AW26" s="111"/>
       <c r="AX26" s="111"/>
-      <c r="AY26" s="124"/>
-      <c r="AZ26" s="124"/>
+      <c r="AY26" s="123"/>
+      <c r="AZ26" s="123"/>
       <c r="BA26" s="111"/>
       <c r="BB26" s="111"/>
       <c r="BC26" s="111"/>
       <c r="BD26" s="111"/>
       <c r="BE26" s="111"/>
-      <c r="BF26" s="124"/>
-      <c r="BG26" s="124"/>
+      <c r="BF26" s="123"/>
+      <c r="BG26" s="123"/>
       <c r="BH26" s="111"/>
       <c r="BI26" s="111"/>
       <c r="BJ26" s="111"/>
       <c r="BK26" s="111"/>
       <c r="BL26" s="111"/>
-      <c r="BM26" s="124"/>
-      <c r="BN26" s="124"/>
+      <c r="BM26" s="123"/>
+      <c r="BN26" s="123"/>
       <c r="BO26" s="15"/>
       <c r="BP26" s="15"/>
       <c r="BQ26" s="15"/>
@@ -8288,7 +7634,7 @@
       <c r="C27" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="120" t="s">
+      <c r="D27" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="104">
@@ -8310,59 +7656,59 @@
       <c r="K27" s="104"/>
       <c r="L27" s="104"/>
       <c r="M27" s="104"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="120"/>
+      <c r="N27" s="119"/>
+      <c r="O27" s="119"/>
       <c r="P27" s="104"/>
-      <c r="Q27" s="123"/>
+      <c r="Q27" s="122"/>
       <c r="R27" s="111"/>
       <c r="S27" s="15"/>
       <c r="T27" s="15"/>
       <c r="U27" s="111"/>
       <c r="V27" s="111"/>
-      <c r="W27" s="124"/>
-      <c r="X27" s="124"/>
+      <c r="W27" s="123"/>
+      <c r="X27" s="123"/>
       <c r="Y27" s="15"/>
       <c r="Z27" s="15"/>
       <c r="AA27" s="15"/>
       <c r="AB27" s="111"/>
       <c r="AC27" s="111"/>
-      <c r="AD27" s="124"/>
-      <c r="AE27" s="124"/>
+      <c r="AD27" s="123"/>
+      <c r="AE27" s="123"/>
       <c r="AF27" s="111"/>
       <c r="AG27" s="111"/>
       <c r="AH27" s="110"/>
       <c r="AI27" s="111"/>
       <c r="AJ27" s="111"/>
-      <c r="AK27" s="124"/>
-      <c r="AL27" s="124"/>
+      <c r="AK27" s="123"/>
+      <c r="AL27" s="123"/>
       <c r="AM27" s="110"/>
       <c r="AN27" s="110"/>
       <c r="AO27" s="110"/>
       <c r="AP27" s="111"/>
       <c r="AQ27" s="111"/>
-      <c r="AR27" s="124"/>
-      <c r="AS27" s="124"/>
+      <c r="AR27" s="123"/>
+      <c r="AS27" s="123"/>
       <c r="AT27" s="111"/>
       <c r="AU27" s="111"/>
       <c r="AV27" s="111"/>
       <c r="AW27" s="111"/>
       <c r="AX27" s="111"/>
-      <c r="AY27" s="124"/>
-      <c r="AZ27" s="124"/>
+      <c r="AY27" s="123"/>
+      <c r="AZ27" s="123"/>
       <c r="BA27" s="111"/>
       <c r="BB27" s="111"/>
       <c r="BC27" s="111"/>
       <c r="BD27" s="111"/>
       <c r="BE27" s="111"/>
-      <c r="BF27" s="124"/>
-      <c r="BG27" s="124"/>
+      <c r="BF27" s="123"/>
+      <c r="BG27" s="123"/>
       <c r="BH27" s="111"/>
       <c r="BI27" s="111"/>
       <c r="BJ27" s="111"/>
       <c r="BK27" s="111"/>
       <c r="BL27" s="111"/>
-      <c r="BM27" s="124"/>
-      <c r="BN27" s="124"/>
+      <c r="BM27" s="123"/>
+      <c r="BN27" s="123"/>
       <c r="BO27" s="15"/>
       <c r="BP27" s="15"/>
       <c r="BQ27" s="15"/>
@@ -8406,7 +7752,7 @@
       <c r="I28" s="115">
         <v>9</v>
       </c>
-      <c r="J28" s="117">
+      <c r="J28" s="126">
         <v>0</v>
       </c>
       <c r="K28" s="116"/>
@@ -8415,126 +7761,126 @@
       <c r="N28" s="115"/>
       <c r="O28" s="115"/>
       <c r="P28" s="104"/>
-      <c r="Q28" s="118"/>
-      <c r="R28" s="119"/>
-      <c r="S28" s="119"/>
-      <c r="T28" s="119"/>
-      <c r="U28" s="119"/>
-      <c r="V28" s="119"/>
-      <c r="W28" s="119"/>
-      <c r="X28" s="119"/>
-      <c r="Y28" s="119"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="119"/>
-      <c r="AB28" s="119"/>
-      <c r="AC28" s="119"/>
-      <c r="AD28" s="119"/>
-      <c r="AE28" s="119"/>
-      <c r="AF28" s="119"/>
-      <c r="AG28" s="119"/>
-      <c r="AH28" s="119"/>
-      <c r="AI28" s="119"/>
-      <c r="AJ28" s="119"/>
-      <c r="AK28" s="119"/>
-      <c r="AL28" s="119"/>
-      <c r="AM28" s="119"/>
-      <c r="AN28" s="119"/>
-      <c r="AO28" s="119"/>
-      <c r="AP28" s="119"/>
-      <c r="AQ28" s="119"/>
-      <c r="AR28" s="119"/>
-      <c r="AS28" s="119"/>
-      <c r="AT28" s="119"/>
-      <c r="AU28" s="119"/>
-      <c r="AV28" s="119"/>
-      <c r="AW28" s="119"/>
-      <c r="AX28" s="119"/>
-      <c r="AY28" s="119"/>
-      <c r="AZ28" s="119"/>
-      <c r="BA28" s="119"/>
-      <c r="BB28" s="119"/>
-      <c r="BC28" s="119"/>
-      <c r="BD28" s="119"/>
-      <c r="BE28" s="119"/>
-      <c r="BF28" s="119"/>
-      <c r="BG28" s="119"/>
-      <c r="BH28" s="119"/>
-      <c r="BI28" s="119"/>
-      <c r="BJ28" s="119"/>
-      <c r="BK28" s="119"/>
-      <c r="BL28" s="119"/>
-      <c r="BM28" s="119"/>
-      <c r="BN28" s="119"/>
-      <c r="BO28" s="119"/>
-      <c r="BP28" s="119"/>
-      <c r="BQ28" s="119"/>
-      <c r="BR28" s="119"/>
-      <c r="BS28" s="119"/>
-      <c r="BT28" s="119"/>
-      <c r="BU28" s="119"/>
-      <c r="BV28" s="119"/>
-      <c r="BW28" s="119"/>
-      <c r="BX28" s="119"/>
-      <c r="BY28" s="119"/>
-      <c r="BZ28" s="119"/>
-      <c r="CA28" s="119"/>
-      <c r="CB28" s="119"/>
-      <c r="CC28" s="119"/>
-      <c r="CD28" s="119"/>
-      <c r="CE28" s="119"/>
-      <c r="CF28" s="119"/>
-      <c r="CG28" s="119"/>
-      <c r="CH28" s="119"/>
-      <c r="CI28" s="119"/>
-      <c r="CJ28" s="119"/>
-      <c r="CK28" s="119"/>
-      <c r="CL28" s="119"/>
-      <c r="CM28" s="119"/>
-      <c r="CN28" s="119"/>
-      <c r="CO28" s="119"/>
-      <c r="CP28" s="119"/>
-      <c r="CQ28" s="119"/>
-      <c r="CR28" s="119"/>
-      <c r="CS28" s="119"/>
-      <c r="CT28" s="119"/>
-      <c r="CU28" s="119"/>
-      <c r="CV28" s="119"/>
-      <c r="CW28" s="119"/>
-      <c r="CX28" s="119"/>
-      <c r="CY28" s="119"/>
-      <c r="CZ28" s="119"/>
-      <c r="DA28" s="119"/>
-      <c r="DB28" s="119"/>
-      <c r="DC28" s="119"/>
-      <c r="DD28" s="119"/>
-      <c r="DE28" s="119"/>
-      <c r="DF28" s="119"/>
-      <c r="DG28" s="119"/>
-      <c r="DH28" s="119"/>
-      <c r="DI28" s="119"/>
-      <c r="DJ28" s="119"/>
-      <c r="DK28" s="119"/>
-      <c r="DL28" s="119"/>
-      <c r="DM28" s="119"/>
-      <c r="DN28" s="119"/>
-      <c r="DO28" s="119"/>
-      <c r="DP28" s="119"/>
-      <c r="DQ28" s="119"/>
-      <c r="DR28" s="119"/>
-      <c r="DS28" s="119"/>
-      <c r="DT28" s="119"/>
-      <c r="DU28" s="119"/>
-      <c r="DV28" s="119"/>
-      <c r="DW28" s="119"/>
-      <c r="DX28" s="119"/>
-      <c r="DY28" s="119"/>
-      <c r="DZ28" s="119"/>
-      <c r="EA28" s="119"/>
-      <c r="EB28" s="119"/>
-      <c r="EC28" s="119"/>
-      <c r="ED28" s="119"/>
-      <c r="EE28" s="119"/>
-      <c r="EF28" s="119"/>
+      <c r="Q28" s="117"/>
+      <c r="R28" s="118"/>
+      <c r="S28" s="118"/>
+      <c r="T28" s="118"/>
+      <c r="U28" s="118"/>
+      <c r="V28" s="118"/>
+      <c r="W28" s="118"/>
+      <c r="X28" s="118"/>
+      <c r="Y28" s="118"/>
+      <c r="Z28" s="118"/>
+      <c r="AA28" s="118"/>
+      <c r="AB28" s="118"/>
+      <c r="AC28" s="118"/>
+      <c r="AD28" s="118"/>
+      <c r="AE28" s="118"/>
+      <c r="AF28" s="118"/>
+      <c r="AG28" s="118"/>
+      <c r="AH28" s="118"/>
+      <c r="AI28" s="118"/>
+      <c r="AJ28" s="118"/>
+      <c r="AK28" s="118"/>
+      <c r="AL28" s="118"/>
+      <c r="AM28" s="118"/>
+      <c r="AN28" s="118"/>
+      <c r="AO28" s="118"/>
+      <c r="AP28" s="118"/>
+      <c r="AQ28" s="118"/>
+      <c r="AR28" s="118"/>
+      <c r="AS28" s="118"/>
+      <c r="AT28" s="118"/>
+      <c r="AU28" s="118"/>
+      <c r="AV28" s="118"/>
+      <c r="AW28" s="118"/>
+      <c r="AX28" s="118"/>
+      <c r="AY28" s="118"/>
+      <c r="AZ28" s="118"/>
+      <c r="BA28" s="118"/>
+      <c r="BB28" s="118"/>
+      <c r="BC28" s="118"/>
+      <c r="BD28" s="118"/>
+      <c r="BE28" s="118"/>
+      <c r="BF28" s="118"/>
+      <c r="BG28" s="118"/>
+      <c r="BH28" s="118"/>
+      <c r="BI28" s="118"/>
+      <c r="BJ28" s="118"/>
+      <c r="BK28" s="118"/>
+      <c r="BL28" s="118"/>
+      <c r="BM28" s="118"/>
+      <c r="BN28" s="118"/>
+      <c r="BO28" s="118"/>
+      <c r="BP28" s="118"/>
+      <c r="BQ28" s="118"/>
+      <c r="BR28" s="118"/>
+      <c r="BS28" s="118"/>
+      <c r="BT28" s="118"/>
+      <c r="BU28" s="118"/>
+      <c r="BV28" s="118"/>
+      <c r="BW28" s="118"/>
+      <c r="BX28" s="118"/>
+      <c r="BY28" s="118"/>
+      <c r="BZ28" s="118"/>
+      <c r="CA28" s="118"/>
+      <c r="CB28" s="118"/>
+      <c r="CC28" s="118"/>
+      <c r="CD28" s="118"/>
+      <c r="CE28" s="118"/>
+      <c r="CF28" s="118"/>
+      <c r="CG28" s="118"/>
+      <c r="CH28" s="118"/>
+      <c r="CI28" s="118"/>
+      <c r="CJ28" s="118"/>
+      <c r="CK28" s="118"/>
+      <c r="CL28" s="118"/>
+      <c r="CM28" s="118"/>
+      <c r="CN28" s="118"/>
+      <c r="CO28" s="118"/>
+      <c r="CP28" s="118"/>
+      <c r="CQ28" s="118"/>
+      <c r="CR28" s="118"/>
+      <c r="CS28" s="118"/>
+      <c r="CT28" s="118"/>
+      <c r="CU28" s="118"/>
+      <c r="CV28" s="118"/>
+      <c r="CW28" s="118"/>
+      <c r="CX28" s="118"/>
+      <c r="CY28" s="118"/>
+      <c r="CZ28" s="118"/>
+      <c r="DA28" s="118"/>
+      <c r="DB28" s="118"/>
+      <c r="DC28" s="118"/>
+      <c r="DD28" s="118"/>
+      <c r="DE28" s="118"/>
+      <c r="DF28" s="118"/>
+      <c r="DG28" s="118"/>
+      <c r="DH28" s="118"/>
+      <c r="DI28" s="118"/>
+      <c r="DJ28" s="118"/>
+      <c r="DK28" s="118"/>
+      <c r="DL28" s="118"/>
+      <c r="DM28" s="118"/>
+      <c r="DN28" s="118"/>
+      <c r="DO28" s="118"/>
+      <c r="DP28" s="118"/>
+      <c r="DQ28" s="118"/>
+      <c r="DR28" s="118"/>
+      <c r="DS28" s="118"/>
+      <c r="DT28" s="118"/>
+      <c r="DU28" s="118"/>
+      <c r="DV28" s="118"/>
+      <c r="DW28" s="118"/>
+      <c r="DX28" s="118"/>
+      <c r="DY28" s="118"/>
+      <c r="DZ28" s="118"/>
+      <c r="EA28" s="118"/>
+      <c r="EB28" s="118"/>
+      <c r="EC28" s="118"/>
+      <c r="ED28" s="118"/>
+      <c r="EE28" s="118"/>
+      <c r="EF28" s="118"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:136">
       <c r="A29" s="102" t="s">
@@ -8546,7 +7892,7 @@
       <c r="C29" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="120" t="s">
+      <c r="D29" s="119" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="104">
@@ -8568,8 +7914,8 @@
       <c r="K29" s="104"/>
       <c r="L29" s="104"/>
       <c r="M29" s="104"/>
-      <c r="N29" s="120"/>
-      <c r="O29" s="120"/>
+      <c r="N29" s="119"/>
+      <c r="O29" s="119"/>
       <c r="P29" s="104"/>
       <c r="Q29" s="128"/>
       <c r="R29" s="15"/>
@@ -8642,7 +7988,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="127"/>
       <c r="C30" s="127"/>
-      <c r="D30" s="120"/>
+      <c r="D30" s="119"/>
       <c r="E30" s="104"/>
       <c r="F30" s="104"/>
       <c r="G30" s="105"/>
@@ -8652,9 +7998,9 @@
       <c r="K30" s="104"/>
       <c r="L30" s="104"/>
       <c r="M30" s="104"/>
-      <c r="N30" s="120"/>
-      <c r="O30" s="120"/>
-      <c r="P30" s="120"/>
+      <c r="N30" s="119"/>
+      <c r="O30" s="119"/>
+      <c r="P30" s="119"/>
       <c r="Q30" s="15"/>
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
@@ -8726,7 +8072,7 @@
       <c r="A31" s="19"/>
       <c r="B31" s="127"/>
       <c r="C31" s="127"/>
-      <c r="D31" s="120"/>
+      <c r="D31" s="119"/>
       <c r="E31" s="104"/>
       <c r="F31" s="104"/>
       <c r="G31" s="105"/>
@@ -8736,9 +8082,9 @@
       <c r="K31" s="104"/>
       <c r="L31" s="104"/>
       <c r="M31" s="104"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="120"/>
-      <c r="P31" s="120"/>
+      <c r="N31" s="119"/>
+      <c r="O31" s="119"/>
+      <c r="P31" s="119"/>
       <c r="Q31" s="15"/>
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
@@ -8810,7 +8156,7 @@
       <c r="A32" s="19"/>
       <c r="B32" s="127"/>
       <c r="C32" s="127"/>
-      <c r="D32" s="120"/>
+      <c r="D32" s="119"/>
       <c r="E32" s="104"/>
       <c r="F32" s="104"/>
       <c r="G32" s="105"/>
@@ -8820,9 +8166,9 @@
       <c r="K32" s="104"/>
       <c r="L32" s="104"/>
       <c r="M32" s="104"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="120"/>
-      <c r="P32" s="120"/>
+      <c r="N32" s="119"/>
+      <c r="O32" s="119"/>
+      <c r="P32" s="119"/>
       <c r="Q32" s="15"/>
       <c r="R32" s="15"/>
       <c r="S32" s="15"/>
@@ -8894,7 +8240,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="127"/>
       <c r="C33" s="127"/>
-      <c r="D33" s="120"/>
+      <c r="D33" s="119"/>
       <c r="E33" s="104"/>
       <c r="F33" s="104"/>
       <c r="G33" s="105"/>
@@ -8904,9 +8250,9 @@
       <c r="K33" s="104"/>
       <c r="L33" s="104"/>
       <c r="M33" s="104"/>
-      <c r="N33" s="120"/>
-      <c r="O33" s="120"/>
-      <c r="P33" s="120"/>
+      <c r="N33" s="119"/>
+      <c r="O33" s="119"/>
+      <c r="P33" s="119"/>
       <c r="Q33" s="15"/>
       <c r="R33" s="15"/>
       <c r="S33" s="15"/>
@@ -8978,7 +8324,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="127"/>
       <c r="C34" s="127"/>
-      <c r="D34" s="120"/>
+      <c r="D34" s="119"/>
       <c r="E34" s="104"/>
       <c r="F34" s="104"/>
       <c r="G34" s="105"/>
@@ -8988,9 +8334,9 @@
       <c r="K34" s="104"/>
       <c r="L34" s="104"/>
       <c r="M34" s="104"/>
-      <c r="N34" s="120"/>
-      <c r="O34" s="120"/>
-      <c r="P34" s="120"/>
+      <c r="N34" s="119"/>
+      <c r="O34" s="119"/>
+      <c r="P34" s="119"/>
       <c r="Q34" s="15"/>
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
@@ -9062,7 +8408,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="127"/>
       <c r="C35" s="127"/>
-      <c r="D35" s="120"/>
+      <c r="D35" s="119"/>
       <c r="E35" s="104"/>
       <c r="F35" s="104" t="s">
         <v>78</v>
@@ -9078,9 +8424,9 @@
       <c r="K35" s="104"/>
       <c r="L35" s="104"/>
       <c r="M35" s="104"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="120"/>
-      <c r="P35" s="120"/>
+      <c r="N35" s="119"/>
+      <c r="O35" s="119"/>
+      <c r="P35" s="119"/>
       <c r="Q35" s="15"/>
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
@@ -9152,7 +8498,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="127"/>
       <c r="C36" s="127"/>
-      <c r="D36" s="120"/>
+      <c r="D36" s="119"/>
       <c r="E36" s="104"/>
       <c r="F36" s="104" t="s">
         <v>79</v>
@@ -9168,9 +8514,9 @@
       <c r="K36" s="104"/>
       <c r="L36" s="104"/>
       <c r="M36" s="104"/>
-      <c r="N36" s="120"/>
-      <c r="O36" s="120"/>
-      <c r="P36" s="120"/>
+      <c r="N36" s="119"/>
+      <c r="O36" s="119"/>
+      <c r="P36" s="119"/>
       <c r="Q36" s="15"/>
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
@@ -9242,7 +8588,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="127"/>
       <c r="C37" s="127"/>
-      <c r="D37" s="120"/>
+      <c r="D37" s="119"/>
       <c r="E37" s="104"/>
       <c r="F37" s="104" t="s">
         <v>80</v>
@@ -9261,9 +8607,9 @@
       <c r="K37" s="104"/>
       <c r="L37" s="104"/>
       <c r="M37" s="104"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="120"/>
-      <c r="P37" s="120"/>
+      <c r="N37" s="119"/>
+      <c r="O37" s="119"/>
+      <c r="P37" s="119"/>
       <c r="Q37" s="15"/>
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
@@ -9335,7 +8681,7 @@
       <c r="A38" s="19"/>
       <c r="B38" s="127"/>
       <c r="C38" s="127"/>
-      <c r="D38" s="120"/>
+      <c r="D38" s="119"/>
       <c r="E38" s="104"/>
       <c r="F38" s="104" t="s">
         <v>81</v>
@@ -9356,9 +8702,9 @@
       <c r="K38" s="104"/>
       <c r="L38" s="104"/>
       <c r="M38" s="104"/>
-      <c r="N38" s="120"/>
-      <c r="O38" s="120"/>
-      <c r="P38" s="120"/>
+      <c r="N38" s="119"/>
+      <c r="O38" s="119"/>
+      <c r="P38" s="119"/>
       <c r="Q38" s="15"/>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
@@ -9430,7 +8776,7 @@
       <c r="A39" s="19"/>
       <c r="B39" s="127"/>
       <c r="C39" s="127"/>
-      <c r="D39" s="120"/>
+      <c r="D39" s="119"/>
       <c r="E39" s="104"/>
       <c r="F39" s="104"/>
       <c r="G39" s="105"/>
@@ -9440,9 +8786,9 @@
       <c r="K39" s="104"/>
       <c r="L39" s="104"/>
       <c r="M39" s="104"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
-      <c r="P39" s="120"/>
+      <c r="N39" s="119"/>
+      <c r="O39" s="119"/>
+      <c r="P39" s="119"/>
       <c r="Q39" s="15"/>
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
@@ -9514,7 +8860,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="127"/>
       <c r="C40" s="127"/>
-      <c r="D40" s="120"/>
+      <c r="D40" s="119"/>
       <c r="E40" s="104"/>
       <c r="F40" s="104"/>
       <c r="G40" s="105"/>
@@ -9524,9 +8870,9 @@
       <c r="K40" s="104"/>
       <c r="L40" s="104"/>
       <c r="M40" s="104"/>
-      <c r="N40" s="120"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="120"/>
+      <c r="N40" s="119"/>
+      <c r="O40" s="119"/>
+      <c r="P40" s="119"/>
       <c r="Q40" s="15"/>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
@@ -9598,7 +8944,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="127"/>
       <c r="C41" s="127"/>
-      <c r="D41" s="120"/>
+      <c r="D41" s="119"/>
       <c r="E41" s="104"/>
       <c r="F41" s="104"/>
       <c r="G41" s="105"/>
@@ -9608,9 +8954,9 @@
       <c r="K41" s="104"/>
       <c r="L41" s="104"/>
       <c r="M41" s="104"/>
-      <c r="N41" s="120"/>
-      <c r="O41" s="120"/>
-      <c r="P41" s="120"/>
+      <c r="N41" s="119"/>
+      <c r="O41" s="119"/>
+      <c r="P41" s="119"/>
       <c r="Q41" s="15"/>
       <c r="R41" s="15"/>
       <c r="S41" s="15"/>
@@ -9682,7 +9028,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="127"/>
       <c r="C42" s="127"/>
-      <c r="D42" s="120"/>
+      <c r="D42" s="119"/>
       <c r="E42" s="104"/>
       <c r="F42" s="104"/>
       <c r="G42" s="105"/>
@@ -9692,9 +9038,9 @@
       <c r="K42" s="104"/>
       <c r="L42" s="104"/>
       <c r="M42" s="104"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120"/>
+      <c r="N42" s="119"/>
+      <c r="O42" s="119"/>
+      <c r="P42" s="119"/>
       <c r="Q42" s="15"/>
       <c r="R42" s="15"/>
       <c r="S42" s="15"/>
@@ -9766,7 +9112,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="127"/>
       <c r="C43" s="127"/>
-      <c r="D43" s="120"/>
+      <c r="D43" s="119"/>
       <c r="E43" s="104"/>
       <c r="F43" s="104"/>
       <c r="G43" s="105"/>
@@ -9776,9 +9122,9 @@
       <c r="K43" s="104"/>
       <c r="L43" s="104"/>
       <c r="M43" s="104"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="120"/>
-      <c r="P43" s="120"/>
+      <c r="N43" s="119"/>
+      <c r="O43" s="119"/>
+      <c r="P43" s="119"/>
       <c r="Q43" s="15"/>
       <c r="R43" s="15"/>
       <c r="S43" s="15"/>
@@ -9850,7 +9196,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="127"/>
       <c r="C44" s="127"/>
-      <c r="D44" s="120"/>
+      <c r="D44" s="119"/>
       <c r="E44" s="104"/>
       <c r="F44" s="104"/>
       <c r="G44" s="105"/>
@@ -9860,9 +9206,9 @@
       <c r="K44" s="104"/>
       <c r="L44" s="104"/>
       <c r="M44" s="104"/>
-      <c r="N44" s="120"/>
-      <c r="O44" s="120"/>
-      <c r="P44" s="120"/>
+      <c r="N44" s="119"/>
+      <c r="O44" s="119"/>
+      <c r="P44" s="119"/>
       <c r="Q44" s="15"/>
       <c r="R44" s="15"/>
       <c r="S44" s="15"/>
@@ -9934,7 +9280,7 @@
       <c r="A45" s="19"/>
       <c r="B45" s="127"/>
       <c r="C45" s="127"/>
-      <c r="D45" s="120"/>
+      <c r="D45" s="119"/>
       <c r="E45" s="104"/>
       <c r="F45" s="104"/>
       <c r="G45" s="105"/>
@@ -9944,9 +9290,9 @@
       <c r="K45" s="104"/>
       <c r="L45" s="104"/>
       <c r="M45" s="104"/>
-      <c r="N45" s="120"/>
-      <c r="O45" s="120"/>
-      <c r="P45" s="120"/>
+      <c r="N45" s="119"/>
+      <c r="O45" s="119"/>
+      <c r="P45" s="119"/>
       <c r="Q45" s="15"/>
       <c r="R45" s="15"/>
       <c r="S45" s="15"/>
@@ -10018,7 +9364,7 @@
       <c r="A46" s="19"/>
       <c r="B46" s="127"/>
       <c r="C46" s="127"/>
-      <c r="D46" s="120"/>
+      <c r="D46" s="119"/>
       <c r="E46" s="104"/>
       <c r="F46" s="104"/>
       <c r="G46" s="105"/>
@@ -10028,9 +9374,9 @@
       <c r="K46" s="104"/>
       <c r="L46" s="104"/>
       <c r="M46" s="104"/>
-      <c r="N46" s="120"/>
-      <c r="O46" s="120"/>
-      <c r="P46" s="120"/>
+      <c r="N46" s="119"/>
+      <c r="O46" s="119"/>
+      <c r="P46" s="119"/>
       <c r="Q46" s="15"/>
       <c r="R46" s="15"/>
       <c r="S46" s="15"/>
@@ -10102,7 +9448,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="127"/>
       <c r="C47" s="127"/>
-      <c r="D47" s="120"/>
+      <c r="D47" s="119"/>
       <c r="E47" s="104"/>
       <c r="F47" s="104"/>
       <c r="G47" s="105"/>
@@ -10112,9 +9458,9 @@
       <c r="K47" s="104"/>
       <c r="L47" s="104"/>
       <c r="M47" s="104"/>
-      <c r="N47" s="120"/>
-      <c r="O47" s="120"/>
-      <c r="P47" s="120"/>
+      <c r="N47" s="119"/>
+      <c r="O47" s="119"/>
+      <c r="P47" s="119"/>
       <c r="Q47" s="15"/>
       <c r="R47" s="15"/>
       <c r="S47" s="15"/>
@@ -10186,7 +9532,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="127"/>
       <c r="C48" s="127"/>
-      <c r="D48" s="120"/>
+      <c r="D48" s="119"/>
       <c r="E48" s="104"/>
       <c r="F48" s="104"/>
       <c r="G48" s="105"/>
@@ -10196,9 +9542,9 @@
       <c r="K48" s="104"/>
       <c r="L48" s="104"/>
       <c r="M48" s="104"/>
-      <c r="N48" s="120"/>
-      <c r="O48" s="120"/>
-      <c r="P48" s="120"/>
+      <c r="N48" s="119"/>
+      <c r="O48" s="119"/>
+      <c r="P48" s="119"/>
       <c r="Q48" s="15"/>
       <c r="R48" s="15"/>
       <c r="S48" s="15"/>
@@ -10270,7 +9616,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="127"/>
       <c r="C49" s="127"/>
-      <c r="D49" s="120"/>
+      <c r="D49" s="119"/>
       <c r="E49" s="104"/>
       <c r="F49" s="104"/>
       <c r="G49" s="105"/>
@@ -10280,9 +9626,9 @@
       <c r="K49" s="104"/>
       <c r="L49" s="104"/>
       <c r="M49" s="104"/>
-      <c r="N49" s="120"/>
-      <c r="O49" s="120"/>
-      <c r="P49" s="120"/>
+      <c r="N49" s="119"/>
+      <c r="O49" s="119"/>
+      <c r="P49" s="119"/>
       <c r="Q49" s="15"/>
       <c r="R49" s="15"/>
       <c r="S49" s="15"/>
@@ -10354,7 +9700,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="127"/>
       <c r="C50" s="127"/>
-      <c r="D50" s="120"/>
+      <c r="D50" s="119"/>
       <c r="E50" s="104"/>
       <c r="F50" s="104"/>
       <c r="G50" s="105"/>
@@ -10364,9 +9710,9 @@
       <c r="K50" s="104"/>
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
-      <c r="N50" s="120"/>
-      <c r="O50" s="120"/>
-      <c r="P50" s="120"/>
+      <c r="N50" s="119"/>
+      <c r="O50" s="119"/>
+      <c r="P50" s="119"/>
       <c r="Q50" s="15"/>
       <c r="R50" s="15"/>
       <c r="S50" s="15"/>
@@ -10438,7 +9784,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="127"/>
       <c r="C51" s="127"/>
-      <c r="D51" s="120"/>
+      <c r="D51" s="119"/>
       <c r="E51" s="104"/>
       <c r="F51" s="104"/>
       <c r="G51" s="105"/>
@@ -10448,9 +9794,9 @@
       <c r="K51" s="104"/>
       <c r="L51" s="104"/>
       <c r="M51" s="104"/>
-      <c r="N51" s="120"/>
-      <c r="O51" s="120"/>
-      <c r="P51" s="120"/>
+      <c r="N51" s="119"/>
+      <c r="O51" s="119"/>
+      <c r="P51" s="119"/>
       <c r="Q51" s="15"/>
       <c r="R51" s="15"/>
       <c r="S51" s="15"/>
@@ -10522,7 +9868,7 @@
       <c r="A52" s="19"/>
       <c r="B52" s="127"/>
       <c r="C52" s="127"/>
-      <c r="D52" s="120"/>
+      <c r="D52" s="119"/>
       <c r="E52" s="104"/>
       <c r="F52" s="104"/>
       <c r="G52" s="105"/>
@@ -10532,9 +9878,9 @@
       <c r="K52" s="104"/>
       <c r="L52" s="104"/>
       <c r="M52" s="104"/>
-      <c r="N52" s="120"/>
-      <c r="O52" s="120"/>
-      <c r="P52" s="120"/>
+      <c r="N52" s="119"/>
+      <c r="O52" s="119"/>
+      <c r="P52" s="119"/>
       <c r="Q52" s="15"/>
       <c r="R52" s="15"/>
       <c r="S52" s="15"/>
@@ -10606,7 +9952,7 @@
       <c r="A53" s="19"/>
       <c r="B53" s="127"/>
       <c r="C53" s="127"/>
-      <c r="D53" s="120"/>
+      <c r="D53" s="119"/>
       <c r="E53" s="104"/>
       <c r="F53" s="104"/>
       <c r="G53" s="105"/>
@@ -10616,9 +9962,9 @@
       <c r="K53" s="104"/>
       <c r="L53" s="104"/>
       <c r="M53" s="104"/>
-      <c r="N53" s="120"/>
-      <c r="O53" s="120"/>
-      <c r="P53" s="120"/>
+      <c r="N53" s="119"/>
+      <c r="O53" s="119"/>
+      <c r="P53" s="119"/>
       <c r="Q53" s="15"/>
       <c r="R53" s="15"/>
       <c r="S53" s="15"/>
@@ -10690,7 +10036,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="127"/>
       <c r="C54" s="127"/>
-      <c r="D54" s="120"/>
+      <c r="D54" s="119"/>
       <c r="E54" s="104"/>
       <c r="F54" s="104"/>
       <c r="G54" s="105"/>
@@ -10700,9 +10046,9 @@
       <c r="K54" s="104"/>
       <c r="L54" s="104"/>
       <c r="M54" s="104"/>
-      <c r="N54" s="120"/>
-      <c r="O54" s="120"/>
-      <c r="P54" s="120"/>
+      <c r="N54" s="119"/>
+      <c r="O54" s="119"/>
+      <c r="P54" s="119"/>
       <c r="Q54" s="15"/>
       <c r="R54" s="15"/>
       <c r="S54" s="15"/>
@@ -10774,7 +10120,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="127"/>
       <c r="C55" s="127"/>
-      <c r="D55" s="120"/>
+      <c r="D55" s="119"/>
       <c r="E55" s="104"/>
       <c r="F55" s="104"/>
       <c r="G55" s="105"/>
@@ -10784,9 +10130,9 @@
       <c r="K55" s="104"/>
       <c r="L55" s="104"/>
       <c r="M55" s="104"/>
-      <c r="N55" s="120"/>
-      <c r="O55" s="120"/>
-      <c r="P55" s="120"/>
+      <c r="N55" s="119"/>
+      <c r="O55" s="119"/>
+      <c r="P55" s="119"/>
       <c r="Q55" s="15"/>
       <c r="R55" s="15"/>
       <c r="S55" s="15"/>
@@ -10858,7 +10204,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="127"/>
       <c r="C56" s="127"/>
-      <c r="D56" s="120"/>
+      <c r="D56" s="119"/>
       <c r="E56" s="104"/>
       <c r="F56" s="104"/>
       <c r="G56" s="105"/>
@@ -10868,9 +10214,9 @@
       <c r="K56" s="104"/>
       <c r="L56" s="104"/>
       <c r="M56" s="104"/>
-      <c r="N56" s="120"/>
-      <c r="O56" s="120"/>
-      <c r="P56" s="120"/>
+      <c r="N56" s="119"/>
+      <c r="O56" s="119"/>
+      <c r="P56" s="119"/>
       <c r="Q56" s="15"/>
       <c r="R56" s="15"/>
       <c r="S56" s="15"/>
@@ -10942,7 +10288,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="127"/>
       <c r="C57" s="127"/>
-      <c r="D57" s="120"/>
+      <c r="D57" s="119"/>
       <c r="E57" s="104"/>
       <c r="F57" s="104"/>
       <c r="G57" s="105"/>
@@ -10952,9 +10298,9 @@
       <c r="K57" s="104"/>
       <c r="L57" s="104"/>
       <c r="M57" s="104"/>
-      <c r="N57" s="120"/>
-      <c r="O57" s="120"/>
-      <c r="P57" s="120"/>
+      <c r="N57" s="119"/>
+      <c r="O57" s="119"/>
+      <c r="P57" s="119"/>
       <c r="Q57" s="15"/>
       <c r="R57" s="15"/>
       <c r="S57" s="15"/>
@@ -11026,7 +10372,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="127"/>
       <c r="C58" s="127"/>
-      <c r="D58" s="120"/>
+      <c r="D58" s="119"/>
       <c r="E58" s="104"/>
       <c r="F58" s="104"/>
       <c r="G58" s="105"/>
@@ -11036,9 +10382,9 @@
       <c r="K58" s="104"/>
       <c r="L58" s="104"/>
       <c r="M58" s="104"/>
-      <c r="N58" s="120"/>
-      <c r="O58" s="120"/>
-      <c r="P58" s="120"/>
+      <c r="N58" s="119"/>
+      <c r="O58" s="119"/>
+      <c r="P58" s="119"/>
       <c r="Q58" s="15"/>
       <c r="R58" s="15"/>
       <c r="S58" s="15"/>
@@ -11110,7 +10456,7 @@
       <c r="A59" s="19"/>
       <c r="B59" s="127"/>
       <c r="C59" s="127"/>
-      <c r="D59" s="120"/>
+      <c r="D59" s="119"/>
       <c r="E59" s="104"/>
       <c r="F59" s="104"/>
       <c r="G59" s="105"/>
@@ -11120,9 +10466,9 @@
       <c r="K59" s="104"/>
       <c r="L59" s="104"/>
       <c r="M59" s="104"/>
-      <c r="N59" s="120"/>
-      <c r="O59" s="120"/>
-      <c r="P59" s="120"/>
+      <c r="N59" s="119"/>
+      <c r="O59" s="119"/>
+      <c r="P59" s="119"/>
       <c r="Q59" s="15"/>
       <c r="R59" s="15"/>
       <c r="S59" s="15"/>
@@ -11194,7 +10540,7 @@
       <c r="A60" s="19"/>
       <c r="B60" s="127"/>
       <c r="C60" s="127"/>
-      <c r="D60" s="120"/>
+      <c r="D60" s="119"/>
       <c r="E60" s="104"/>
       <c r="F60" s="104"/>
       <c r="G60" s="105"/>
@@ -11204,9 +10550,9 @@
       <c r="K60" s="104"/>
       <c r="L60" s="104"/>
       <c r="M60" s="104"/>
-      <c r="N60" s="120"/>
-      <c r="O60" s="120"/>
-      <c r="P60" s="120"/>
+      <c r="N60" s="119"/>
+      <c r="O60" s="119"/>
+      <c r="P60" s="119"/>
       <c r="Q60" s="15"/>
       <c r="R60" s="15"/>
       <c r="S60" s="15"/>
@@ -11278,7 +10624,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="127"/>
       <c r="C61" s="127"/>
-      <c r="D61" s="120"/>
+      <c r="D61" s="119"/>
       <c r="E61" s="104"/>
       <c r="F61" s="104"/>
       <c r="G61" s="105"/>
@@ -11288,9 +10634,9 @@
       <c r="K61" s="104"/>
       <c r="L61" s="104"/>
       <c r="M61" s="104"/>
-      <c r="N61" s="120"/>
-      <c r="O61" s="120"/>
-      <c r="P61" s="120"/>
+      <c r="N61" s="119"/>
+      <c r="O61" s="119"/>
+      <c r="P61" s="119"/>
       <c r="Q61" s="15"/>
       <c r="R61" s="15"/>
       <c r="S61" s="15"/>
@@ -11362,7 +10708,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="127"/>
       <c r="C62" s="127"/>
-      <c r="D62" s="120"/>
+      <c r="D62" s="119"/>
       <c r="E62" s="104"/>
       <c r="F62" s="104"/>
       <c r="G62" s="105"/>
@@ -11372,9 +10718,9 @@
       <c r="K62" s="104"/>
       <c r="L62" s="104"/>
       <c r="M62" s="104"/>
-      <c r="N62" s="120"/>
-      <c r="O62" s="120"/>
-      <c r="P62" s="120"/>
+      <c r="N62" s="119"/>
+      <c r="O62" s="119"/>
+      <c r="P62" s="119"/>
       <c r="Q62" s="15"/>
       <c r="R62" s="15"/>
       <c r="S62" s="15"/>
@@ -11446,7 +10792,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="127"/>
       <c r="C63" s="127"/>
-      <c r="D63" s="120"/>
+      <c r="D63" s="119"/>
       <c r="E63" s="104"/>
       <c r="F63" s="104"/>
       <c r="G63" s="105"/>
@@ -11456,9 +10802,9 @@
       <c r="K63" s="104"/>
       <c r="L63" s="104"/>
       <c r="M63" s="104"/>
-      <c r="N63" s="120"/>
-      <c r="O63" s="120"/>
-      <c r="P63" s="120"/>
+      <c r="N63" s="119"/>
+      <c r="O63" s="119"/>
+      <c r="P63" s="119"/>
       <c r="Q63" s="15"/>
       <c r="R63" s="15"/>
       <c r="S63" s="15"/>
@@ -11530,7 +10876,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="127"/>
       <c r="C64" s="127"/>
-      <c r="D64" s="120"/>
+      <c r="D64" s="119"/>
       <c r="E64" s="104"/>
       <c r="F64" s="104"/>
       <c r="G64" s="105"/>
@@ -11540,9 +10886,9 @@
       <c r="K64" s="104"/>
       <c r="L64" s="104"/>
       <c r="M64" s="104"/>
-      <c r="N64" s="120"/>
-      <c r="O64" s="120"/>
-      <c r="P64" s="120"/>
+      <c r="N64" s="119"/>
+      <c r="O64" s="119"/>
+      <c r="P64" s="119"/>
       <c r="Q64" s="15"/>
       <c r="R64" s="15"/>
       <c r="S64" s="15"/>
@@ -11614,7 +10960,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="127"/>
       <c r="C65" s="127"/>
-      <c r="D65" s="120"/>
+      <c r="D65" s="119"/>
       <c r="E65" s="104"/>
       <c r="F65" s="104"/>
       <c r="G65" s="105"/>
@@ -11624,9 +10970,9 @@
       <c r="K65" s="104"/>
       <c r="L65" s="104"/>
       <c r="M65" s="104"/>
-      <c r="N65" s="120"/>
-      <c r="O65" s="120"/>
-      <c r="P65" s="120"/>
+      <c r="N65" s="119"/>
+      <c r="O65" s="119"/>
+      <c r="P65" s="119"/>
       <c r="Q65" s="15"/>
       <c r="R65" s="15"/>
       <c r="S65" s="15"/>
@@ -11698,7 +11044,7 @@
       <c r="A66" s="19"/>
       <c r="B66" s="127"/>
       <c r="C66" s="127"/>
-      <c r="D66" s="120"/>
+      <c r="D66" s="119"/>
       <c r="E66" s="104"/>
       <c r="F66" s="104"/>
       <c r="G66" s="105"/>
@@ -11708,9 +11054,9 @@
       <c r="K66" s="104"/>
       <c r="L66" s="104"/>
       <c r="M66" s="104"/>
-      <c r="N66" s="120"/>
-      <c r="O66" s="120"/>
-      <c r="P66" s="120"/>
+      <c r="N66" s="119"/>
+      <c r="O66" s="119"/>
+      <c r="P66" s="119"/>
       <c r="Q66" s="15"/>
       <c r="R66" s="15"/>
       <c r="S66" s="15"/>
@@ -11782,7 +11128,7 @@
       <c r="A67" s="19"/>
       <c r="B67" s="127"/>
       <c r="C67" s="127"/>
-      <c r="D67" s="120"/>
+      <c r="D67" s="119"/>
       <c r="E67" s="104"/>
       <c r="F67" s="104"/>
       <c r="G67" s="105"/>
@@ -11792,9 +11138,9 @@
       <c r="K67" s="104"/>
       <c r="L67" s="104"/>
       <c r="M67" s="104"/>
-      <c r="N67" s="120"/>
-      <c r="O67" s="120"/>
-      <c r="P67" s="120"/>
+      <c r="N67" s="119"/>
+      <c r="O67" s="119"/>
+      <c r="P67" s="119"/>
       <c r="Q67" s="15"/>
       <c r="R67" s="15"/>
       <c r="S67" s="15"/>
@@ -11866,7 +11212,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="127"/>
       <c r="C68" s="127"/>
-      <c r="D68" s="120"/>
+      <c r="D68" s="119"/>
       <c r="E68" s="104"/>
       <c r="F68" s="104"/>
       <c r="G68" s="105"/>
@@ -11876,9 +11222,9 @@
       <c r="K68" s="104"/>
       <c r="L68" s="104"/>
       <c r="M68" s="104"/>
-      <c r="N68" s="120"/>
-      <c r="O68" s="120"/>
-      <c r="P68" s="120"/>
+      <c r="N68" s="119"/>
+      <c r="O68" s="119"/>
+      <c r="P68" s="119"/>
       <c r="Q68" s="15"/>
       <c r="R68" s="15"/>
       <c r="S68" s="15"/>
@@ -11950,7 +11296,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="127"/>
       <c r="C69" s="127"/>
-      <c r="D69" s="120"/>
+      <c r="D69" s="119"/>
       <c r="E69" s="104"/>
       <c r="F69" s="104"/>
       <c r="G69" s="105"/>
@@ -11960,9 +11306,9 @@
       <c r="K69" s="104"/>
       <c r="L69" s="104"/>
       <c r="M69" s="104"/>
-      <c r="N69" s="120"/>
-      <c r="O69" s="120"/>
-      <c r="P69" s="120"/>
+      <c r="N69" s="119"/>
+      <c r="O69" s="119"/>
+      <c r="P69" s="119"/>
       <c r="Q69" s="15"/>
       <c r="R69" s="15"/>
       <c r="S69" s="15"/>
@@ -12034,7 +11380,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="127"/>
       <c r="C70" s="127"/>
-      <c r="D70" s="120"/>
+      <c r="D70" s="119"/>
       <c r="E70" s="104"/>
       <c r="F70" s="104"/>
       <c r="G70" s="105"/>
@@ -12044,9 +11390,9 @@
       <c r="K70" s="104"/>
       <c r="L70" s="104"/>
       <c r="M70" s="104"/>
-      <c r="N70" s="120"/>
-      <c r="O70" s="120"/>
-      <c r="P70" s="120"/>
+      <c r="N70" s="119"/>
+      <c r="O70" s="119"/>
+      <c r="P70" s="119"/>
       <c r="Q70" s="15"/>
       <c r="R70" s="15"/>
       <c r="S70" s="15"/>
@@ -12118,7 +11464,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="127"/>
       <c r="C71" s="127"/>
-      <c r="D71" s="120"/>
+      <c r="D71" s="119"/>
       <c r="E71" s="104"/>
       <c r="F71" s="104"/>
       <c r="G71" s="105"/>
@@ -12128,9 +11474,9 @@
       <c r="K71" s="104"/>
       <c r="L71" s="104"/>
       <c r="M71" s="104"/>
-      <c r="N71" s="120"/>
-      <c r="O71" s="120"/>
-      <c r="P71" s="120"/>
+      <c r="N71" s="119"/>
+      <c r="O71" s="119"/>
+      <c r="P71" s="119"/>
       <c r="Q71" s="15"/>
       <c r="R71" s="15"/>
       <c r="S71" s="15"/>
@@ -12202,7 +11548,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="127"/>
       <c r="C72" s="127"/>
-      <c r="D72" s="120"/>
+      <c r="D72" s="119"/>
       <c r="E72" s="104"/>
       <c r="F72" s="104"/>
       <c r="G72" s="105"/>
@@ -12212,9 +11558,9 @@
       <c r="K72" s="104"/>
       <c r="L72" s="104"/>
       <c r="M72" s="104"/>
-      <c r="N72" s="120"/>
-      <c r="O72" s="120"/>
-      <c r="P72" s="120"/>
+      <c r="N72" s="119"/>
+      <c r="O72" s="119"/>
+      <c r="P72" s="119"/>
       <c r="Q72" s="15"/>
       <c r="R72" s="15"/>
       <c r="S72" s="15"/>
@@ -12286,7 +11632,7 @@
       <c r="A73" s="19"/>
       <c r="B73" s="127"/>
       <c r="C73" s="127"/>
-      <c r="D73" s="120"/>
+      <c r="D73" s="119"/>
       <c r="E73" s="104"/>
       <c r="F73" s="104"/>
       <c r="G73" s="105"/>
@@ -12296,9 +11642,9 @@
       <c r="K73" s="104"/>
       <c r="L73" s="104"/>
       <c r="M73" s="104"/>
-      <c r="N73" s="120"/>
-      <c r="O73" s="120"/>
-      <c r="P73" s="120"/>
+      <c r="N73" s="119"/>
+      <c r="O73" s="119"/>
+      <c r="P73" s="119"/>
       <c r="Q73" s="15"/>
       <c r="R73" s="15"/>
       <c r="S73" s="15"/>
@@ -12370,7 +11716,7 @@
       <c r="A74" s="19"/>
       <c r="B74" s="127"/>
       <c r="C74" s="127"/>
-      <c r="D74" s="120"/>
+      <c r="D74" s="119"/>
       <c r="E74" s="104"/>
       <c r="F74" s="104"/>
       <c r="G74" s="105"/>
@@ -12380,9 +11726,9 @@
       <c r="K74" s="104"/>
       <c r="L74" s="104"/>
       <c r="M74" s="104"/>
-      <c r="N74" s="120"/>
-      <c r="O74" s="120"/>
-      <c r="P74" s="120"/>
+      <c r="N74" s="119"/>
+      <c r="O74" s="119"/>
+      <c r="P74" s="119"/>
       <c r="Q74" s="15"/>
       <c r="R74" s="15"/>
       <c r="S74" s="15"/>
@@ -12454,7 +11800,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="127"/>
       <c r="C75" s="127"/>
-      <c r="D75" s="120"/>
+      <c r="D75" s="119"/>
       <c r="E75" s="104"/>
       <c r="F75" s="104"/>
       <c r="G75" s="105"/>
@@ -12464,9 +11810,9 @@
       <c r="K75" s="104"/>
       <c r="L75" s="104"/>
       <c r="M75" s="104"/>
-      <c r="N75" s="120"/>
-      <c r="O75" s="120"/>
-      <c r="P75" s="120"/>
+      <c r="N75" s="119"/>
+      <c r="O75" s="119"/>
+      <c r="P75" s="119"/>
       <c r="Q75" s="15"/>
       <c r="R75" s="15"/>
       <c r="S75" s="15"/>
@@ -12538,7 +11884,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="127"/>
       <c r="C76" s="127"/>
-      <c r="D76" s="120"/>
+      <c r="D76" s="119"/>
       <c r="E76" s="104"/>
       <c r="F76" s="104"/>
       <c r="G76" s="105"/>
@@ -12548,9 +11894,9 @@
       <c r="K76" s="104"/>
       <c r="L76" s="104"/>
       <c r="M76" s="104"/>
-      <c r="N76" s="120"/>
-      <c r="O76" s="120"/>
-      <c r="P76" s="120"/>
+      <c r="N76" s="119"/>
+      <c r="O76" s="119"/>
+      <c r="P76" s="119"/>
       <c r="Q76" s="15"/>
       <c r="R76" s="15"/>
       <c r="S76" s="15"/>
@@ -12622,7 +11968,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="127"/>
       <c r="C77" s="127"/>
-      <c r="D77" s="120"/>
+      <c r="D77" s="119"/>
       <c r="E77" s="104"/>
       <c r="F77" s="104"/>
       <c r="G77" s="105"/>
@@ -12632,9 +11978,9 @@
       <c r="K77" s="104"/>
       <c r="L77" s="104"/>
       <c r="M77" s="104"/>
-      <c r="N77" s="120"/>
-      <c r="O77" s="120"/>
-      <c r="P77" s="120"/>
+      <c r="N77" s="119"/>
+      <c r="O77" s="119"/>
+      <c r="P77" s="119"/>
       <c r="Q77" s="15"/>
       <c r="R77" s="15"/>
       <c r="S77" s="15"/>
@@ -12706,7 +12052,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="127"/>
       <c r="C78" s="127"/>
-      <c r="D78" s="120"/>
+      <c r="D78" s="119"/>
       <c r="E78" s="104"/>
       <c r="F78" s="104"/>
       <c r="G78" s="105"/>
@@ -12716,9 +12062,9 @@
       <c r="K78" s="104"/>
       <c r="L78" s="104"/>
       <c r="M78" s="104"/>
-      <c r="N78" s="120"/>
-      <c r="O78" s="120"/>
-      <c r="P78" s="120"/>
+      <c r="N78" s="119"/>
+      <c r="O78" s="119"/>
+      <c r="P78" s="119"/>
       <c r="Q78" s="15"/>
       <c r="R78" s="15"/>
       <c r="S78" s="15"/>
@@ -12790,7 +12136,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="127"/>
       <c r="C79" s="127"/>
-      <c r="D79" s="120"/>
+      <c r="D79" s="119"/>
       <c r="E79" s="104"/>
       <c r="F79" s="104"/>
       <c r="G79" s="105"/>
@@ -12800,9 +12146,9 @@
       <c r="K79" s="104"/>
       <c r="L79" s="104"/>
       <c r="M79" s="104"/>
-      <c r="N79" s="120"/>
-      <c r="O79" s="120"/>
-      <c r="P79" s="120"/>
+      <c r="N79" s="119"/>
+      <c r="O79" s="119"/>
+      <c r="P79" s="119"/>
       <c r="Q79" s="15"/>
       <c r="R79" s="15"/>
       <c r="S79" s="15"/>
@@ -12874,7 +12220,7 @@
       <c r="A80" s="19"/>
       <c r="B80" s="127"/>
       <c r="C80" s="127"/>
-      <c r="D80" s="120"/>
+      <c r="D80" s="119"/>
       <c r="E80" s="104"/>
       <c r="F80" s="104"/>
       <c r="G80" s="105"/>
@@ -12884,9 +12230,9 @@
       <c r="K80" s="104"/>
       <c r="L80" s="104"/>
       <c r="M80" s="104"/>
-      <c r="N80" s="120"/>
-      <c r="O80" s="120"/>
-      <c r="P80" s="120"/>
+      <c r="N80" s="119"/>
+      <c r="O80" s="119"/>
+      <c r="P80" s="119"/>
       <c r="Q80" s="15"/>
       <c r="R80" s="15"/>
       <c r="S80" s="15"/>
@@ -12958,7 +12304,7 @@
       <c r="A81" s="19"/>
       <c r="B81" s="127"/>
       <c r="C81" s="127"/>
-      <c r="D81" s="120"/>
+      <c r="D81" s="119"/>
       <c r="E81" s="104"/>
       <c r="F81" s="104"/>
       <c r="G81" s="105"/>
@@ -12968,9 +12314,9 @@
       <c r="K81" s="104"/>
       <c r="L81" s="104"/>
       <c r="M81" s="104"/>
-      <c r="N81" s="120"/>
-      <c r="O81" s="120"/>
-      <c r="P81" s="120"/>
+      <c r="N81" s="119"/>
+      <c r="O81" s="119"/>
+      <c r="P81" s="119"/>
       <c r="Q81" s="15"/>
       <c r="R81" s="15"/>
       <c r="S81" s="15"/>
@@ -13042,7 +12388,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="127"/>
       <c r="C82" s="127"/>
-      <c r="D82" s="120"/>
+      <c r="D82" s="119"/>
       <c r="E82" s="104"/>
       <c r="F82" s="104"/>
       <c r="G82" s="105"/>
@@ -13052,9 +12398,9 @@
       <c r="K82" s="104"/>
       <c r="L82" s="104"/>
       <c r="M82" s="104"/>
-      <c r="N82" s="120"/>
-      <c r="O82" s="120"/>
-      <c r="P82" s="120"/>
+      <c r="N82" s="119"/>
+      <c r="O82" s="119"/>
+      <c r="P82" s="119"/>
       <c r="Q82" s="15"/>
       <c r="R82" s="15"/>
       <c r="S82" s="15"/>
@@ -13126,7 +12472,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="127"/>
       <c r="C83" s="127"/>
-      <c r="D83" s="120"/>
+      <c r="D83" s="119"/>
       <c r="E83" s="104"/>
       <c r="F83" s="104"/>
       <c r="G83" s="105"/>
@@ -13136,9 +12482,9 @@
       <c r="K83" s="104"/>
       <c r="L83" s="104"/>
       <c r="M83" s="104"/>
-      <c r="N83" s="120"/>
-      <c r="O83" s="120"/>
-      <c r="P83" s="120"/>
+      <c r="N83" s="119"/>
+      <c r="O83" s="119"/>
+      <c r="P83" s="119"/>
       <c r="Q83" s="15"/>
       <c r="R83" s="15"/>
       <c r="S83" s="15"/>
@@ -13210,7 +12556,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="127"/>
       <c r="C84" s="127"/>
-      <c r="D84" s="120"/>
+      <c r="D84" s="119"/>
       <c r="E84" s="104"/>
       <c r="F84" s="104"/>
       <c r="G84" s="105"/>
@@ -13220,9 +12566,9 @@
       <c r="K84" s="104"/>
       <c r="L84" s="104"/>
       <c r="M84" s="104"/>
-      <c r="N84" s="120"/>
-      <c r="O84" s="120"/>
-      <c r="P84" s="120"/>
+      <c r="N84" s="119"/>
+      <c r="O84" s="119"/>
+      <c r="P84" s="119"/>
       <c r="Q84" s="15"/>
       <c r="R84" s="15"/>
       <c r="S84" s="15"/>
@@ -13294,7 +12640,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="127"/>
       <c r="C85" s="127"/>
-      <c r="D85" s="120"/>
+      <c r="D85" s="119"/>
       <c r="E85" s="104"/>
       <c r="F85" s="104"/>
       <c r="G85" s="105"/>
@@ -13304,9 +12650,9 @@
       <c r="K85" s="104"/>
       <c r="L85" s="104"/>
       <c r="M85" s="104"/>
-      <c r="N85" s="120"/>
-      <c r="O85" s="120"/>
-      <c r="P85" s="120"/>
+      <c r="N85" s="119"/>
+      <c r="O85" s="119"/>
+      <c r="P85" s="119"/>
       <c r="Q85" s="15"/>
       <c r="R85" s="15"/>
       <c r="S85" s="15"/>
@@ -13378,7 +12724,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="127"/>
       <c r="C86" s="127"/>
-      <c r="D86" s="120"/>
+      <c r="D86" s="119"/>
       <c r="E86" s="104"/>
       <c r="F86" s="104"/>
       <c r="G86" s="105"/>
@@ -13388,9 +12734,9 @@
       <c r="K86" s="104"/>
       <c r="L86" s="104"/>
       <c r="M86" s="104"/>
-      <c r="N86" s="120"/>
-      <c r="O86" s="120"/>
-      <c r="P86" s="120"/>
+      <c r="N86" s="119"/>
+      <c r="O86" s="119"/>
+      <c r="P86" s="119"/>
       <c r="Q86" s="15"/>
       <c r="R86" s="15"/>
       <c r="S86" s="15"/>
@@ -13462,7 +12808,7 @@
       <c r="A87" s="19"/>
       <c r="B87" s="127"/>
       <c r="C87" s="127"/>
-      <c r="D87" s="120"/>
+      <c r="D87" s="119"/>
       <c r="E87" s="104"/>
       <c r="F87" s="104"/>
       <c r="G87" s="105"/>
@@ -13472,9 +12818,9 @@
       <c r="K87" s="104"/>
       <c r="L87" s="104"/>
       <c r="M87" s="104"/>
-      <c r="N87" s="120"/>
-      <c r="O87" s="120"/>
-      <c r="P87" s="120"/>
+      <c r="N87" s="119"/>
+      <c r="O87" s="119"/>
+      <c r="P87" s="119"/>
       <c r="Q87" s="15"/>
       <c r="R87" s="15"/>
       <c r="S87" s="15"/>
@@ -13546,7 +12892,7 @@
       <c r="A88" s="19"/>
       <c r="B88" s="127"/>
       <c r="C88" s="127"/>
-      <c r="D88" s="120"/>
+      <c r="D88" s="119"/>
       <c r="E88" s="104"/>
       <c r="F88" s="104"/>
       <c r="G88" s="105"/>
@@ -13556,9 +12902,9 @@
       <c r="K88" s="104"/>
       <c r="L88" s="104"/>
       <c r="M88" s="104"/>
-      <c r="N88" s="120"/>
-      <c r="O88" s="120"/>
-      <c r="P88" s="120"/>
+      <c r="N88" s="119"/>
+      <c r="O88" s="119"/>
+      <c r="P88" s="119"/>
       <c r="Q88" s="15"/>
       <c r="R88" s="15"/>
       <c r="S88" s="15"/>
@@ -13630,7 +12976,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="127"/>
       <c r="C89" s="127"/>
-      <c r="D89" s="120"/>
+      <c r="D89" s="119"/>
       <c r="E89" s="104"/>
       <c r="F89" s="104"/>
       <c r="G89" s="105"/>
@@ -13640,9 +12986,9 @@
       <c r="K89" s="104"/>
       <c r="L89" s="104"/>
       <c r="M89" s="104"/>
-      <c r="N89" s="120"/>
-      <c r="O89" s="120"/>
-      <c r="P89" s="120"/>
+      <c r="N89" s="119"/>
+      <c r="O89" s="119"/>
+      <c r="P89" s="119"/>
       <c r="Q89" s="15"/>
       <c r="R89" s="15"/>
       <c r="S89" s="15"/>
@@ -13714,7 +13060,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="127"/>
       <c r="C90" s="127"/>
-      <c r="D90" s="120"/>
+      <c r="D90" s="119"/>
       <c r="E90" s="104"/>
       <c r="F90" s="104"/>
       <c r="G90" s="105"/>
@@ -13724,9 +13070,9 @@
       <c r="K90" s="104"/>
       <c r="L90" s="104"/>
       <c r="M90" s="104"/>
-      <c r="N90" s="120"/>
-      <c r="O90" s="120"/>
-      <c r="P90" s="120"/>
+      <c r="N90" s="119"/>
+      <c r="O90" s="119"/>
+      <c r="P90" s="119"/>
       <c r="Q90" s="15"/>
       <c r="R90" s="15"/>
       <c r="S90" s="15"/>
@@ -13798,7 +13144,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="127"/>
       <c r="C91" s="127"/>
-      <c r="D91" s="120"/>
+      <c r="D91" s="119"/>
       <c r="E91" s="104"/>
       <c r="F91" s="104"/>
       <c r="G91" s="105"/>
@@ -13808,9 +13154,9 @@
       <c r="K91" s="104"/>
       <c r="L91" s="104"/>
       <c r="M91" s="104"/>
-      <c r="N91" s="120"/>
-      <c r="O91" s="120"/>
-      <c r="P91" s="120"/>
+      <c r="N91" s="119"/>
+      <c r="O91" s="119"/>
+      <c r="P91" s="119"/>
       <c r="Q91" s="15"/>
       <c r="R91" s="15"/>
       <c r="S91" s="15"/>
@@ -13882,7 +13228,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="127"/>
       <c r="C92" s="127"/>
-      <c r="D92" s="120"/>
+      <c r="D92" s="119"/>
       <c r="E92" s="104"/>
       <c r="F92" s="104"/>
       <c r="G92" s="105"/>
@@ -13892,9 +13238,9 @@
       <c r="K92" s="104"/>
       <c r="L92" s="104"/>
       <c r="M92" s="104"/>
-      <c r="N92" s="120"/>
-      <c r="O92" s="120"/>
-      <c r="P92" s="120"/>
+      <c r="N92" s="119"/>
+      <c r="O92" s="119"/>
+      <c r="P92" s="119"/>
       <c r="Q92" s="15"/>
       <c r="R92" s="15"/>
       <c r="S92" s="15"/>
@@ -13966,7 +13312,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="127"/>
       <c r="C93" s="127"/>
-      <c r="D93" s="120"/>
+      <c r="D93" s="119"/>
       <c r="E93" s="104"/>
       <c r="F93" s="104"/>
       <c r="G93" s="105"/>
@@ -13976,9 +13322,9 @@
       <c r="K93" s="104"/>
       <c r="L93" s="104"/>
       <c r="M93" s="104"/>
-      <c r="N93" s="120"/>
-      <c r="O93" s="120"/>
-      <c r="P93" s="120"/>
+      <c r="N93" s="119"/>
+      <c r="O93" s="119"/>
+      <c r="P93" s="119"/>
       <c r="Q93" s="15"/>
       <c r="R93" s="15"/>
       <c r="S93" s="15"/>
@@ -14050,7 +13396,7 @@
       <c r="A94" s="19"/>
       <c r="B94" s="127"/>
       <c r="C94" s="127"/>
-      <c r="D94" s="120"/>
+      <c r="D94" s="119"/>
       <c r="E94" s="104"/>
       <c r="F94" s="104"/>
       <c r="G94" s="105"/>
@@ -14060,9 +13406,9 @@
       <c r="K94" s="104"/>
       <c r="L94" s="104"/>
       <c r="M94" s="104"/>
-      <c r="N94" s="120"/>
-      <c r="O94" s="120"/>
-      <c r="P94" s="120"/>
+      <c r="N94" s="119"/>
+      <c r="O94" s="119"/>
+      <c r="P94" s="119"/>
       <c r="Q94" s="15"/>
       <c r="R94" s="15"/>
       <c r="S94" s="15"/>
@@ -14134,7 +13480,7 @@
       <c r="A95" s="19"/>
       <c r="B95" s="127"/>
       <c r="C95" s="127"/>
-      <c r="D95" s="120"/>
+      <c r="D95" s="119"/>
       <c r="E95" s="104"/>
       <c r="F95" s="104"/>
       <c r="G95" s="105"/>
@@ -14144,9 +13490,9 @@
       <c r="K95" s="104"/>
       <c r="L95" s="104"/>
       <c r="M95" s="104"/>
-      <c r="N95" s="120"/>
-      <c r="O95" s="120"/>
-      <c r="P95" s="120"/>
+      <c r="N95" s="119"/>
+      <c r="O95" s="119"/>
+      <c r="P95" s="119"/>
       <c r="Q95" s="15"/>
       <c r="R95" s="15"/>
       <c r="S95" s="15"/>
@@ -14218,7 +13564,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="127"/>
       <c r="C96" s="127"/>
-      <c r="D96" s="120"/>
+      <c r="D96" s="119"/>
       <c r="E96" s="104"/>
       <c r="F96" s="104"/>
       <c r="G96" s="105"/>
@@ -14228,9 +13574,9 @@
       <c r="K96" s="104"/>
       <c r="L96" s="104"/>
       <c r="M96" s="104"/>
-      <c r="N96" s="120"/>
-      <c r="O96" s="120"/>
-      <c r="P96" s="120"/>
+      <c r="N96" s="119"/>
+      <c r="O96" s="119"/>
+      <c r="P96" s="119"/>
       <c r="Q96" s="15"/>
       <c r="R96" s="15"/>
       <c r="S96" s="15"/>
@@ -14302,7 +13648,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="127"/>
       <c r="C97" s="127"/>
-      <c r="D97" s="120"/>
+      <c r="D97" s="119"/>
       <c r="E97" s="104"/>
       <c r="F97" s="104"/>
       <c r="G97" s="105"/>
@@ -14312,9 +13658,9 @@
       <c r="K97" s="104"/>
       <c r="L97" s="104"/>
       <c r="M97" s="104"/>
-      <c r="N97" s="120"/>
-      <c r="O97" s="120"/>
-      <c r="P97" s="120"/>
+      <c r="N97" s="119"/>
+      <c r="O97" s="119"/>
+      <c r="P97" s="119"/>
       <c r="Q97" s="15"/>
       <c r="R97" s="15"/>
       <c r="S97" s="15"/>
@@ -14386,7 +13732,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="127"/>
       <c r="C98" s="127"/>
-      <c r="D98" s="120"/>
+      <c r="D98" s="119"/>
       <c r="E98" s="104"/>
       <c r="F98" s="104"/>
       <c r="G98" s="105"/>
@@ -14396,9 +13742,9 @@
       <c r="K98" s="104"/>
       <c r="L98" s="104"/>
       <c r="M98" s="104"/>
-      <c r="N98" s="120"/>
-      <c r="O98" s="120"/>
-      <c r="P98" s="120"/>
+      <c r="N98" s="119"/>
+      <c r="O98" s="119"/>
+      <c r="P98" s="119"/>
       <c r="Q98" s="15"/>
       <c r="R98" s="15"/>
       <c r="S98" s="15"/>
@@ -14470,7 +13816,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="127"/>
       <c r="C99" s="127"/>
-      <c r="D99" s="120"/>
+      <c r="D99" s="119"/>
       <c r="E99" s="104"/>
       <c r="F99" s="104"/>
       <c r="G99" s="105"/>
@@ -14480,9 +13826,9 @@
       <c r="K99" s="104"/>
       <c r="L99" s="104"/>
       <c r="M99" s="104"/>
-      <c r="N99" s="120"/>
-      <c r="O99" s="120"/>
-      <c r="P99" s="120"/>
+      <c r="N99" s="119"/>
+      <c r="O99" s="119"/>
+      <c r="P99" s="119"/>
       <c r="Q99" s="15"/>
       <c r="R99" s="15"/>
       <c r="S99" s="15"/>
@@ -14554,7 +13900,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="127"/>
       <c r="C100" s="127"/>
-      <c r="D100" s="120"/>
+      <c r="D100" s="119"/>
       <c r="E100" s="104"/>
       <c r="F100" s="104"/>
       <c r="G100" s="105"/>
@@ -14564,9 +13910,9 @@
       <c r="K100" s="104"/>
       <c r="L100" s="104"/>
       <c r="M100" s="104"/>
-      <c r="N100" s="120"/>
-      <c r="O100" s="120"/>
-      <c r="P100" s="120"/>
+      <c r="N100" s="119"/>
+      <c r="O100" s="119"/>
+      <c r="P100" s="119"/>
       <c r="Q100" s="15"/>
       <c r="R100" s="15"/>
       <c r="S100" s="15"/>
@@ -14638,7 +13984,7 @@
       <c r="A101" s="19"/>
       <c r="B101" s="127"/>
       <c r="C101" s="127"/>
-      <c r="D101" s="120"/>
+      <c r="D101" s="119"/>
       <c r="E101" s="104"/>
       <c r="F101" s="104"/>
       <c r="G101" s="105"/>
@@ -14648,9 +13994,9 @@
       <c r="K101" s="104"/>
       <c r="L101" s="104"/>
       <c r="M101" s="104"/>
-      <c r="N101" s="120"/>
-      <c r="O101" s="120"/>
-      <c r="P101" s="120"/>
+      <c r="N101" s="119"/>
+      <c r="O101" s="119"/>
+      <c r="P101" s="119"/>
       <c r="Q101" s="15"/>
       <c r="R101" s="15"/>
       <c r="S101" s="15"/>
@@ -14722,7 +14068,7 @@
       <c r="A102" s="19"/>
       <c r="B102" s="127"/>
       <c r="C102" s="127"/>
-      <c r="D102" s="120"/>
+      <c r="D102" s="119"/>
       <c r="E102" s="104"/>
       <c r="F102" s="104"/>
       <c r="G102" s="105"/>
@@ -14732,9 +14078,9 @@
       <c r="K102" s="104"/>
       <c r="L102" s="104"/>
       <c r="M102" s="104"/>
-      <c r="N102" s="120"/>
-      <c r="O102" s="120"/>
-      <c r="P102" s="120"/>
+      <c r="N102" s="119"/>
+      <c r="O102" s="119"/>
+      <c r="P102" s="119"/>
       <c r="Q102" s="15"/>
       <c r="R102" s="15"/>
       <c r="S102" s="15"/>
@@ -14806,7 +14152,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="127"/>
       <c r="C103" s="127"/>
-      <c r="D103" s="120"/>
+      <c r="D103" s="119"/>
       <c r="E103" s="104"/>
       <c r="F103" s="104"/>
       <c r="G103" s="105"/>
@@ -14816,9 +14162,9 @@
       <c r="K103" s="104"/>
       <c r="L103" s="104"/>
       <c r="M103" s="104"/>
-      <c r="N103" s="120"/>
-      <c r="O103" s="120"/>
-      <c r="P103" s="120"/>
+      <c r="N103" s="119"/>
+      <c r="O103" s="119"/>
+      <c r="P103" s="119"/>
       <c r="Q103" s="15"/>
       <c r="R103" s="15"/>
       <c r="S103" s="15"/>
@@ -14890,7 +14236,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="127"/>
       <c r="C104" s="127"/>
-      <c r="D104" s="120"/>
+      <c r="D104" s="119"/>
       <c r="E104" s="104"/>
       <c r="F104" s="104"/>
       <c r="G104" s="105"/>
@@ -14900,9 +14246,9 @@
       <c r="K104" s="104"/>
       <c r="L104" s="104"/>
       <c r="M104" s="104"/>
-      <c r="N104" s="120"/>
-      <c r="O104" s="120"/>
-      <c r="P104" s="120"/>
+      <c r="N104" s="119"/>
+      <c r="O104" s="119"/>
+      <c r="P104" s="119"/>
       <c r="Q104" s="15"/>
       <c r="R104" s="15"/>
       <c r="S104" s="15"/>
@@ -14974,7 +14320,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="127"/>
       <c r="C105" s="127"/>
-      <c r="D105" s="120"/>
+      <c r="D105" s="119"/>
       <c r="E105" s="104"/>
       <c r="F105" s="104"/>
       <c r="G105" s="105"/>
@@ -14984,9 +14330,9 @@
       <c r="K105" s="104"/>
       <c r="L105" s="104"/>
       <c r="M105" s="104"/>
-      <c r="N105" s="120"/>
-      <c r="O105" s="120"/>
-      <c r="P105" s="120"/>
+      <c r="N105" s="119"/>
+      <c r="O105" s="119"/>
+      <c r="P105" s="119"/>
       <c r="Q105" s="15"/>
       <c r="R105" s="15"/>
       <c r="S105" s="15"/>
@@ -15058,7 +14404,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="127"/>
       <c r="C106" s="127"/>
-      <c r="D106" s="120"/>
+      <c r="D106" s="119"/>
       <c r="E106" s="104"/>
       <c r="F106" s="104"/>
       <c r="G106" s="105"/>
@@ -15068,9 +14414,9 @@
       <c r="K106" s="104"/>
       <c r="L106" s="104"/>
       <c r="M106" s="104"/>
-      <c r="N106" s="120"/>
-      <c r="O106" s="120"/>
-      <c r="P106" s="120"/>
+      <c r="N106" s="119"/>
+      <c r="O106" s="119"/>
+      <c r="P106" s="119"/>
       <c r="Q106" s="15"/>
       <c r="R106" s="15"/>
       <c r="S106" s="15"/>
@@ -15142,7 +14488,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="127"/>
       <c r="C107" s="127"/>
-      <c r="D107" s="120"/>
+      <c r="D107" s="119"/>
       <c r="E107" s="104"/>
       <c r="F107" s="104"/>
       <c r="G107" s="105"/>
@@ -15152,9 +14498,9 @@
       <c r="K107" s="104"/>
       <c r="L107" s="104"/>
       <c r="M107" s="104"/>
-      <c r="N107" s="120"/>
-      <c r="O107" s="120"/>
-      <c r="P107" s="120"/>
+      <c r="N107" s="119"/>
+      <c r="O107" s="119"/>
+      <c r="P107" s="119"/>
       <c r="Q107" s="15"/>
       <c r="R107" s="15"/>
       <c r="S107" s="15"/>
@@ -15226,7 +14572,7 @@
       <c r="A108" s="19"/>
       <c r="B108" s="127"/>
       <c r="C108" s="127"/>
-      <c r="D108" s="120"/>
+      <c r="D108" s="119"/>
       <c r="E108" s="104"/>
       <c r="F108" s="104"/>
       <c r="G108" s="105"/>
@@ -15236,9 +14582,9 @@
       <c r="K108" s="104"/>
       <c r="L108" s="104"/>
       <c r="M108" s="104"/>
-      <c r="N108" s="120"/>
-      <c r="O108" s="120"/>
-      <c r="P108" s="120"/>
+      <c r="N108" s="119"/>
+      <c r="O108" s="119"/>
+      <c r="P108" s="119"/>
       <c r="Q108" s="15"/>
       <c r="R108" s="15"/>
       <c r="S108" s="15"/>
@@ -15310,7 +14656,7 @@
       <c r="A109" s="19"/>
       <c r="B109" s="127"/>
       <c r="C109" s="127"/>
-      <c r="D109" s="120"/>
+      <c r="D109" s="119"/>
       <c r="E109" s="104"/>
       <c r="F109" s="104"/>
       <c r="G109" s="105"/>
@@ -15320,9 +14666,9 @@
       <c r="K109" s="104"/>
       <c r="L109" s="104"/>
       <c r="M109" s="104"/>
-      <c r="N109" s="120"/>
-      <c r="O109" s="120"/>
-      <c r="P109" s="120"/>
+      <c r="N109" s="119"/>
+      <c r="O109" s="119"/>
+      <c r="P109" s="119"/>
       <c r="Q109" s="15"/>
       <c r="R109" s="15"/>
       <c r="S109" s="15"/>
@@ -15394,7 +14740,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="127"/>
       <c r="C110" s="127"/>
-      <c r="D110" s="120"/>
+      <c r="D110" s="119"/>
       <c r="E110" s="104"/>
       <c r="F110" s="104"/>
       <c r="G110" s="105"/>
@@ -15404,9 +14750,9 @@
       <c r="K110" s="104"/>
       <c r="L110" s="104"/>
       <c r="M110" s="104"/>
-      <c r="N110" s="120"/>
-      <c r="O110" s="120"/>
-      <c r="P110" s="120"/>
+      <c r="N110" s="119"/>
+      <c r="O110" s="119"/>
+      <c r="P110" s="119"/>
       <c r="Q110" s="15"/>
       <c r="R110" s="15"/>
       <c r="S110" s="15"/>
@@ -15478,7 +14824,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="127"/>
       <c r="C111" s="127"/>
-      <c r="D111" s="120"/>
+      <c r="D111" s="119"/>
       <c r="E111" s="104"/>
       <c r="F111" s="104"/>
       <c r="G111" s="105"/>
@@ -15488,9 +14834,9 @@
       <c r="K111" s="104"/>
       <c r="L111" s="104"/>
       <c r="M111" s="104"/>
-      <c r="N111" s="120"/>
-      <c r="O111" s="120"/>
-      <c r="P111" s="120"/>
+      <c r="N111" s="119"/>
+      <c r="O111" s="119"/>
+      <c r="P111" s="119"/>
       <c r="Q111" s="15"/>
       <c r="R111" s="15"/>
       <c r="S111" s="15"/>
@@ -15562,7 +14908,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="127"/>
       <c r="C112" s="127"/>
-      <c r="D112" s="120"/>
+      <c r="D112" s="119"/>
       <c r="E112" s="104"/>
       <c r="F112" s="104"/>
       <c r="G112" s="105"/>
@@ -15572,9 +14918,9 @@
       <c r="K112" s="104"/>
       <c r="L112" s="104"/>
       <c r="M112" s="104"/>
-      <c r="N112" s="120"/>
-      <c r="O112" s="120"/>
-      <c r="P112" s="120"/>
+      <c r="N112" s="119"/>
+      <c r="O112" s="119"/>
+      <c r="P112" s="119"/>
       <c r="Q112" s="15"/>
       <c r="R112" s="15"/>
       <c r="S112" s="15"/>
@@ -15646,7 +14992,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="127"/>
       <c r="C113" s="127"/>
-      <c r="D113" s="120"/>
+      <c r="D113" s="119"/>
       <c r="E113" s="104"/>
       <c r="F113" s="104"/>
       <c r="G113" s="105"/>
@@ -15656,9 +15002,9 @@
       <c r="K113" s="104"/>
       <c r="L113" s="104"/>
       <c r="M113" s="104"/>
-      <c r="N113" s="120"/>
-      <c r="O113" s="120"/>
-      <c r="P113" s="120"/>
+      <c r="N113" s="119"/>
+      <c r="O113" s="119"/>
+      <c r="P113" s="119"/>
       <c r="Q113" s="15"/>
       <c r="R113" s="15"/>
       <c r="S113" s="15"/>
@@ -15730,7 +15076,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="127"/>
       <c r="C114" s="127"/>
-      <c r="D114" s="120"/>
+      <c r="D114" s="119"/>
       <c r="E114" s="104"/>
       <c r="F114" s="104"/>
       <c r="G114" s="105"/>
@@ -15740,9 +15086,9 @@
       <c r="K114" s="104"/>
       <c r="L114" s="104"/>
       <c r="M114" s="104"/>
-      <c r="N114" s="120"/>
-      <c r="O114" s="120"/>
-      <c r="P114" s="120"/>
+      <c r="N114" s="119"/>
+      <c r="O114" s="119"/>
+      <c r="P114" s="119"/>
       <c r="Q114" s="15"/>
       <c r="R114" s="15"/>
       <c r="S114" s="15"/>
@@ -15814,7 +15160,7 @@
       <c r="A115" s="19"/>
       <c r="B115" s="127"/>
       <c r="C115" s="127"/>
-      <c r="D115" s="120"/>
+      <c r="D115" s="119"/>
       <c r="E115" s="104"/>
       <c r="F115" s="104"/>
       <c r="G115" s="105"/>
@@ -15824,9 +15170,9 @@
       <c r="K115" s="104"/>
       <c r="L115" s="104"/>
       <c r="M115" s="104"/>
-      <c r="N115" s="120"/>
-      <c r="O115" s="120"/>
-      <c r="P115" s="120"/>
+      <c r="N115" s="119"/>
+      <c r="O115" s="119"/>
+      <c r="P115" s="119"/>
       <c r="Q115" s="15"/>
       <c r="R115" s="15"/>
       <c r="S115" s="15"/>
@@ -15898,7 +15244,7 @@
       <c r="A116" s="19"/>
       <c r="B116" s="127"/>
       <c r="C116" s="127"/>
-      <c r="D116" s="120"/>
+      <c r="D116" s="119"/>
       <c r="E116" s="104"/>
       <c r="F116" s="104"/>
       <c r="G116" s="105"/>
@@ -15908,9 +15254,9 @@
       <c r="K116" s="104"/>
       <c r="L116" s="104"/>
       <c r="M116" s="104"/>
-      <c r="N116" s="120"/>
-      <c r="O116" s="120"/>
-      <c r="P116" s="120"/>
+      <c r="N116" s="119"/>
+      <c r="O116" s="119"/>
+      <c r="P116" s="119"/>
       <c r="Q116" s="15"/>
       <c r="R116" s="15"/>
       <c r="S116" s="15"/>
@@ -15982,7 +15328,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="127"/>
       <c r="C117" s="127"/>
-      <c r="D117" s="120"/>
+      <c r="D117" s="119"/>
       <c r="E117" s="104"/>
       <c r="F117" s="104"/>
       <c r="G117" s="105"/>
@@ -15992,9 +15338,9 @@
       <c r="K117" s="104"/>
       <c r="L117" s="104"/>
       <c r="M117" s="104"/>
-      <c r="N117" s="120"/>
-      <c r="O117" s="120"/>
-      <c r="P117" s="120"/>
+      <c r="N117" s="119"/>
+      <c r="O117" s="119"/>
+      <c r="P117" s="119"/>
       <c r="Q117" s="15"/>
       <c r="R117" s="15"/>
       <c r="S117" s="15"/>
@@ -16066,7 +15412,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="127"/>
       <c r="C118" s="127"/>
-      <c r="D118" s="120"/>
+      <c r="D118" s="119"/>
       <c r="E118" s="104"/>
       <c r="F118" s="104"/>
       <c r="G118" s="105"/>
@@ -16076,9 +15422,9 @@
       <c r="K118" s="104"/>
       <c r="L118" s="104"/>
       <c r="M118" s="104"/>
-      <c r="N118" s="120"/>
-      <c r="O118" s="120"/>
-      <c r="P118" s="120"/>
+      <c r="N118" s="119"/>
+      <c r="O118" s="119"/>
+      <c r="P118" s="119"/>
       <c r="Q118" s="15"/>
       <c r="R118" s="15"/>
       <c r="S118" s="15"/>
@@ -16150,7 +15496,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="127"/>
       <c r="C119" s="127"/>
-      <c r="D119" s="120"/>
+      <c r="D119" s="119"/>
       <c r="E119" s="104"/>
       <c r="F119" s="104"/>
       <c r="G119" s="105"/>
@@ -16160,9 +15506,9 @@
       <c r="K119" s="104"/>
       <c r="L119" s="104"/>
       <c r="M119" s="104"/>
-      <c r="N119" s="120"/>
-      <c r="O119" s="120"/>
-      <c r="P119" s="120"/>
+      <c r="N119" s="119"/>
+      <c r="O119" s="119"/>
+      <c r="P119" s="119"/>
       <c r="Q119" s="15"/>
       <c r="R119" s="15"/>
       <c r="S119" s="15"/>
@@ -16234,7 +15580,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="127"/>
       <c r="C120" s="127"/>
-      <c r="D120" s="120"/>
+      <c r="D120" s="119"/>
       <c r="E120" s="104"/>
       <c r="F120" s="104"/>
       <c r="G120" s="105"/>
@@ -16244,9 +15590,9 @@
       <c r="K120" s="104"/>
       <c r="L120" s="104"/>
       <c r="M120" s="104"/>
-      <c r="N120" s="120"/>
-      <c r="O120" s="120"/>
-      <c r="P120" s="120"/>
+      <c r="N120" s="119"/>
+      <c r="O120" s="119"/>
+      <c r="P120" s="119"/>
       <c r="Q120" s="15"/>
       <c r="R120" s="15"/>
       <c r="S120" s="15"/>
@@ -16318,7 +15664,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="127"/>
       <c r="C121" s="127"/>
-      <c r="D121" s="120"/>
+      <c r="D121" s="119"/>
       <c r="E121" s="104"/>
       <c r="F121" s="104"/>
       <c r="G121" s="105"/>
@@ -16328,9 +15674,9 @@
       <c r="K121" s="104"/>
       <c r="L121" s="104"/>
       <c r="M121" s="104"/>
-      <c r="N121" s="120"/>
-      <c r="O121" s="120"/>
-      <c r="P121" s="120"/>
+      <c r="N121" s="119"/>
+      <c r="O121" s="119"/>
+      <c r="P121" s="119"/>
       <c r="Q121" s="15"/>
       <c r="R121" s="15"/>
       <c r="S121" s="15"/>
@@ -16402,7 +15748,7 @@
       <c r="A122" s="19"/>
       <c r="B122" s="127"/>
       <c r="C122" s="127"/>
-      <c r="D122" s="120"/>
+      <c r="D122" s="119"/>
       <c r="E122" s="104"/>
       <c r="F122" s="104"/>
       <c r="G122" s="105"/>
@@ -16412,9 +15758,9 @@
       <c r="K122" s="104"/>
       <c r="L122" s="104"/>
       <c r="M122" s="104"/>
-      <c r="N122" s="120"/>
-      <c r="O122" s="120"/>
-      <c r="P122" s="120"/>
+      <c r="N122" s="119"/>
+      <c r="O122" s="119"/>
+      <c r="P122" s="119"/>
       <c r="Q122" s="15"/>
       <c r="R122" s="15"/>
       <c r="S122" s="15"/>
@@ -16486,7 +15832,7 @@
       <c r="A123" s="19"/>
       <c r="B123" s="127"/>
       <c r="C123" s="127"/>
-      <c r="D123" s="120"/>
+      <c r="D123" s="119"/>
       <c r="E123" s="104"/>
       <c r="F123" s="104"/>
       <c r="G123" s="105"/>
@@ -16496,9 +15842,9 @@
       <c r="K123" s="104"/>
       <c r="L123" s="104"/>
       <c r="M123" s="104"/>
-      <c r="N123" s="120"/>
-      <c r="O123" s="120"/>
-      <c r="P123" s="120"/>
+      <c r="N123" s="119"/>
+      <c r="O123" s="119"/>
+      <c r="P123" s="119"/>
       <c r="Q123" s="15"/>
       <c r="R123" s="15"/>
       <c r="S123" s="15"/>
@@ -16570,7 +15916,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="127"/>
       <c r="C124" s="127"/>
-      <c r="D124" s="120"/>
+      <c r="D124" s="119"/>
       <c r="E124" s="104"/>
       <c r="F124" s="104"/>
       <c r="G124" s="105"/>
@@ -16580,9 +15926,9 @@
       <c r="K124" s="104"/>
       <c r="L124" s="104"/>
       <c r="M124" s="104"/>
-      <c r="N124" s="120"/>
-      <c r="O124" s="120"/>
-      <c r="P124" s="120"/>
+      <c r="N124" s="119"/>
+      <c r="O124" s="119"/>
+      <c r="P124" s="119"/>
       <c r="Q124" s="15"/>
       <c r="R124" s="15"/>
       <c r="S124" s="15"/>
@@ -16654,7 +16000,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="127"/>
       <c r="C125" s="127"/>
-      <c r="D125" s="120"/>
+      <c r="D125" s="119"/>
       <c r="E125" s="104"/>
       <c r="F125" s="104"/>
       <c r="G125" s="105"/>
@@ -16664,9 +16010,9 @@
       <c r="K125" s="104"/>
       <c r="L125" s="104"/>
       <c r="M125" s="104"/>
-      <c r="N125" s="120"/>
-      <c r="O125" s="120"/>
-      <c r="P125" s="120"/>
+      <c r="N125" s="119"/>
+      <c r="O125" s="119"/>
+      <c r="P125" s="119"/>
       <c r="Q125" s="15"/>
       <c r="R125" s="15"/>
       <c r="S125" s="15"/>
@@ -16738,7 +16084,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="127"/>
       <c r="C126" s="127"/>
-      <c r="D126" s="120"/>
+      <c r="D126" s="119"/>
       <c r="E126" s="104"/>
       <c r="F126" s="104"/>
       <c r="G126" s="105"/>
@@ -16748,9 +16094,9 @@
       <c r="K126" s="104"/>
       <c r="L126" s="104"/>
       <c r="M126" s="104"/>
-      <c r="N126" s="120"/>
-      <c r="O126" s="120"/>
-      <c r="P126" s="120"/>
+      <c r="N126" s="119"/>
+      <c r="O126" s="119"/>
+      <c r="P126" s="119"/>
       <c r="Q126" s="15"/>
       <c r="R126" s="15"/>
       <c r="S126" s="15"/>
@@ -16822,7 +16168,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="127"/>
       <c r="C127" s="127"/>
-      <c r="D127" s="120"/>
+      <c r="D127" s="119"/>
       <c r="E127" s="104"/>
       <c r="F127" s="104"/>
       <c r="G127" s="105"/>
@@ -16832,9 +16178,9 @@
       <c r="K127" s="104"/>
       <c r="L127" s="104"/>
       <c r="M127" s="104"/>
-      <c r="N127" s="120"/>
-      <c r="O127" s="120"/>
-      <c r="P127" s="120"/>
+      <c r="N127" s="119"/>
+      <c r="O127" s="119"/>
+      <c r="P127" s="119"/>
       <c r="Q127" s="15"/>
       <c r="R127" s="15"/>
       <c r="S127" s="15"/>
@@ -16906,7 +16252,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="127"/>
       <c r="C128" s="127"/>
-      <c r="D128" s="120"/>
+      <c r="D128" s="119"/>
       <c r="E128" s="104"/>
       <c r="F128" s="104"/>
       <c r="G128" s="105"/>
@@ -16916,9 +16262,9 @@
       <c r="K128" s="104"/>
       <c r="L128" s="104"/>
       <c r="M128" s="104"/>
-      <c r="N128" s="120"/>
-      <c r="O128" s="120"/>
-      <c r="P128" s="120"/>
+      <c r="N128" s="119"/>
+      <c r="O128" s="119"/>
+      <c r="P128" s="119"/>
       <c r="Q128" s="15"/>
       <c r="R128" s="15"/>
       <c r="S128" s="15"/>
@@ -16990,7 +16336,7 @@
       <c r="A129" s="19"/>
       <c r="B129" s="127"/>
       <c r="C129" s="127"/>
-      <c r="D129" s="120"/>
+      <c r="D129" s="119"/>
       <c r="E129" s="104"/>
       <c r="F129" s="104"/>
       <c r="G129" s="105"/>
@@ -17000,9 +16346,9 @@
       <c r="K129" s="104"/>
       <c r="L129" s="104"/>
       <c r="M129" s="104"/>
-      <c r="N129" s="120"/>
-      <c r="O129" s="120"/>
-      <c r="P129" s="120"/>
+      <c r="N129" s="119"/>
+      <c r="O129" s="119"/>
+      <c r="P129" s="119"/>
       <c r="Q129" s="15"/>
       <c r="R129" s="15"/>
       <c r="S129" s="15"/>
@@ -17074,7 +16420,7 @@
       <c r="A130" s="19"/>
       <c r="B130" s="127"/>
       <c r="C130" s="127"/>
-      <c r="D130" s="120"/>
+      <c r="D130" s="119"/>
       <c r="E130" s="104"/>
       <c r="F130" s="104"/>
       <c r="G130" s="105"/>
@@ -17084,9 +16430,9 @@
       <c r="K130" s="104"/>
       <c r="L130" s="104"/>
       <c r="M130" s="104"/>
-      <c r="N130" s="120"/>
-      <c r="O130" s="120"/>
-      <c r="P130" s="120"/>
+      <c r="N130" s="119"/>
+      <c r="O130" s="119"/>
+      <c r="P130" s="119"/>
       <c r="Q130" s="15"/>
       <c r="R130" s="15"/>
       <c r="S130" s="15"/>
@@ -17158,7 +16504,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="127"/>
       <c r="C131" s="127"/>
-      <c r="D131" s="120"/>
+      <c r="D131" s="119"/>
       <c r="E131" s="104"/>
       <c r="F131" s="104"/>
       <c r="G131" s="105"/>
@@ -17168,9 +16514,9 @@
       <c r="K131" s="104"/>
       <c r="L131" s="104"/>
       <c r="M131" s="104"/>
-      <c r="N131" s="120"/>
-      <c r="O131" s="120"/>
-      <c r="P131" s="120"/>
+      <c r="N131" s="119"/>
+      <c r="O131" s="119"/>
+      <c r="P131" s="119"/>
       <c r="Q131" s="15"/>
       <c r="R131" s="15"/>
       <c r="S131" s="15"/>
@@ -17242,7 +16588,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="127"/>
       <c r="C132" s="127"/>
-      <c r="D132" s="120"/>
+      <c r="D132" s="119"/>
       <c r="E132" s="104"/>
       <c r="F132" s="104"/>
       <c r="G132" s="105"/>
@@ -17252,9 +16598,9 @@
       <c r="K132" s="104"/>
       <c r="L132" s="104"/>
       <c r="M132" s="104"/>
-      <c r="N132" s="120"/>
-      <c r="O132" s="120"/>
-      <c r="P132" s="120"/>
+      <c r="N132" s="119"/>
+      <c r="O132" s="119"/>
+      <c r="P132" s="119"/>
       <c r="Q132" s="15"/>
       <c r="R132" s="15"/>
       <c r="S132" s="15"/>
@@ -17326,7 +16672,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="127"/>
       <c r="C133" s="127"/>
-      <c r="D133" s="120"/>
+      <c r="D133" s="119"/>
       <c r="E133" s="104"/>
       <c r="F133" s="104"/>
       <c r="G133" s="105"/>
@@ -17336,9 +16682,9 @@
       <c r="K133" s="104"/>
       <c r="L133" s="104"/>
       <c r="M133" s="104"/>
-      <c r="N133" s="120"/>
-      <c r="O133" s="120"/>
-      <c r="P133" s="120"/>
+      <c r="N133" s="119"/>
+      <c r="O133" s="119"/>
+      <c r="P133" s="119"/>
       <c r="Q133" s="15"/>
       <c r="R133" s="15"/>
       <c r="S133" s="15"/>
@@ -17410,7 +16756,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="127"/>
       <c r="C134" s="127"/>
-      <c r="D134" s="120"/>
+      <c r="D134" s="119"/>
       <c r="E134" s="104"/>
       <c r="F134" s="104"/>
       <c r="G134" s="105"/>
@@ -17420,9 +16766,9 @@
       <c r="K134" s="104"/>
       <c r="L134" s="104"/>
       <c r="M134" s="104"/>
-      <c r="N134" s="120"/>
-      <c r="O134" s="120"/>
-      <c r="P134" s="120"/>
+      <c r="N134" s="119"/>
+      <c r="O134" s="119"/>
+      <c r="P134" s="119"/>
       <c r="Q134" s="15"/>
       <c r="R134" s="15"/>
       <c r="S134" s="15"/>
@@ -17494,7 +16840,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="127"/>
       <c r="C135" s="127"/>
-      <c r="D135" s="120"/>
+      <c r="D135" s="119"/>
       <c r="E135" s="104"/>
       <c r="F135" s="104"/>
       <c r="G135" s="105"/>
@@ -17504,9 +16850,9 @@
       <c r="K135" s="104"/>
       <c r="L135" s="104"/>
       <c r="M135" s="104"/>
-      <c r="N135" s="120"/>
-      <c r="O135" s="120"/>
-      <c r="P135" s="120"/>
+      <c r="N135" s="119"/>
+      <c r="O135" s="119"/>
+      <c r="P135" s="119"/>
       <c r="Q135" s="15"/>
       <c r="R135" s="15"/>
       <c r="S135" s="15"/>
@@ -17578,7 +16924,7 @@
       <c r="A136" s="19"/>
       <c r="B136" s="127"/>
       <c r="C136" s="127"/>
-      <c r="D136" s="120"/>
+      <c r="D136" s="119"/>
       <c r="E136" s="104"/>
       <c r="F136" s="104"/>
       <c r="G136" s="105"/>
@@ -17588,9 +16934,9 @@
       <c r="K136" s="104"/>
       <c r="L136" s="104"/>
       <c r="M136" s="104"/>
-      <c r="N136" s="120"/>
-      <c r="O136" s="120"/>
-      <c r="P136" s="120"/>
+      <c r="N136" s="119"/>
+      <c r="O136" s="119"/>
+      <c r="P136" s="119"/>
       <c r="Q136" s="15"/>
       <c r="R136" s="15"/>
       <c r="S136" s="15"/>
@@ -17662,7 +17008,7 @@
       <c r="A137" s="19"/>
       <c r="B137" s="127"/>
       <c r="C137" s="127"/>
-      <c r="D137" s="120"/>
+      <c r="D137" s="119"/>
       <c r="E137" s="104"/>
       <c r="F137" s="104"/>
       <c r="G137" s="105"/>
@@ -17672,9 +17018,9 @@
       <c r="K137" s="104"/>
       <c r="L137" s="104"/>
       <c r="M137" s="104"/>
-      <c r="N137" s="120"/>
-      <c r="O137" s="120"/>
-      <c r="P137" s="120"/>
+      <c r="N137" s="119"/>
+      <c r="O137" s="119"/>
+      <c r="P137" s="119"/>
       <c r="Q137" s="15"/>
       <c r="R137" s="15"/>
       <c r="S137" s="15"/>
@@ -17746,7 +17092,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="127"/>
       <c r="C138" s="127"/>
-      <c r="D138" s="120"/>
+      <c r="D138" s="119"/>
       <c r="E138" s="104"/>
       <c r="F138" s="104"/>
       <c r="G138" s="105"/>
@@ -17756,9 +17102,9 @@
       <c r="K138" s="104"/>
       <c r="L138" s="104"/>
       <c r="M138" s="104"/>
-      <c r="N138" s="120"/>
-      <c r="O138" s="120"/>
-      <c r="P138" s="120"/>
+      <c r="N138" s="119"/>
+      <c r="O138" s="119"/>
+      <c r="P138" s="119"/>
       <c r="Q138" s="15"/>
       <c r="R138" s="15"/>
       <c r="S138" s="15"/>
@@ -17830,7 +17176,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="127"/>
       <c r="C139" s="127"/>
-      <c r="D139" s="120"/>
+      <c r="D139" s="119"/>
       <c r="E139" s="104"/>
       <c r="F139" s="104"/>
       <c r="G139" s="105"/>
@@ -17840,9 +17186,9 @@
       <c r="K139" s="104"/>
       <c r="L139" s="104"/>
       <c r="M139" s="104"/>
-      <c r="N139" s="120"/>
-      <c r="O139" s="120"/>
-      <c r="P139" s="120"/>
+      <c r="N139" s="119"/>
+      <c r="O139" s="119"/>
+      <c r="P139" s="119"/>
       <c r="Q139" s="15"/>
       <c r="R139" s="15"/>
       <c r="S139" s="15"/>
@@ -17914,7 +17260,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="127"/>
       <c r="C140" s="127"/>
-      <c r="D140" s="120"/>
+      <c r="D140" s="119"/>
       <c r="E140" s="104"/>
       <c r="F140" s="104"/>
       <c r="G140" s="105"/>
@@ -17924,9 +17270,9 @@
       <c r="K140" s="104"/>
       <c r="L140" s="104"/>
       <c r="M140" s="104"/>
-      <c r="N140" s="120"/>
-      <c r="O140" s="120"/>
-      <c r="P140" s="120"/>
+      <c r="N140" s="119"/>
+      <c r="O140" s="119"/>
+      <c r="P140" s="119"/>
       <c r="Q140" s="15"/>
       <c r="R140" s="15"/>
       <c r="S140" s="15"/>
@@ -17998,7 +17344,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="127"/>
       <c r="C141" s="127"/>
-      <c r="D141" s="120"/>
+      <c r="D141" s="119"/>
       <c r="E141" s="104"/>
       <c r="F141" s="104"/>
       <c r="G141" s="105"/>
@@ -18008,9 +17354,9 @@
       <c r="K141" s="104"/>
       <c r="L141" s="104"/>
       <c r="M141" s="104"/>
-      <c r="N141" s="120"/>
-      <c r="O141" s="120"/>
-      <c r="P141" s="120"/>
+      <c r="N141" s="119"/>
+      <c r="O141" s="119"/>
+      <c r="P141" s="119"/>
       <c r="Q141" s="15"/>
       <c r="R141" s="15"/>
       <c r="S141" s="15"/>
@@ -18082,7 +17428,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="127"/>
       <c r="C142" s="127"/>
-      <c r="D142" s="120"/>
+      <c r="D142" s="119"/>
       <c r="E142" s="104"/>
       <c r="F142" s="104"/>
       <c r="G142" s="105"/>
@@ -18092,9 +17438,9 @@
       <c r="K142" s="104"/>
       <c r="L142" s="104"/>
       <c r="M142" s="104"/>
-      <c r="N142" s="120"/>
-      <c r="O142" s="120"/>
-      <c r="P142" s="120"/>
+      <c r="N142" s="119"/>
+      <c r="O142" s="119"/>
+      <c r="P142" s="119"/>
       <c r="Q142" s="15"/>
       <c r="R142" s="15"/>
       <c r="S142" s="15"/>
@@ -18166,7 +17512,7 @@
       <c r="A143" s="19"/>
       <c r="B143" s="127"/>
       <c r="C143" s="127"/>
-      <c r="D143" s="120"/>
+      <c r="D143" s="119"/>
       <c r="E143" s="104"/>
       <c r="F143" s="104"/>
       <c r="G143" s="105"/>
@@ -18176,9 +17522,9 @@
       <c r="K143" s="104"/>
       <c r="L143" s="104"/>
       <c r="M143" s="104"/>
-      <c r="N143" s="120"/>
-      <c r="O143" s="120"/>
-      <c r="P143" s="120"/>
+      <c r="N143" s="119"/>
+      <c r="O143" s="119"/>
+      <c r="P143" s="119"/>
       <c r="Q143" s="15"/>
       <c r="R143" s="15"/>
       <c r="S143" s="15"/>
@@ -18250,7 +17596,7 @@
       <c r="A144" s="19"/>
       <c r="B144" s="127"/>
       <c r="C144" s="127"/>
-      <c r="D144" s="120"/>
+      <c r="D144" s="119"/>
       <c r="E144" s="104"/>
       <c r="F144" s="104"/>
       <c r="G144" s="105"/>
@@ -18260,9 +17606,9 @@
       <c r="K144" s="104"/>
       <c r="L144" s="104"/>
       <c r="M144" s="104"/>
-      <c r="N144" s="120"/>
-      <c r="O144" s="120"/>
-      <c r="P144" s="120"/>
+      <c r="N144" s="119"/>
+      <c r="O144" s="119"/>
+      <c r="P144" s="119"/>
       <c r="Q144" s="15"/>
       <c r="R144" s="15"/>
       <c r="S144" s="15"/>
@@ -18334,7 +17680,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="127"/>
       <c r="C145" s="127"/>
-      <c r="D145" s="120"/>
+      <c r="D145" s="119"/>
       <c r="E145" s="104"/>
       <c r="F145" s="104"/>
       <c r="G145" s="105"/>
@@ -18344,9 +17690,9 @@
       <c r="K145" s="104"/>
       <c r="L145" s="104"/>
       <c r="M145" s="104"/>
-      <c r="N145" s="120"/>
-      <c r="O145" s="120"/>
-      <c r="P145" s="120"/>
+      <c r="N145" s="119"/>
+      <c r="O145" s="119"/>
+      <c r="P145" s="119"/>
       <c r="Q145" s="15"/>
       <c r="R145" s="15"/>
       <c r="S145" s="15"/>
@@ -18418,7 +17764,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="127"/>
       <c r="C146" s="127"/>
-      <c r="D146" s="120"/>
+      <c r="D146" s="119"/>
       <c r="E146" s="104"/>
       <c r="F146" s="104"/>
       <c r="G146" s="105"/>
@@ -18428,9 +17774,9 @@
       <c r="K146" s="104"/>
       <c r="L146" s="104"/>
       <c r="M146" s="104"/>
-      <c r="N146" s="120"/>
-      <c r="O146" s="120"/>
-      <c r="P146" s="120"/>
+      <c r="N146" s="119"/>
+      <c r="O146" s="119"/>
+      <c r="P146" s="119"/>
       <c r="Q146" s="15"/>
       <c r="R146" s="15"/>
       <c r="S146" s="15"/>
@@ -18502,7 +17848,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="127"/>
       <c r="C147" s="127"/>
-      <c r="D147" s="120"/>
+      <c r="D147" s="119"/>
       <c r="E147" s="104"/>
       <c r="F147" s="104"/>
       <c r="G147" s="105"/>
@@ -18512,9 +17858,9 @@
       <c r="K147" s="104"/>
       <c r="L147" s="104"/>
       <c r="M147" s="104"/>
-      <c r="N147" s="120"/>
-      <c r="O147" s="120"/>
-      <c r="P147" s="120"/>
+      <c r="N147" s="119"/>
+      <c r="O147" s="119"/>
+      <c r="P147" s="119"/>
       <c r="Q147" s="15"/>
       <c r="R147" s="15"/>
       <c r="S147" s="15"/>
@@ -18586,7 +17932,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="127"/>
       <c r="C148" s="127"/>
-      <c r="D148" s="120"/>
+      <c r="D148" s="119"/>
       <c r="E148" s="104"/>
       <c r="F148" s="104"/>
       <c r="G148" s="105"/>
@@ -18596,9 +17942,9 @@
       <c r="K148" s="104"/>
       <c r="L148" s="104"/>
       <c r="M148" s="104"/>
-      <c r="N148" s="120"/>
-      <c r="O148" s="120"/>
-      <c r="P148" s="120"/>
+      <c r="N148" s="119"/>
+      <c r="O148" s="119"/>
+      <c r="P148" s="119"/>
       <c r="Q148" s="15"/>
       <c r="R148" s="15"/>
       <c r="S148" s="15"/>
@@ -18670,7 +18016,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="127"/>
       <c r="C149" s="127"/>
-      <c r="D149" s="120"/>
+      <c r="D149" s="119"/>
       <c r="E149" s="104"/>
       <c r="F149" s="104"/>
       <c r="G149" s="105"/>
@@ -18680,9 +18026,9 @@
       <c r="K149" s="104"/>
       <c r="L149" s="104"/>
       <c r="M149" s="104"/>
-      <c r="N149" s="120"/>
-      <c r="O149" s="120"/>
-      <c r="P149" s="120"/>
+      <c r="N149" s="119"/>
+      <c r="O149" s="119"/>
+      <c r="P149" s="119"/>
       <c r="Q149" s="15"/>
       <c r="R149" s="15"/>
       <c r="S149" s="15"/>
@@ -18754,7 +18100,7 @@
       <c r="A150" s="19"/>
       <c r="B150" s="127"/>
       <c r="C150" s="127"/>
-      <c r="D150" s="120"/>
+      <c r="D150" s="119"/>
       <c r="E150" s="104"/>
       <c r="F150" s="104"/>
       <c r="G150" s="105"/>
@@ -18764,9 +18110,9 @@
       <c r="K150" s="104"/>
       <c r="L150" s="104"/>
       <c r="M150" s="104"/>
-      <c r="N150" s="120"/>
-      <c r="O150" s="120"/>
-      <c r="P150" s="120"/>
+      <c r="N150" s="119"/>
+      <c r="O150" s="119"/>
+      <c r="P150" s="119"/>
       <c r="Q150" s="15"/>
       <c r="R150" s="15"/>
       <c r="S150" s="15"/>
@@ -18838,7 +18184,7 @@
       <c r="A151" s="19"/>
       <c r="B151" s="127"/>
       <c r="C151" s="127"/>
-      <c r="D151" s="120"/>
+      <c r="D151" s="119"/>
       <c r="E151" s="104"/>
       <c r="F151" s="104"/>
       <c r="G151" s="105"/>
@@ -18848,9 +18194,9 @@
       <c r="K151" s="104"/>
       <c r="L151" s="104"/>
       <c r="M151" s="104"/>
-      <c r="N151" s="120"/>
-      <c r="O151" s="120"/>
-      <c r="P151" s="120"/>
+      <c r="N151" s="119"/>
+      <c r="O151" s="119"/>
+      <c r="P151" s="119"/>
       <c r="Q151" s="15"/>
       <c r="R151" s="15"/>
       <c r="S151" s="15"/>
@@ -18922,7 +18268,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="127"/>
       <c r="C152" s="127"/>
-      <c r="D152" s="120"/>
+      <c r="D152" s="119"/>
       <c r="E152" s="104"/>
       <c r="F152" s="104"/>
       <c r="G152" s="105"/>
@@ -18932,9 +18278,9 @@
       <c r="K152" s="104"/>
       <c r="L152" s="104"/>
       <c r="M152" s="104"/>
-      <c r="N152" s="120"/>
-      <c r="O152" s="120"/>
-      <c r="P152" s="120"/>
+      <c r="N152" s="119"/>
+      <c r="O152" s="119"/>
+      <c r="P152" s="119"/>
       <c r="Q152" s="15"/>
       <c r="R152" s="15"/>
       <c r="S152" s="15"/>
@@ -19006,7 +18352,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="127"/>
       <c r="C153" s="127"/>
-      <c r="D153" s="120"/>
+      <c r="D153" s="119"/>
       <c r="E153" s="104"/>
       <c r="F153" s="104"/>
       <c r="G153" s="105"/>
@@ -19016,9 +18362,9 @@
       <c r="K153" s="104"/>
       <c r="L153" s="104"/>
       <c r="M153" s="104"/>
-      <c r="N153" s="120"/>
-      <c r="O153" s="120"/>
-      <c r="P153" s="120"/>
+      <c r="N153" s="119"/>
+      <c r="O153" s="119"/>
+      <c r="P153" s="119"/>
       <c r="Q153" s="15"/>
       <c r="R153" s="15"/>
       <c r="S153" s="15"/>
@@ -19090,7 +18436,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="127"/>
       <c r="C154" s="127"/>
-      <c r="D154" s="120"/>
+      <c r="D154" s="119"/>
       <c r="E154" s="104"/>
       <c r="F154" s="104"/>
       <c r="G154" s="105"/>
@@ -19100,9 +18446,9 @@
       <c r="K154" s="104"/>
       <c r="L154" s="104"/>
       <c r="M154" s="104"/>
-      <c r="N154" s="120"/>
-      <c r="O154" s="120"/>
-      <c r="P154" s="120"/>
+      <c r="N154" s="119"/>
+      <c r="O154" s="119"/>
+      <c r="P154" s="119"/>
       <c r="Q154" s="15"/>
       <c r="R154" s="15"/>
       <c r="S154" s="15"/>
@@ -19174,7 +18520,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="127"/>
       <c r="C155" s="127"/>
-      <c r="D155" s="120"/>
+      <c r="D155" s="119"/>
       <c r="E155" s="104"/>
       <c r="F155" s="104"/>
       <c r="G155" s="105"/>
@@ -19184,9 +18530,9 @@
       <c r="K155" s="104"/>
       <c r="L155" s="104"/>
       <c r="M155" s="104"/>
-      <c r="N155" s="120"/>
-      <c r="O155" s="120"/>
-      <c r="P155" s="120"/>
+      <c r="N155" s="119"/>
+      <c r="O155" s="119"/>
+      <c r="P155" s="119"/>
       <c r="Q155" s="15"/>
       <c r="R155" s="15"/>
       <c r="S155" s="15"/>
@@ -19258,7 +18604,7 @@
       <c r="A156" s="19"/>
       <c r="B156" s="127"/>
       <c r="C156" s="127"/>
-      <c r="D156" s="120"/>
+      <c r="D156" s="119"/>
       <c r="E156" s="104"/>
       <c r="F156" s="104"/>
       <c r="G156" s="105"/>
@@ -19268,9 +18614,9 @@
       <c r="K156" s="104"/>
       <c r="L156" s="104"/>
       <c r="M156" s="104"/>
-      <c r="N156" s="120"/>
-      <c r="O156" s="120"/>
-      <c r="P156" s="120"/>
+      <c r="N156" s="119"/>
+      <c r="O156" s="119"/>
+      <c r="P156" s="119"/>
       <c r="Q156" s="15"/>
       <c r="R156" s="15"/>
       <c r="S156" s="15"/>
@@ -19342,7 +18688,7 @@
       <c r="A157" s="19"/>
       <c r="B157" s="127"/>
       <c r="C157" s="127"/>
-      <c r="D157" s="120"/>
+      <c r="D157" s="119"/>
       <c r="E157" s="104"/>
       <c r="F157" s="104"/>
       <c r="G157" s="105"/>
@@ -19352,9 +18698,9 @@
       <c r="K157" s="104"/>
       <c r="L157" s="104"/>
       <c r="M157" s="104"/>
-      <c r="N157" s="120"/>
-      <c r="O157" s="120"/>
-      <c r="P157" s="120"/>
+      <c r="N157" s="119"/>
+      <c r="O157" s="119"/>
+      <c r="P157" s="119"/>
       <c r="Q157" s="15"/>
       <c r="R157" s="15"/>
       <c r="S157" s="15"/>
@@ -19426,7 +18772,7 @@
       <c r="A158" s="19"/>
       <c r="B158" s="127"/>
       <c r="C158" s="127"/>
-      <c r="D158" s="120"/>
+      <c r="D158" s="119"/>
       <c r="E158" s="104"/>
       <c r="F158" s="104"/>
       <c r="G158" s="105"/>
@@ -19436,9 +18782,9 @@
       <c r="K158" s="104"/>
       <c r="L158" s="104"/>
       <c r="M158" s="104"/>
-      <c r="N158" s="120"/>
-      <c r="O158" s="120"/>
-      <c r="P158" s="120"/>
+      <c r="N158" s="119"/>
+      <c r="O158" s="119"/>
+      <c r="P158" s="119"/>
       <c r="Q158" s="15"/>
       <c r="R158" s="15"/>
       <c r="S158" s="15"/>
@@ -19510,7 +18856,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="127"/>
       <c r="C159" s="127"/>
-      <c r="D159" s="120"/>
+      <c r="D159" s="119"/>
       <c r="E159" s="104"/>
       <c r="F159" s="104"/>
       <c r="G159" s="105"/>
@@ -19520,9 +18866,9 @@
       <c r="K159" s="104"/>
       <c r="L159" s="104"/>
       <c r="M159" s="104"/>
-      <c r="N159" s="120"/>
-      <c r="O159" s="120"/>
-      <c r="P159" s="120"/>
+      <c r="N159" s="119"/>
+      <c r="O159" s="119"/>
+      <c r="P159" s="119"/>
       <c r="Q159" s="15"/>
       <c r="R159" s="15"/>
       <c r="S159" s="15"/>
@@ -19594,7 +18940,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="127"/>
       <c r="C160" s="127"/>
-      <c r="D160" s="120"/>
+      <c r="D160" s="119"/>
       <c r="E160" s="104"/>
       <c r="F160" s="104"/>
       <c r="G160" s="105"/>
@@ -19604,9 +18950,9 @@
       <c r="K160" s="104"/>
       <c r="L160" s="104"/>
       <c r="M160" s="104"/>
-      <c r="N160" s="120"/>
-      <c r="O160" s="120"/>
-      <c r="P160" s="120"/>
+      <c r="N160" s="119"/>
+      <c r="O160" s="119"/>
+      <c r="P160" s="119"/>
       <c r="Q160" s="15"/>
       <c r="R160" s="15"/>
       <c r="S160" s="15"/>
@@ -19678,7 +19024,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="127"/>
       <c r="C161" s="127"/>
-      <c r="D161" s="120"/>
+      <c r="D161" s="119"/>
       <c r="E161" s="104"/>
       <c r="F161" s="104"/>
       <c r="G161" s="105"/>
@@ -19688,9 +19034,9 @@
       <c r="K161" s="104"/>
       <c r="L161" s="104"/>
       <c r="M161" s="104"/>
-      <c r="N161" s="120"/>
-      <c r="O161" s="120"/>
-      <c r="P161" s="120"/>
+      <c r="N161" s="119"/>
+      <c r="O161" s="119"/>
+      <c r="P161" s="119"/>
       <c r="Q161" s="15"/>
       <c r="R161" s="15"/>
       <c r="S161" s="15"/>
@@ -19762,7 +19108,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="127"/>
       <c r="C162" s="127"/>
-      <c r="D162" s="120"/>
+      <c r="D162" s="119"/>
       <c r="E162" s="104"/>
       <c r="F162" s="104"/>
       <c r="G162" s="105"/>
@@ -19772,9 +19118,9 @@
       <c r="K162" s="104"/>
       <c r="L162" s="104"/>
       <c r="M162" s="104"/>
-      <c r="N162" s="120"/>
-      <c r="O162" s="120"/>
-      <c r="P162" s="120"/>
+      <c r="N162" s="119"/>
+      <c r="O162" s="119"/>
+      <c r="P162" s="119"/>
       <c r="Q162" s="15"/>
       <c r="R162" s="15"/>
       <c r="S162" s="15"/>
@@ -19846,7 +19192,7 @@
       <c r="A163" s="19"/>
       <c r="B163" s="127"/>
       <c r="C163" s="127"/>
-      <c r="D163" s="120"/>
+      <c r="D163" s="119"/>
       <c r="E163" s="104"/>
       <c r="F163" s="104"/>
       <c r="G163" s="105"/>
@@ -19856,9 +19202,9 @@
       <c r="K163" s="104"/>
       <c r="L163" s="104"/>
       <c r="M163" s="104"/>
-      <c r="N163" s="120"/>
-      <c r="O163" s="120"/>
-      <c r="P163" s="120"/>
+      <c r="N163" s="119"/>
+      <c r="O163" s="119"/>
+      <c r="P163" s="119"/>
       <c r="Q163" s="15"/>
       <c r="R163" s="15"/>
       <c r="S163" s="15"/>
@@ -19930,7 +19276,7 @@
       <c r="A164" s="19"/>
       <c r="B164" s="127"/>
       <c r="C164" s="127"/>
-      <c r="D164" s="120"/>
+      <c r="D164" s="119"/>
       <c r="E164" s="104"/>
       <c r="F164" s="104"/>
       <c r="G164" s="105"/>
@@ -19940,9 +19286,9 @@
       <c r="K164" s="104"/>
       <c r="L164" s="104"/>
       <c r="M164" s="104"/>
-      <c r="N164" s="120"/>
-      <c r="O164" s="120"/>
-      <c r="P164" s="120"/>
+      <c r="N164" s="119"/>
+      <c r="O164" s="119"/>
+      <c r="P164" s="119"/>
       <c r="Q164" s="15"/>
       <c r="R164" s="15"/>
       <c r="S164" s="15"/>
@@ -20014,7 +19360,7 @@
       <c r="A165" s="19"/>
       <c r="B165" s="127"/>
       <c r="C165" s="127"/>
-      <c r="D165" s="120"/>
+      <c r="D165" s="119"/>
       <c r="E165" s="104"/>
       <c r="F165" s="104"/>
       <c r="G165" s="105"/>
@@ -20024,9 +19370,9 @@
       <c r="K165" s="104"/>
       <c r="L165" s="104"/>
       <c r="M165" s="104"/>
-      <c r="N165" s="120"/>
-      <c r="O165" s="120"/>
-      <c r="P165" s="120"/>
+      <c r="N165" s="119"/>
+      <c r="O165" s="119"/>
+      <c r="P165" s="119"/>
       <c r="Q165" s="15"/>
       <c r="R165" s="15"/>
       <c r="S165" s="15"/>
@@ -20098,7 +19444,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="127"/>
       <c r="C166" s="127"/>
-      <c r="D166" s="120"/>
+      <c r="D166" s="119"/>
       <c r="E166" s="104"/>
       <c r="F166" s="104"/>
       <c r="G166" s="105"/>
@@ -20108,9 +19454,9 @@
       <c r="K166" s="104"/>
       <c r="L166" s="104"/>
       <c r="M166" s="104"/>
-      <c r="N166" s="120"/>
-      <c r="O166" s="120"/>
-      <c r="P166" s="120"/>
+      <c r="N166" s="119"/>
+      <c r="O166" s="119"/>
+      <c r="P166" s="119"/>
       <c r="Q166" s="15"/>
       <c r="R166" s="15"/>
       <c r="S166" s="15"/>
@@ -20182,7 +19528,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="127"/>
       <c r="C167" s="127"/>
-      <c r="D167" s="120"/>
+      <c r="D167" s="119"/>
       <c r="E167" s="104"/>
       <c r="F167" s="104"/>
       <c r="G167" s="105"/>
@@ -20192,9 +19538,9 @@
       <c r="K167" s="104"/>
       <c r="L167" s="104"/>
       <c r="M167" s="104"/>
-      <c r="N167" s="120"/>
-      <c r="O167" s="120"/>
-      <c r="P167" s="120"/>
+      <c r="N167" s="119"/>
+      <c r="O167" s="119"/>
+      <c r="P167" s="119"/>
       <c r="Q167" s="15"/>
       <c r="R167" s="15"/>
       <c r="S167" s="15"/>
@@ -20266,7 +19612,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="127"/>
       <c r="C168" s="127"/>
-      <c r="D168" s="120"/>
+      <c r="D168" s="119"/>
       <c r="E168" s="104"/>
       <c r="F168" s="104"/>
       <c r="G168" s="105"/>
@@ -20276,9 +19622,9 @@
       <c r="K168" s="104"/>
       <c r="L168" s="104"/>
       <c r="M168" s="104"/>
-      <c r="N168" s="120"/>
-      <c r="O168" s="120"/>
-      <c r="P168" s="120"/>
+      <c r="N168" s="119"/>
+      <c r="O168" s="119"/>
+      <c r="P168" s="119"/>
       <c r="Q168" s="15"/>
       <c r="R168" s="15"/>
       <c r="S168" s="15"/>
@@ -20350,7 +19696,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="127"/>
       <c r="C169" s="127"/>
-      <c r="D169" s="120"/>
+      <c r="D169" s="119"/>
       <c r="E169" s="104"/>
       <c r="F169" s="104"/>
       <c r="G169" s="105"/>
@@ -20360,9 +19706,9 @@
       <c r="K169" s="104"/>
       <c r="L169" s="104"/>
       <c r="M169" s="104"/>
-      <c r="N169" s="120"/>
-      <c r="O169" s="120"/>
-      <c r="P169" s="120"/>
+      <c r="N169" s="119"/>
+      <c r="O169" s="119"/>
+      <c r="P169" s="119"/>
       <c r="Q169" s="15"/>
       <c r="R169" s="15"/>
       <c r="S169" s="15"/>
@@ -20434,7 +19780,7 @@
       <c r="A170" s="19"/>
       <c r="B170" s="127"/>
       <c r="C170" s="127"/>
-      <c r="D170" s="120"/>
+      <c r="D170" s="119"/>
       <c r="E170" s="104"/>
       <c r="F170" s="104"/>
       <c r="G170" s="105"/>
@@ -20444,9 +19790,9 @@
       <c r="K170" s="104"/>
       <c r="L170" s="104"/>
       <c r="M170" s="104"/>
-      <c r="N170" s="120"/>
-      <c r="O170" s="120"/>
-      <c r="P170" s="120"/>
+      <c r="N170" s="119"/>
+      <c r="O170" s="119"/>
+      <c r="P170" s="119"/>
       <c r="Q170" s="15"/>
       <c r="R170" s="15"/>
       <c r="S170" s="15"/>
@@ -20518,7 +19864,7 @@
       <c r="A171" s="19"/>
       <c r="B171" s="127"/>
       <c r="C171" s="127"/>
-      <c r="D171" s="120"/>
+      <c r="D171" s="119"/>
       <c r="E171" s="104"/>
       <c r="F171" s="104"/>
       <c r="G171" s="105"/>
@@ -20528,9 +19874,9 @@
       <c r="K171" s="104"/>
       <c r="L171" s="104"/>
       <c r="M171" s="104"/>
-      <c r="N171" s="120"/>
-      <c r="O171" s="120"/>
-      <c r="P171" s="120"/>
+      <c r="N171" s="119"/>
+      <c r="O171" s="119"/>
+      <c r="P171" s="119"/>
       <c r="Q171" s="15"/>
       <c r="R171" s="15"/>
       <c r="S171" s="15"/>
@@ -20602,7 +19948,7 @@
       <c r="A172" s="19"/>
       <c r="B172" s="127"/>
       <c r="C172" s="127"/>
-      <c r="D172" s="120"/>
+      <c r="D172" s="119"/>
       <c r="E172" s="104"/>
       <c r="F172" s="104"/>
       <c r="G172" s="105"/>
@@ -20612,9 +19958,9 @@
       <c r="K172" s="104"/>
       <c r="L172" s="104"/>
       <c r="M172" s="104"/>
-      <c r="N172" s="120"/>
-      <c r="O172" s="120"/>
-      <c r="P172" s="120"/>
+      <c r="N172" s="119"/>
+      <c r="O172" s="119"/>
+      <c r="P172" s="119"/>
       <c r="Q172" s="15"/>
       <c r="R172" s="15"/>
       <c r="S172" s="15"/>
@@ -20686,7 +20032,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="127"/>
       <c r="C173" s="127"/>
-      <c r="D173" s="120"/>
+      <c r="D173" s="119"/>
       <c r="E173" s="104"/>
       <c r="F173" s="104"/>
       <c r="G173" s="105"/>
@@ -20696,9 +20042,9 @@
       <c r="K173" s="104"/>
       <c r="L173" s="104"/>
       <c r="M173" s="104"/>
-      <c r="N173" s="120"/>
-      <c r="O173" s="120"/>
-      <c r="P173" s="120"/>
+      <c r="N173" s="119"/>
+      <c r="O173" s="119"/>
+      <c r="P173" s="119"/>
       <c r="Q173" s="15"/>
       <c r="R173" s="15"/>
       <c r="S173" s="15"/>
@@ -20770,7 +20116,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="127"/>
       <c r="C174" s="127"/>
-      <c r="D174" s="120"/>
+      <c r="D174" s="119"/>
       <c r="E174" s="104"/>
       <c r="F174" s="104"/>
       <c r="G174" s="105"/>
@@ -20780,9 +20126,9 @@
       <c r="K174" s="104"/>
       <c r="L174" s="104"/>
       <c r="M174" s="104"/>
-      <c r="N174" s="120"/>
-      <c r="O174" s="120"/>
-      <c r="P174" s="120"/>
+      <c r="N174" s="119"/>
+      <c r="O174" s="119"/>
+      <c r="P174" s="119"/>
       <c r="Q174" s="15"/>
       <c r="R174" s="15"/>
       <c r="S174" s="15"/>
@@ -20854,7 +20200,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="127"/>
       <c r="C175" s="127"/>
-      <c r="D175" s="120"/>
+      <c r="D175" s="119"/>
       <c r="E175" s="104"/>
       <c r="F175" s="104"/>
       <c r="G175" s="105"/>
@@ -20864,9 +20210,9 @@
       <c r="K175" s="104"/>
       <c r="L175" s="104"/>
       <c r="M175" s="104"/>
-      <c r="N175" s="120"/>
-      <c r="O175" s="120"/>
-      <c r="P175" s="120"/>
+      <c r="N175" s="119"/>
+      <c r="O175" s="119"/>
+      <c r="P175" s="119"/>
       <c r="Q175" s="15"/>
       <c r="R175" s="15"/>
       <c r="S175" s="15"/>
@@ -20938,7 +20284,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="127"/>
       <c r="C176" s="127"/>
-      <c r="D176" s="120"/>
+      <c r="D176" s="119"/>
       <c r="E176" s="104"/>
       <c r="F176" s="104"/>
       <c r="G176" s="105"/>
@@ -20948,9 +20294,9 @@
       <c r="K176" s="104"/>
       <c r="L176" s="104"/>
       <c r="M176" s="104"/>
-      <c r="N176" s="120"/>
-      <c r="O176" s="120"/>
-      <c r="P176" s="120"/>
+      <c r="N176" s="119"/>
+      <c r="O176" s="119"/>
+      <c r="P176" s="119"/>
       <c r="Q176" s="15"/>
       <c r="R176" s="15"/>
       <c r="S176" s="15"/>
@@ -21022,7 +20368,7 @@
       <c r="A177" s="19"/>
       <c r="B177" s="127"/>
       <c r="C177" s="127"/>
-      <c r="D177" s="120"/>
+      <c r="D177" s="119"/>
       <c r="E177" s="104"/>
       <c r="F177" s="104"/>
       <c r="G177" s="105"/>
@@ -21032,9 +20378,9 @@
       <c r="K177" s="104"/>
       <c r="L177" s="104"/>
       <c r="M177" s="104"/>
-      <c r="N177" s="120"/>
-      <c r="O177" s="120"/>
-      <c r="P177" s="120"/>
+      <c r="N177" s="119"/>
+      <c r="O177" s="119"/>
+      <c r="P177" s="119"/>
       <c r="Q177" s="15"/>
       <c r="R177" s="15"/>
       <c r="S177" s="15"/>
@@ -21106,7 +20452,7 @@
       <c r="A178" s="19"/>
       <c r="B178" s="127"/>
       <c r="C178" s="127"/>
-      <c r="D178" s="120"/>
+      <c r="D178" s="119"/>
       <c r="E178" s="104"/>
       <c r="F178" s="104"/>
       <c r="G178" s="105"/>
@@ -21116,9 +20462,9 @@
       <c r="K178" s="104"/>
       <c r="L178" s="104"/>
       <c r="M178" s="104"/>
-      <c r="N178" s="120"/>
-      <c r="O178" s="120"/>
-      <c r="P178" s="120"/>
+      <c r="N178" s="119"/>
+      <c r="O178" s="119"/>
+      <c r="P178" s="119"/>
       <c r="Q178" s="15"/>
       <c r="R178" s="15"/>
       <c r="S178" s="15"/>
@@ -21190,7 +20536,7 @@
       <c r="A179" s="19"/>
       <c r="B179" s="127"/>
       <c r="C179" s="127"/>
-      <c r="D179" s="120"/>
+      <c r="D179" s="119"/>
       <c r="E179" s="104"/>
       <c r="F179" s="104"/>
       <c r="G179" s="105"/>
@@ -21200,9 +20546,9 @@
       <c r="K179" s="104"/>
       <c r="L179" s="104"/>
       <c r="M179" s="104"/>
-      <c r="N179" s="120"/>
-      <c r="O179" s="120"/>
-      <c r="P179" s="120"/>
+      <c r="N179" s="119"/>
+      <c r="O179" s="119"/>
+      <c r="P179" s="119"/>
       <c r="Q179" s="15"/>
       <c r="R179" s="15"/>
       <c r="S179" s="15"/>
@@ -21274,7 +20620,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="127"/>
       <c r="C180" s="127"/>
-      <c r="D180" s="120"/>
+      <c r="D180" s="119"/>
       <c r="E180" s="104"/>
       <c r="F180" s="104"/>
       <c r="G180" s="105"/>
@@ -21284,9 +20630,9 @@
       <c r="K180" s="104"/>
       <c r="L180" s="104"/>
       <c r="M180" s="104"/>
-      <c r="N180" s="120"/>
-      <c r="O180" s="120"/>
-      <c r="P180" s="120"/>
+      <c r="N180" s="119"/>
+      <c r="O180" s="119"/>
+      <c r="P180" s="119"/>
       <c r="Q180" s="15"/>
       <c r="R180" s="15"/>
       <c r="S180" s="15"/>
@@ -21358,7 +20704,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="127"/>
       <c r="C181" s="127"/>
-      <c r="D181" s="120"/>
+      <c r="D181" s="119"/>
       <c r="E181" s="104"/>
       <c r="F181" s="104"/>
       <c r="G181" s="105"/>
@@ -21368,9 +20714,9 @@
       <c r="K181" s="104"/>
       <c r="L181" s="104"/>
       <c r="M181" s="104"/>
-      <c r="N181" s="120"/>
-      <c r="O181" s="120"/>
-      <c r="P181" s="120"/>
+      <c r="N181" s="119"/>
+      <c r="O181" s="119"/>
+      <c r="P181" s="119"/>
       <c r="Q181" s="15"/>
       <c r="R181" s="15"/>
       <c r="S181" s="15"/>
@@ -21442,7 +20788,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="127"/>
       <c r="C182" s="127"/>
-      <c r="D182" s="120"/>
+      <c r="D182" s="119"/>
       <c r="E182" s="104"/>
       <c r="F182" s="104"/>
       <c r="G182" s="105"/>
@@ -21452,9 +20798,9 @@
       <c r="K182" s="104"/>
       <c r="L182" s="104"/>
       <c r="M182" s="104"/>
-      <c r="N182" s="120"/>
-      <c r="O182" s="120"/>
-      <c r="P182" s="120"/>
+      <c r="N182" s="119"/>
+      <c r="O182" s="119"/>
+      <c r="P182" s="119"/>
       <c r="Q182" s="15"/>
       <c r="R182" s="15"/>
       <c r="S182" s="15"/>
@@ -21526,7 +20872,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="127"/>
       <c r="C183" s="127"/>
-      <c r="D183" s="120"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="104"/>
       <c r="F183" s="104"/>
       <c r="G183" s="105"/>
@@ -21536,9 +20882,9 @@
       <c r="K183" s="104"/>
       <c r="L183" s="104"/>
       <c r="M183" s="104"/>
-      <c r="N183" s="120"/>
-      <c r="O183" s="120"/>
-      <c r="P183" s="120"/>
+      <c r="N183" s="119"/>
+      <c r="O183" s="119"/>
+      <c r="P183" s="119"/>
       <c r="Q183" s="15"/>
       <c r="R183" s="15"/>
       <c r="S183" s="15"/>
@@ -21610,7 +20956,7 @@
       <c r="A184" s="19"/>
       <c r="B184" s="127"/>
       <c r="C184" s="127"/>
-      <c r="D184" s="120"/>
+      <c r="D184" s="119"/>
       <c r="E184" s="104"/>
       <c r="F184" s="104"/>
       <c r="G184" s="105"/>
@@ -21620,9 +20966,9 @@
       <c r="K184" s="104"/>
       <c r="L184" s="104"/>
       <c r="M184" s="104"/>
-      <c r="N184" s="120"/>
-      <c r="O184" s="120"/>
-      <c r="P184" s="120"/>
+      <c r="N184" s="119"/>
+      <c r="O184" s="119"/>
+      <c r="P184" s="119"/>
       <c r="Q184" s="15"/>
       <c r="R184" s="15"/>
       <c r="S184" s="15"/>
@@ -21694,7 +21040,7 @@
       <c r="A185" s="19"/>
       <c r="B185" s="127"/>
       <c r="C185" s="127"/>
-      <c r="D185" s="120"/>
+      <c r="D185" s="119"/>
       <c r="E185" s="104"/>
       <c r="F185" s="104"/>
       <c r="G185" s="105"/>
@@ -21704,9 +21050,9 @@
       <c r="K185" s="104"/>
       <c r="L185" s="104"/>
       <c r="M185" s="104"/>
-      <c r="N185" s="120"/>
-      <c r="O185" s="120"/>
-      <c r="P185" s="120"/>
+      <c r="N185" s="119"/>
+      <c r="O185" s="119"/>
+      <c r="P185" s="119"/>
       <c r="Q185" s="15"/>
       <c r="R185" s="15"/>
       <c r="S185" s="15"/>
@@ -21778,7 +21124,7 @@
       <c r="A186" s="19"/>
       <c r="B186" s="127"/>
       <c r="C186" s="127"/>
-      <c r="D186" s="120"/>
+      <c r="D186" s="119"/>
       <c r="E186" s="104"/>
       <c r="F186" s="104"/>
       <c r="G186" s="105"/>
@@ -21788,9 +21134,9 @@
       <c r="K186" s="104"/>
       <c r="L186" s="104"/>
       <c r="M186" s="104"/>
-      <c r="N186" s="120"/>
-      <c r="O186" s="120"/>
-      <c r="P186" s="120"/>
+      <c r="N186" s="119"/>
+      <c r="O186" s="119"/>
+      <c r="P186" s="119"/>
       <c r="Q186" s="15"/>
       <c r="R186" s="15"/>
       <c r="S186" s="15"/>
@@ -21862,7 +21208,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="127"/>
       <c r="C187" s="127"/>
-      <c r="D187" s="120"/>
+      <c r="D187" s="119"/>
       <c r="E187" s="104"/>
       <c r="F187" s="104"/>
       <c r="G187" s="105"/>
@@ -21872,9 +21218,9 @@
       <c r="K187" s="104"/>
       <c r="L187" s="104"/>
       <c r="M187" s="104"/>
-      <c r="N187" s="120"/>
-      <c r="O187" s="120"/>
-      <c r="P187" s="120"/>
+      <c r="N187" s="119"/>
+      <c r="O187" s="119"/>
+      <c r="P187" s="119"/>
       <c r="Q187" s="15"/>
       <c r="R187" s="15"/>
       <c r="S187" s="15"/>
@@ -21946,7 +21292,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="127"/>
       <c r="C188" s="127"/>
-      <c r="D188" s="120"/>
+      <c r="D188" s="119"/>
       <c r="E188" s="104"/>
       <c r="F188" s="104"/>
       <c r="G188" s="105"/>
@@ -21956,9 +21302,9 @@
       <c r="K188" s="104"/>
       <c r="L188" s="104"/>
       <c r="M188" s="104"/>
-      <c r="N188" s="120"/>
-      <c r="O188" s="120"/>
-      <c r="P188" s="120"/>
+      <c r="N188" s="119"/>
+      <c r="O188" s="119"/>
+      <c r="P188" s="119"/>
       <c r="Q188" s="15"/>
       <c r="R188" s="15"/>
       <c r="S188" s="15"/>
@@ -22030,7 +21376,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="127"/>
       <c r="C189" s="127"/>
-      <c r="D189" s="120"/>
+      <c r="D189" s="119"/>
       <c r="E189" s="104"/>
       <c r="F189" s="104"/>
       <c r="G189" s="105"/>
@@ -22040,9 +21386,9 @@
       <c r="K189" s="104"/>
       <c r="L189" s="104"/>
       <c r="M189" s="104"/>
-      <c r="N189" s="120"/>
-      <c r="O189" s="120"/>
-      <c r="P189" s="120"/>
+      <c r="N189" s="119"/>
+      <c r="O189" s="119"/>
+      <c r="P189" s="119"/>
       <c r="Q189" s="15"/>
       <c r="R189" s="15"/>
       <c r="S189" s="15"/>
@@ -22114,7 +21460,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="127"/>
       <c r="C190" s="127"/>
-      <c r="D190" s="120"/>
+      <c r="D190" s="119"/>
       <c r="E190" s="104"/>
       <c r="F190" s="104"/>
       <c r="G190" s="105"/>
@@ -22124,9 +21470,9 @@
       <c r="K190" s="104"/>
       <c r="L190" s="104"/>
       <c r="M190" s="104"/>
-      <c r="N190" s="120"/>
-      <c r="O190" s="120"/>
-      <c r="P190" s="120"/>
+      <c r="N190" s="119"/>
+      <c r="O190" s="119"/>
+      <c r="P190" s="119"/>
       <c r="Q190" s="15"/>
       <c r="R190" s="15"/>
       <c r="S190" s="15"/>
@@ -22198,7 +21544,7 @@
       <c r="A191" s="19"/>
       <c r="B191" s="127"/>
       <c r="C191" s="127"/>
-      <c r="D191" s="120"/>
+      <c r="D191" s="119"/>
       <c r="E191" s="104"/>
       <c r="F191" s="104"/>
       <c r="G191" s="105"/>
@@ -22208,9 +21554,9 @@
       <c r="K191" s="104"/>
       <c r="L191" s="104"/>
       <c r="M191" s="104"/>
-      <c r="N191" s="120"/>
-      <c r="O191" s="120"/>
-      <c r="P191" s="120"/>
+      <c r="N191" s="119"/>
+      <c r="O191" s="119"/>
+      <c r="P191" s="119"/>
       <c r="Q191" s="15"/>
       <c r="R191" s="15"/>
       <c r="S191" s="15"/>
@@ -22282,7 +21628,7 @@
       <c r="A192" s="19"/>
       <c r="B192" s="127"/>
       <c r="C192" s="127"/>
-      <c r="D192" s="120"/>
+      <c r="D192" s="119"/>
       <c r="E192" s="104"/>
       <c r="F192" s="104"/>
       <c r="G192" s="105"/>
@@ -22292,9 +21638,9 @@
       <c r="K192" s="104"/>
       <c r="L192" s="104"/>
       <c r="M192" s="104"/>
-      <c r="N192" s="120"/>
-      <c r="O192" s="120"/>
-      <c r="P192" s="120"/>
+      <c r="N192" s="119"/>
+      <c r="O192" s="119"/>
+      <c r="P192" s="119"/>
       <c r="Q192" s="15"/>
       <c r="R192" s="15"/>
       <c r="S192" s="15"/>
@@ -22366,7 +21712,7 @@
       <c r="A193" s="19"/>
       <c r="B193" s="127"/>
       <c r="C193" s="127"/>
-      <c r="D193" s="120"/>
+      <c r="D193" s="119"/>
       <c r="E193" s="104"/>
       <c r="F193" s="104"/>
       <c r="G193" s="105"/>
@@ -22376,9 +21722,9 @@
       <c r="K193" s="104"/>
       <c r="L193" s="104"/>
       <c r="M193" s="104"/>
-      <c r="N193" s="120"/>
-      <c r="O193" s="120"/>
-      <c r="P193" s="120"/>
+      <c r="N193" s="119"/>
+      <c r="O193" s="119"/>
+      <c r="P193" s="119"/>
       <c r="Q193" s="15"/>
       <c r="R193" s="15"/>
       <c r="S193" s="15"/>
@@ -22450,7 +21796,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="127"/>
       <c r="C194" s="127"/>
-      <c r="D194" s="120"/>
+      <c r="D194" s="119"/>
       <c r="E194" s="104"/>
       <c r="F194" s="104"/>
       <c r="G194" s="105"/>
@@ -22460,9 +21806,9 @@
       <c r="K194" s="104"/>
       <c r="L194" s="104"/>
       <c r="M194" s="104"/>
-      <c r="N194" s="120"/>
-      <c r="O194" s="120"/>
-      <c r="P194" s="120"/>
+      <c r="N194" s="119"/>
+      <c r="O194" s="119"/>
+      <c r="P194" s="119"/>
       <c r="Q194" s="15"/>
       <c r="R194" s="15"/>
       <c r="S194" s="15"/>
@@ -22534,7 +21880,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="127"/>
       <c r="C195" s="127"/>
-      <c r="D195" s="120"/>
+      <c r="D195" s="119"/>
       <c r="E195" s="104"/>
       <c r="F195" s="104"/>
       <c r="G195" s="105"/>
@@ -22544,9 +21890,9 @@
       <c r="K195" s="104"/>
       <c r="L195" s="104"/>
       <c r="M195" s="104"/>
-      <c r="N195" s="120"/>
-      <c r="O195" s="120"/>
-      <c r="P195" s="120"/>
+      <c r="N195" s="119"/>
+      <c r="O195" s="119"/>
+      <c r="P195" s="119"/>
       <c r="Q195" s="15"/>
       <c r="R195" s="15"/>
       <c r="S195" s="15"/>
@@ -22618,7 +21964,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="127"/>
       <c r="C196" s="127"/>
-      <c r="D196" s="120"/>
+      <c r="D196" s="119"/>
       <c r="E196" s="104"/>
       <c r="F196" s="104"/>
       <c r="G196" s="105"/>
@@ -22628,9 +21974,9 @@
       <c r="K196" s="104"/>
       <c r="L196" s="104"/>
       <c r="M196" s="104"/>
-      <c r="N196" s="120"/>
-      <c r="O196" s="120"/>
-      <c r="P196" s="120"/>
+      <c r="N196" s="119"/>
+      <c r="O196" s="119"/>
+      <c r="P196" s="119"/>
       <c r="Q196" s="15"/>
       <c r="R196" s="15"/>
       <c r="S196" s="15"/>
@@ -22702,7 +22048,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="127"/>
       <c r="C197" s="127"/>
-      <c r="D197" s="120"/>
+      <c r="D197" s="119"/>
       <c r="E197" s="104"/>
       <c r="F197" s="104"/>
       <c r="G197" s="105"/>
@@ -22712,9 +22058,9 @@
       <c r="K197" s="104"/>
       <c r="L197" s="104"/>
       <c r="M197" s="104"/>
-      <c r="N197" s="120"/>
-      <c r="O197" s="120"/>
-      <c r="P197" s="120"/>
+      <c r="N197" s="119"/>
+      <c r="O197" s="119"/>
+      <c r="P197" s="119"/>
       <c r="Q197" s="15"/>
       <c r="R197" s="15"/>
       <c r="S197" s="15"/>
@@ -22829,7 +22175,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa746dbf-12f2-443f-95a3-e59ee52e18fe}</x14:id>
+          <x14:id>{feb41b57-5429-4ab1-baaa-366519f0a351}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22846,13 +22192,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C29 C30:C197">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C197">
       <formula1>"李光军,李斌,张永菲,王昌泽,矫淑宏,胡兆稳,刘瀚远,苏浩南,林凤晟,孙启明,孙佳明,赵添志,田华,高杰,吴秀晗,宁文龙,宋成志"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D7:D29 D30:D197">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D7:D197">
       <formula1>"待启动 💡,进行中 🔛,开发完成👌,已完成 ❇️,已延期 💥"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M7:M8 M10:M29 M30:M197">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M7:M8 M10:M197">
       <formula1>"孙启明,孙佳明,赵添志,田华"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P7:P29">
@@ -22865,7 +22211,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa746dbf-12f2-443f-95a3-e59ee52e18fe}">
+          <x14:cfRule type="dataBar" id="{feb41b57-5429-4ab1-baaa-366519f0a351}">
             <x14:dataBar minLength="0" maxLength="100" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -23804,15 +23150,13 @@
     <row r="13" spans="1:73">
       <c r="A13" s="15"/>
       <c r="B13">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13">
-        <v>59</v>
-      </c>
-      <c r="F13">
-        <v>194</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F13"/>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>

--- a/成本核算平台需求跟踪矩阵.xlsx
+++ b/成本核算平台需求跟踪矩阵.xlsx
@@ -1,43 +1,1273 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
-  </bookViews>
-  <sheets>
-    <sheet name="项目管理" sheetId="2" r:id="rId1"/>
-    <sheet name="项目进展分析" sheetId="3" r:id="rId2"/>
-    <sheet name="项目甘特图" sheetId="4" r:id="rId3"/>
-    <sheet name="使用说明" sheetId="5" r:id="rId4"/>
-    <sheet name="节假日一览表" sheetId="6" r:id="rId5"/>
-    <sheet name="测试问题及整改记录" sheetId="7" r:id="rId6"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
-    <pivotCache cacheId="1" r:id="rId8"/>
-    <pivotCache cacheId="2" r:id="rId9"/>
-    <pivotCache cacheId="3" r:id="rId10"/>
-  </pivotCaches>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Go Excelize</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>6</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="6" baseType="lpstr">
+      <vt:lpstr>项目管理</vt:lpstr>
+      <vt:lpstr>项目进展分析</vt:lpstr>
+      <vt:lpstr>项目甘特图</vt:lpstr>
+      <vt:lpstr>使用说明</vt:lpstr>
+      <vt:lpstr>节假日一览表</vt:lpstr>
+      <vt:lpstr>测试问题及整改记录</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
+</file>
+
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>范皓为</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-30T06:31:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-30T09:22:18Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
+    <vt:lpwstr>073AF1713B094FDBB499D43966EF603B_12</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.25225</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
+    <vt:i4>0</vt:i4>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\drawings\drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2" descr="SEFMNF"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10843260" y="95250"/>
+          <a:ext cx="2577465" cy="3097530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl\drawings\drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>-38100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>745490</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 21" descr="XAjxGJ"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9845040" y="213360"/>
+          <a:ext cx="1158240" cy="707390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>-38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 39" descr="avQchw"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9845040" y="920750"/>
+          <a:ext cx="1158240" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl\pivotCache\pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A4:N29" sheet="项目管理"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="任务" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="一、底座与设计基线"/>
+        <s v="【若依底座接入与品牌裁剪】"/>
+        <s v="【首页驾驶舱基线】"/>
+        <s v="【详细设计文档体系】"/>
+        <s v="【完整数据库SQL与ER图】"/>
+        <s v="【需求跟踪矩阵初始化】"/>
+        <s v="二、配置主链恢复"/>
+        <s v="【业务域字典治理】"/>
+        <s v="【场景中心】"/>
+        <s v="【费用中心】"/>
+        <s v="【变量中心】"/>
+        <s v="【规则中心】"/>
+        <s v="【阶梯费率与依据变量】"/>
+        <s v="三、发布与治理恢复"/>
+        <s v="【发布中心】"/>
+        <s v="【版本差异与费用级视图】"/>
+        <s v="【引用校验与删除保护】"/>
+        <s v="【发布审计与回滚】"/>
+        <s v="四、运行链与性能治理"/>
+        <s v="【试算中心】"/>
+        <s v="【正式核算与批量任务】"/>
+        <s v="【结果台账与追溯】"/>
+        <s v="【百万级性能优化】"/>
+        <s v="【监控告警与通知】"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="备注" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="建立产品重构新基线"/>
+        <s v="完成独立仓库、品牌文案、导航精简"/>
+        <s v="首页切换为企业级成本核算驾驶舱"/>
+        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
+        <s v="形成完整建表语句、ER图、页面原型"/>
+        <s v="将模板转为当前项目进展、测试、计划台账"/>
+        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
+        <s v="独立系统字典并接入业务域下拉和筛选"/>
+        <s v="恢复场景台账、表单、筛选、治理入口"/>
+        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
+        <s v="恢复字典型、接口型、公式型变量工作台"/>
+        <s v="实现费用主线规则台账与条件编辑"/>
+        <s v="显式阶梯依据变量、区间规则、命中解释"/>
+        <s v="恢复场景发布、版本快照和费用级差异视图"/>
+        <s v="恢复发布说明、校验、版本台账、生效切换"/>
+        <s v="支持场景总览差异和费用级差异筛选"/>
+        <s v="恢复变量、费用、规则删除前实时预检查"/>
+        <s v="补齐版本详情、回滚、发布审计链路"/>
+        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
+        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
+        <s v="恢复按发布快照执行的单笔与批量核算"/>
+        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
+        <s v="批量分片、异步执行、索引与缓存优化"/>
+        <s v="恢复任务告警、失败订阅和通知治理"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="负责人" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="GitFhw"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="状态" numFmtId="0">
+      <sharedItems containsBlank="1" count="24">
+        <m/>
+        <s v="已完成 ❇️"/>
+        <s v="进行中 🚀"/>
+        <s v="未开始 ⏳"/>
+        <s v="开发完成👌" u="1"/>
+        <s v="已延期 💥" u="1"/>
+        <s v="进行中 🔛" u="1"/>
+        <s v="使用下拉列表显示任务状态" u="1"/>
+        <s v="待启动 💡" u="1"/>
+        <s v="李光军" u="1"/>
+        <s v="张永菲" u="1"/>
+        <s v="林凤晟" u="1"/>
+        <s v="刘瀚远" u="1"/>
+        <s v="矫淑宏" u="1"/>
+        <s v="孙佳明" u="1"/>
+        <s v="孙启明" u="1"/>
+        <s v="李斌" u="1"/>
+        <s v="苏浩南" u="1"/>
+        <s v="王昌泽" u="1"/>
+        <s v="胡兆稳" u="1"/>
+        <s v="宁文龙" u="1"/>
+        <s v="吴秀晗" u="1"/>
+        <s v="宋成志" u="1"/>
+        <s v="高杰" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-03-31T00:00:00"/>
+        <d v="2026-04-01T00:00:00"/>
+        <d v="2026-04-03T00:00:00"/>
+        <d v="2026-04-08T00:00:00"/>
+        <d v="2026-04-10T00:00:00"/>
+        <d v="2026-04-15T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-24T00:00:00"/>
+        <d v="2026-04-27T00:00:00"/>
+        <d v="2026-05-06T00:00:00"/>
+        <d v="2026-05-10T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-25T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计结束时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-04-21T00:00:00"/>
+        <d v="2026-04-02T00:00:00"/>
+        <d v="2026-04-07T00:00:00"/>
+        <d v="2026-04-09T00:00:00"/>
+        <d v="2026-04-14T00:00:00"/>
+        <d v="2026-04-18T00:00:00"/>
+        <d v="2026-05-08T00:00:00"/>
+        <d v="2026-04-28T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-06-05T00:00:00"/>
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-23T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时预估" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_自然日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="7"/>
+        <n v="9"/>
+        <n v="12"/>
+        <n v="31"/>
+        <n v="11"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_工作日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+        <n v="7"/>
+        <n v="10"/>
+        <n v="23"/>
+        <n v="9"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="完成度_x000a_ %" numFmtId="10">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+        <m/>
+        <n v="1"/>
+        <n v="0.15"/>
+        <n v="0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_开始时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_结束时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="测试人" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl\pivotCache\pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A4:N29" sheet="项目管理"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="任务" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="一、底座与设计基线"/>
+        <s v="【若依底座接入与品牌裁剪】"/>
+        <s v="【首页驾驶舱基线】"/>
+        <s v="【详细设计文档体系】"/>
+        <s v="【完整数据库SQL与ER图】"/>
+        <s v="【需求跟踪矩阵初始化】"/>
+        <s v="二、配置主链恢复"/>
+        <s v="【业务域字典治理】"/>
+        <s v="【场景中心】"/>
+        <s v="【费用中心】"/>
+        <s v="【变量中心】"/>
+        <s v="【规则中心】"/>
+        <s v="【阶梯费率与依据变量】"/>
+        <s v="三、发布与治理恢复"/>
+        <s v="【发布中心】"/>
+        <s v="【版本差异与费用级视图】"/>
+        <s v="【引用校验与删除保护】"/>
+        <s v="【发布审计与回滚】"/>
+        <s v="四、运行链与性能治理"/>
+        <s v="【试算中心】"/>
+        <s v="【正式核算与批量任务】"/>
+        <s v="【结果台账与追溯】"/>
+        <s v="【百万级性能优化】"/>
+        <s v="【监控告警与通知】"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="备注" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="建立产品重构新基线"/>
+        <s v="完成独立仓库、品牌文案、导航精简"/>
+        <s v="首页切换为企业级成本核算驾驶舱"/>
+        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
+        <s v="形成完整建表语句、ER图、页面原型"/>
+        <s v="将模板转为当前项目进展、测试、计划台账"/>
+        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
+        <s v="独立系统字典并接入业务域下拉和筛选"/>
+        <s v="恢复场景台账、表单、筛选、治理入口"/>
+        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
+        <s v="恢复字典型、接口型、公式型变量工作台"/>
+        <s v="实现费用主线规则台账与条件编辑"/>
+        <s v="显式阶梯依据变量、区间规则、命中解释"/>
+        <s v="恢复场景发布、版本快照和费用级差异视图"/>
+        <s v="恢复发布说明、校验、版本台账、生效切换"/>
+        <s v="支持场景总览差异和费用级差异筛选"/>
+        <s v="恢复变量、费用、规则删除前实时预检查"/>
+        <s v="补齐版本详情、回滚、发布审计链路"/>
+        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
+        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
+        <s v="恢复按发布快照执行的单笔与批量核算"/>
+        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
+        <s v="批量分片、异步执行、索引与缓存优化"/>
+        <s v="恢复任务告警、失败订阅和通知治理"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="负责人" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="GitFhw"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="状态" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <m/>
+        <s v="已完成 ❇️"/>
+        <s v="进行中 🚀"/>
+        <s v="未开始 ⏳"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-03-31T00:00:00"/>
+        <d v="2026-04-01T00:00:00"/>
+        <d v="2026-04-03T00:00:00"/>
+        <d v="2026-04-08T00:00:00"/>
+        <d v="2026-04-10T00:00:00"/>
+        <d v="2026-04-15T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-24T00:00:00"/>
+        <d v="2026-04-27T00:00:00"/>
+        <d v="2026-05-06T00:00:00"/>
+        <d v="2026-05-10T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-25T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计结束时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-04-21T00:00:00"/>
+        <d v="2026-04-02T00:00:00"/>
+        <d v="2026-04-07T00:00:00"/>
+        <d v="2026-04-09T00:00:00"/>
+        <d v="2026-04-14T00:00:00"/>
+        <d v="2026-04-18T00:00:00"/>
+        <d v="2026-05-08T00:00:00"/>
+        <d v="2026-04-28T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-06-05T00:00:00"/>
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-23T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时预估" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_自然日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="7"/>
+        <n v="9"/>
+        <n v="12"/>
+        <n v="31"/>
+        <n v="11"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_工作日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+        <n v="7"/>
+        <n v="10"/>
+        <n v="23"/>
+        <n v="9"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="完成度_x000a_ %" numFmtId="10">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+        <m/>
+        <n v="1"/>
+        <n v="0.15"/>
+        <n v="0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_开始时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_结束时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="测试人" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl\pivotCache\pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A4:N29" sheet="项目管理"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="任务" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="一、底座与设计基线"/>
+        <s v="【若依底座接入与品牌裁剪】"/>
+        <s v="【首页驾驶舱基线】"/>
+        <s v="【详细设计文档体系】"/>
+        <s v="【完整数据库SQL与ER图】"/>
+        <s v="【需求跟踪矩阵初始化】"/>
+        <s v="二、配置主链恢复"/>
+        <s v="【业务域字典治理】"/>
+        <s v="【场景中心】"/>
+        <s v="【费用中心】"/>
+        <s v="【变量中心】"/>
+        <s v="【规则中心】"/>
+        <s v="【阶梯费率与依据变量】"/>
+        <s v="三、发布与治理恢复"/>
+        <s v="【发布中心】"/>
+        <s v="【版本差异与费用级视图】"/>
+        <s v="【引用校验与删除保护】"/>
+        <s v="【发布审计与回滚】"/>
+        <s v="四、运行链与性能治理"/>
+        <s v="【试算中心】"/>
+        <s v="【正式核算与批量任务】"/>
+        <s v="【结果台账与追溯】"/>
+        <s v="【百万级性能优化】"/>
+        <s v="【监控告警与通知】"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="备注" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="建立产品重构新基线"/>
+        <s v="完成独立仓库、品牌文案、导航精简"/>
+        <s v="首页切换为企业级成本核算驾驶舱"/>
+        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
+        <s v="形成完整建表语句、ER图、页面原型"/>
+        <s v="将模板转为当前项目进展、测试、计划台账"/>
+        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
+        <s v="独立系统字典并接入业务域下拉和筛选"/>
+        <s v="恢复场景台账、表单、筛选、治理入口"/>
+        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
+        <s v="恢复字典型、接口型、公式型变量工作台"/>
+        <s v="实现费用主线规则台账与条件编辑"/>
+        <s v="显式阶梯依据变量、区间规则、命中解释"/>
+        <s v="恢复场景发布、版本快照和费用级差异视图"/>
+        <s v="恢复发布说明、校验、版本台账、生效切换"/>
+        <s v="支持场景总览差异和费用级差异筛选"/>
+        <s v="恢复变量、费用、规则删除前实时预检查"/>
+        <s v="补齐版本详情、回滚、发布审计链路"/>
+        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
+        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
+        <s v="恢复按发布快照执行的单笔与批量核算"/>
+        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
+        <s v="批量分片、异步执行、索引与缓存优化"/>
+        <s v="恢复任务告警、失败订阅和通知治理"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="负责人" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="GitFhw"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="状态" numFmtId="0">
+      <sharedItems containsBlank="1" count="24">
+        <m/>
+        <s v="已完成 ❇️"/>
+        <s v="进行中 🚀"/>
+        <s v="未开始 ⏳"/>
+        <s v="开发完成👌" u="1"/>
+        <s v="已延期 💥" u="1"/>
+        <s v="进行中 🔛" u="1"/>
+        <s v="使用下拉列表显示任务状态" u="1"/>
+        <s v="待启动 💡" u="1"/>
+        <s v="李光军" u="1"/>
+        <s v="张永菲" u="1"/>
+        <s v="林凤晟" u="1"/>
+        <s v="刘瀚远" u="1"/>
+        <s v="矫淑宏" u="1"/>
+        <s v="孙佳明" u="1"/>
+        <s v="孙启明" u="1"/>
+        <s v="李斌" u="1"/>
+        <s v="苏浩南" u="1"/>
+        <s v="王昌泽" u="1"/>
+        <s v="胡兆稳" u="1"/>
+        <s v="宁文龙" u="1"/>
+        <s v="吴秀晗" u="1"/>
+        <s v="宋成志" u="1"/>
+        <s v="高杰" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-03-31T00:00:00"/>
+        <d v="2026-04-01T00:00:00"/>
+        <d v="2026-04-03T00:00:00"/>
+        <d v="2026-04-08T00:00:00"/>
+        <d v="2026-04-10T00:00:00"/>
+        <d v="2026-04-15T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-24T00:00:00"/>
+        <d v="2026-04-27T00:00:00"/>
+        <d v="2026-05-06T00:00:00"/>
+        <d v="2026-05-10T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-25T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计结束时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-04-21T00:00:00"/>
+        <d v="2026-04-02T00:00:00"/>
+        <d v="2026-04-07T00:00:00"/>
+        <d v="2026-04-09T00:00:00"/>
+        <d v="2026-04-14T00:00:00"/>
+        <d v="2026-04-18T00:00:00"/>
+        <d v="2026-05-08T00:00:00"/>
+        <d v="2026-04-28T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-06-05T00:00:00"/>
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-23T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时预估" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_自然日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="7"/>
+        <n v="9"/>
+        <n v="12"/>
+        <n v="31"/>
+        <n v="11"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_工作日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+        <n v="7"/>
+        <n v="10"/>
+        <n v="23"/>
+        <n v="9"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="完成度_x000a_ %" numFmtId="10">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+        <m/>
+        <n v="1"/>
+        <n v="0.15"/>
+        <n v="0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_开始时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_结束时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="测试人" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl\pivotCache\pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A4:N29" sheet="项目管理"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="任务" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="一、底座与设计基线"/>
+        <s v="【若依底座接入与品牌裁剪】"/>
+        <s v="【首页驾驶舱基线】"/>
+        <s v="【详细设计文档体系】"/>
+        <s v="【完整数据库SQL与ER图】"/>
+        <s v="【需求跟踪矩阵初始化】"/>
+        <s v="二、配置主链恢复"/>
+        <s v="【业务域字典治理】"/>
+        <s v="【场景中心】"/>
+        <s v="【费用中心】"/>
+        <s v="【变量中心】"/>
+        <s v="【规则中心】"/>
+        <s v="【阶梯费率与依据变量】"/>
+        <s v="三、发布与治理恢复"/>
+        <s v="【发布中心】"/>
+        <s v="【版本差异与费用级视图】"/>
+        <s v="【引用校验与删除保护】"/>
+        <s v="【发布审计与回滚】"/>
+        <s v="四、运行链与性能治理"/>
+        <s v="【试算中心】"/>
+        <s v="【正式核算与批量任务】"/>
+        <s v="【结果台账与追溯】"/>
+        <s v="【百万级性能优化】"/>
+        <s v="【监控告警与通知】"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="备注" numFmtId="0">
+      <sharedItems containsBlank="1" count="25">
+        <m/>
+        <s v="建立产品重构新基线"/>
+        <s v="完成独立仓库、品牌文案、导航精简"/>
+        <s v="首页切换为企业级成本核算驾驶舱"/>
+        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
+        <s v="形成完整建表语句、ER图、页面原型"/>
+        <s v="将模板转为当前项目进展、测试、计划台账"/>
+        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
+        <s v="独立系统字典并接入业务域下拉和筛选"/>
+        <s v="恢复场景台账、表单、筛选、治理入口"/>
+        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
+        <s v="恢复字典型、接口型、公式型变量工作台"/>
+        <s v="实现费用主线规则台账与条件编辑"/>
+        <s v="显式阶梯依据变量、区间规则、命中解释"/>
+        <s v="恢复场景发布、版本快照和费用级差异视图"/>
+        <s v="恢复发布说明、校验、版本台账、生效切换"/>
+        <s v="支持场景总览差异和费用级差异筛选"/>
+        <s v="恢复变量、费用、规则删除前实时预检查"/>
+        <s v="补齐版本详情、回滚、发布审计链路"/>
+        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
+        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
+        <s v="恢复按发布快照执行的单笔与批量核算"/>
+        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
+        <s v="批量分片、异步执行、索引与缓存优化"/>
+        <s v="恢复任务告警、失败订阅和通知治理"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="负责人" numFmtId="0">
+      <sharedItems containsBlank="1" count="2">
+        <m/>
+        <s v="GitFhw"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="状态" numFmtId="0">
+      <sharedItems containsBlank="1" count="4">
+        <m/>
+        <s v="已完成 ❇️"/>
+        <s v="进行中 🚀"/>
+        <s v="未开始 ⏳"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-03-31T00:00:00"/>
+        <d v="2026-04-01T00:00:00"/>
+        <d v="2026-04-03T00:00:00"/>
+        <d v="2026-04-08T00:00:00"/>
+        <d v="2026-04-10T00:00:00"/>
+        <d v="2026-04-15T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-24T00:00:00"/>
+        <d v="2026-04-27T00:00:00"/>
+        <d v="2026-05-06T00:00:00"/>
+        <d v="2026-05-10T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-25T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="预计结束时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+        <d v="2026-04-21T00:00:00"/>
+        <d v="2026-04-02T00:00:00"/>
+        <d v="2026-04-07T00:00:00"/>
+        <d v="2026-04-09T00:00:00"/>
+        <d v="2026-04-14T00:00:00"/>
+        <d v="2026-04-18T00:00:00"/>
+        <d v="2026-05-08T00:00:00"/>
+        <d v="2026-04-28T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-06-05T00:00:00"/>
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-20T00:00:00"/>
+        <d v="2026-05-23T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时预估" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_自然日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="7"/>
+        <n v="9"/>
+        <n v="12"/>
+        <n v="31"/>
+        <n v="11"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="工时_x000a_工作日" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
+        <m/>
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+        <n v="7"/>
+        <n v="10"/>
+        <n v="23"/>
+        <n v="9"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="完成度_x000a_ %" numFmtId="10">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+        <m/>
+        <n v="1"/>
+        <n v="0.15"/>
+        <n v="0"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_开始时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="实际_x000a_结束时间" numFmtId="14">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
+        <m/>
+        <d v="2026-03-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="测试人" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="开始时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl\pivotTables\pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
+  <location ref="B24:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0">
+      <items count="26">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="25">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="9"/>
+        <item h="1" m="1" x="10"/>
+        <item h="1" m="1" x="11"/>
+        <item h="1" m="1" x="12"/>
+        <item h="1" m="1" x="13"/>
+        <item h="1" m="1" x="14"/>
+        <item h="1" m="1" x="15"/>
+        <item h="1" m="1" x="16"/>
+        <item h="1" m="1" x="17"/>
+        <item h="1" m="1" x="18"/>
+        <item h="1" m="1" x="19"/>
+        <item h="1" m="1" x="20"/>
+        <item h="1" m="1" x="21"/>
+        <item h="1" m="1" x="22"/>
+        <item h="1" m="1" x="23"/>
+        <item h="1" m="1" x="7"/>
+        <item h="1" x="1"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" m="1" x="8"/>
+        <item h="1" m="1" x="5"/>
+        <item h="1" m="1" x="6"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="计数项:任务" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
   </extLst>
-</workbook>
+</pivotTableDefinition>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\pivotTables\pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table2" cacheId="1" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
+  <location ref="B12:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0">
+      <items count="26">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+  </pivotFields>
+  <dataFields count="1">
+    <dataField name="计数项:任务" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl\pivotTables\pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table3" cacheId="2" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
+  <location ref="E24:F26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0">
+      <items count="26">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="25">
+        <item h="1" x="0"/>
+        <item h="1" m="1" x="9"/>
+        <item h="1" m="1" x="10"/>
+        <item h="1" m="1" x="11"/>
+        <item h="1" m="1" x="12"/>
+        <item h="1" m="1" x="13"/>
+        <item h="1" m="1" x="14"/>
+        <item h="1" m="1" x="15"/>
+        <item h="1" m="1" x="16"/>
+        <item h="1" m="1" x="17"/>
+        <item h="1" m="1" x="18"/>
+        <item h="1" m="1" x="19"/>
+        <item h="1" m="1" x="20"/>
+        <item h="1" m="1" x="21"/>
+        <item h="1" m="1" x="22"/>
+        <item h="1" m="1" x="23"/>
+        <item h="1" m="1" x="7"/>
+        <item h="1" x="1"/>
+        <item h="1" m="1" x="4"/>
+        <item h="1" m="1" x="8"/>
+        <item h="1" m="1" x="5"/>
+        <item h="1" m="1" x="6"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="计数项:任务" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl\pivotTables\pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table4" cacheId="3" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
+  <location ref="E12:F13" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0">
+      <items count="26">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="任务数量统计" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="总工时预估" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="183">
   <si>
     <t>成本核算平台</t>
@@ -663,7 +1893,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -2397,1227 +3627,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="SEFMNF"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10843260" y="95250"/>
-          <a:ext cx="2577465" cy="3097530"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>745490</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 21" descr="XAjxGJ"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9845040" y="213360"/>
-          <a:ext cx="1158240" cy="707390"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>-38100</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 39" descr="avQchw"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9845040" y="920750"/>
-          <a:ext cx="1158240" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A4:N29" sheet="项目管理"/>
-  </cacheSource>
-  <cacheFields count="14">
-    <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="一、底座与设计基线"/>
-        <s v="【若依底座接入与品牌裁剪】"/>
-        <s v="【首页驾驶舱基线】"/>
-        <s v="【详细设计文档体系】"/>
-        <s v="【完整数据库SQL与ER图】"/>
-        <s v="【需求跟踪矩阵初始化】"/>
-        <s v="二、配置主链恢复"/>
-        <s v="【业务域字典治理】"/>
-        <s v="【场景中心】"/>
-        <s v="【费用中心】"/>
-        <s v="【变量中心】"/>
-        <s v="【规则中心】"/>
-        <s v="【阶梯费率与依据变量】"/>
-        <s v="三、发布与治理恢复"/>
-        <s v="【发布中心】"/>
-        <s v="【版本差异与费用级视图】"/>
-        <s v="【引用校验与删除保护】"/>
-        <s v="【发布审计与回滚】"/>
-        <s v="四、运行链与性能治理"/>
-        <s v="【试算中心】"/>
-        <s v="【正式核算与批量任务】"/>
-        <s v="【结果台账与追溯】"/>
-        <s v="【百万级性能优化】"/>
-        <s v="【监控告警与通知】"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="建立产品重构新基线"/>
-        <s v="完成独立仓库、品牌文案、导航精简"/>
-        <s v="首页切换为企业级成本核算驾驶舱"/>
-        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
-        <s v="形成完整建表语句、ER图、页面原型"/>
-        <s v="将模板转为当前项目进展、测试、计划台账"/>
-        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
-        <s v="独立系统字典并接入业务域下拉和筛选"/>
-        <s v="恢复场景台账、表单、筛选、治理入口"/>
-        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
-        <s v="恢复字典型、接口型、公式型变量工作台"/>
-        <s v="实现费用主线规则台账与条件编辑"/>
-        <s v="显式阶梯依据变量、区间规则、命中解释"/>
-        <s v="恢复场景发布、版本快照和费用级差异视图"/>
-        <s v="恢复发布说明、校验、版本台账、生效切换"/>
-        <s v="支持场景总览差异和费用级差异筛选"/>
-        <s v="恢复变量、费用、规则删除前实时预检查"/>
-        <s v="补齐版本详情、回滚、发布审计链路"/>
-        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
-        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
-        <s v="恢复按发布快照执行的单笔与批量核算"/>
-        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
-        <s v="批量分片、异步执行、索引与缓存优化"/>
-        <s v="恢复任务告警、失败订阅和通知治理"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <m/>
-        <s v="GitFhw"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="24">
-        <m/>
-        <s v="已完成 ❇️"/>
-        <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
-        <s v="开发完成👌" u="1"/>
-        <s v="已延期 💥" u="1"/>
-        <s v="进行中 🔛" u="1"/>
-        <s v="使用下拉列表显示任务状态" u="1"/>
-        <s v="待启动 💡" u="1"/>
-        <s v="李光军" u="1"/>
-        <s v="张永菲" u="1"/>
-        <s v="林凤晟" u="1"/>
-        <s v="刘瀚远" u="1"/>
-        <s v="矫淑宏" u="1"/>
-        <s v="孙佳明" u="1"/>
-        <s v="孙启明" u="1"/>
-        <s v="李斌" u="1"/>
-        <s v="苏浩南" u="1"/>
-        <s v="王昌泽" u="1"/>
-        <s v="胡兆稳" u="1"/>
-        <s v="宁文龙" u="1"/>
-        <s v="吴秀晗" u="1"/>
-        <s v="宋成志" u="1"/>
-        <s v="高杰" u="1"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-03-31T00:00:00"/>
-        <d v="2026-04-01T00:00:00"/>
-        <d v="2026-04-03T00:00:00"/>
-        <d v="2026-04-08T00:00:00"/>
-        <d v="2026-04-10T00:00:00"/>
-        <d v="2026-04-15T00:00:00"/>
-        <d v="2026-04-22T00:00:00"/>
-        <d v="2026-04-24T00:00:00"/>
-        <d v="2026-04-27T00:00:00"/>
-        <d v="2026-05-06T00:00:00"/>
-        <d v="2026-05-10T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-25T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-04-21T00:00:00"/>
-        <d v="2026-04-02T00:00:00"/>
-        <d v="2026-04-07T00:00:00"/>
-        <d v="2026-04-09T00:00:00"/>
-        <d v="2026-04-14T00:00:00"/>
-        <d v="2026-04-18T00:00:00"/>
-        <d v="2026-05-08T00:00:00"/>
-        <d v="2026-04-28T00:00:00"/>
-        <d v="2026-04-30T00:00:00"/>
-        <d v="2026-06-05T00:00:00"/>
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-23T00:00:00"/>
-        <d v="2026-05-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="7"/>
-        <n v="9"/>
-        <n v="12"/>
-        <n v="31"/>
-        <n v="11"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="5"/>
-        <n v="7"/>
-        <n v="10"/>
-        <n v="23"/>
-        <n v="9"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
-        <m/>
-        <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A4:N29" sheet="项目管理"/>
-  </cacheSource>
-  <cacheFields count="14">
-    <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="一、底座与设计基线"/>
-        <s v="【若依底座接入与品牌裁剪】"/>
-        <s v="【首页驾驶舱基线】"/>
-        <s v="【详细设计文档体系】"/>
-        <s v="【完整数据库SQL与ER图】"/>
-        <s v="【需求跟踪矩阵初始化】"/>
-        <s v="二、配置主链恢复"/>
-        <s v="【业务域字典治理】"/>
-        <s v="【场景中心】"/>
-        <s v="【费用中心】"/>
-        <s v="【变量中心】"/>
-        <s v="【规则中心】"/>
-        <s v="【阶梯费率与依据变量】"/>
-        <s v="三、发布与治理恢复"/>
-        <s v="【发布中心】"/>
-        <s v="【版本差异与费用级视图】"/>
-        <s v="【引用校验与删除保护】"/>
-        <s v="【发布审计与回滚】"/>
-        <s v="四、运行链与性能治理"/>
-        <s v="【试算中心】"/>
-        <s v="【正式核算与批量任务】"/>
-        <s v="【结果台账与追溯】"/>
-        <s v="【百万级性能优化】"/>
-        <s v="【监控告警与通知】"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="建立产品重构新基线"/>
-        <s v="完成独立仓库、品牌文案、导航精简"/>
-        <s v="首页切换为企业级成本核算驾驶舱"/>
-        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
-        <s v="形成完整建表语句、ER图、页面原型"/>
-        <s v="将模板转为当前项目进展、测试、计划台账"/>
-        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
-        <s v="独立系统字典并接入业务域下拉和筛选"/>
-        <s v="恢复场景台账、表单、筛选、治理入口"/>
-        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
-        <s v="恢复字典型、接口型、公式型变量工作台"/>
-        <s v="实现费用主线规则台账与条件编辑"/>
-        <s v="显式阶梯依据变量、区间规则、命中解释"/>
-        <s v="恢复场景发布、版本快照和费用级差异视图"/>
-        <s v="恢复发布说明、校验、版本台账、生效切换"/>
-        <s v="支持场景总览差异和费用级差异筛选"/>
-        <s v="恢复变量、费用、规则删除前实时预检查"/>
-        <s v="补齐版本详情、回滚、发布审计链路"/>
-        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
-        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
-        <s v="恢复按发布快照执行的单笔与批量核算"/>
-        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
-        <s v="批量分片、异步执行、索引与缓存优化"/>
-        <s v="恢复任务告警、失败订阅和通知治理"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <m/>
-        <s v="GitFhw"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
-        <m/>
-        <s v="已完成 ❇️"/>
-        <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-03-31T00:00:00"/>
-        <d v="2026-04-01T00:00:00"/>
-        <d v="2026-04-03T00:00:00"/>
-        <d v="2026-04-08T00:00:00"/>
-        <d v="2026-04-10T00:00:00"/>
-        <d v="2026-04-15T00:00:00"/>
-        <d v="2026-04-22T00:00:00"/>
-        <d v="2026-04-24T00:00:00"/>
-        <d v="2026-04-27T00:00:00"/>
-        <d v="2026-05-06T00:00:00"/>
-        <d v="2026-05-10T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-25T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-04-21T00:00:00"/>
-        <d v="2026-04-02T00:00:00"/>
-        <d v="2026-04-07T00:00:00"/>
-        <d v="2026-04-09T00:00:00"/>
-        <d v="2026-04-14T00:00:00"/>
-        <d v="2026-04-18T00:00:00"/>
-        <d v="2026-05-08T00:00:00"/>
-        <d v="2026-04-28T00:00:00"/>
-        <d v="2026-04-30T00:00:00"/>
-        <d v="2026-06-05T00:00:00"/>
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-23T00:00:00"/>
-        <d v="2026-05-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="7"/>
-        <n v="9"/>
-        <n v="12"/>
-        <n v="31"/>
-        <n v="11"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="5"/>
-        <n v="7"/>
-        <n v="10"/>
-        <n v="23"/>
-        <n v="9"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
-        <m/>
-        <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A4:N29" sheet="项目管理"/>
-  </cacheSource>
-  <cacheFields count="14">
-    <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="一、底座与设计基线"/>
-        <s v="【若依底座接入与品牌裁剪】"/>
-        <s v="【首页驾驶舱基线】"/>
-        <s v="【详细设计文档体系】"/>
-        <s v="【完整数据库SQL与ER图】"/>
-        <s v="【需求跟踪矩阵初始化】"/>
-        <s v="二、配置主链恢复"/>
-        <s v="【业务域字典治理】"/>
-        <s v="【场景中心】"/>
-        <s v="【费用中心】"/>
-        <s v="【变量中心】"/>
-        <s v="【规则中心】"/>
-        <s v="【阶梯费率与依据变量】"/>
-        <s v="三、发布与治理恢复"/>
-        <s v="【发布中心】"/>
-        <s v="【版本差异与费用级视图】"/>
-        <s v="【引用校验与删除保护】"/>
-        <s v="【发布审计与回滚】"/>
-        <s v="四、运行链与性能治理"/>
-        <s v="【试算中心】"/>
-        <s v="【正式核算与批量任务】"/>
-        <s v="【结果台账与追溯】"/>
-        <s v="【百万级性能优化】"/>
-        <s v="【监控告警与通知】"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="建立产品重构新基线"/>
-        <s v="完成独立仓库、品牌文案、导航精简"/>
-        <s v="首页切换为企业级成本核算驾驶舱"/>
-        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
-        <s v="形成完整建表语句、ER图、页面原型"/>
-        <s v="将模板转为当前项目进展、测试、计划台账"/>
-        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
-        <s v="独立系统字典并接入业务域下拉和筛选"/>
-        <s v="恢复场景台账、表单、筛选、治理入口"/>
-        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
-        <s v="恢复字典型、接口型、公式型变量工作台"/>
-        <s v="实现费用主线规则台账与条件编辑"/>
-        <s v="显式阶梯依据变量、区间规则、命中解释"/>
-        <s v="恢复场景发布、版本快照和费用级差异视图"/>
-        <s v="恢复发布说明、校验、版本台账、生效切换"/>
-        <s v="支持场景总览差异和费用级差异筛选"/>
-        <s v="恢复变量、费用、规则删除前实时预检查"/>
-        <s v="补齐版本详情、回滚、发布审计链路"/>
-        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
-        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
-        <s v="恢复按发布快照执行的单笔与批量核算"/>
-        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
-        <s v="批量分片、异步执行、索引与缓存优化"/>
-        <s v="恢复任务告警、失败订阅和通知治理"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <m/>
-        <s v="GitFhw"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="24">
-        <m/>
-        <s v="已完成 ❇️"/>
-        <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
-        <s v="开发完成👌" u="1"/>
-        <s v="已延期 💥" u="1"/>
-        <s v="进行中 🔛" u="1"/>
-        <s v="使用下拉列表显示任务状态" u="1"/>
-        <s v="待启动 💡" u="1"/>
-        <s v="李光军" u="1"/>
-        <s v="张永菲" u="1"/>
-        <s v="林凤晟" u="1"/>
-        <s v="刘瀚远" u="1"/>
-        <s v="矫淑宏" u="1"/>
-        <s v="孙佳明" u="1"/>
-        <s v="孙启明" u="1"/>
-        <s v="李斌" u="1"/>
-        <s v="苏浩南" u="1"/>
-        <s v="王昌泽" u="1"/>
-        <s v="胡兆稳" u="1"/>
-        <s v="宁文龙" u="1"/>
-        <s v="吴秀晗" u="1"/>
-        <s v="宋成志" u="1"/>
-        <s v="高杰" u="1"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-03-31T00:00:00"/>
-        <d v="2026-04-01T00:00:00"/>
-        <d v="2026-04-03T00:00:00"/>
-        <d v="2026-04-08T00:00:00"/>
-        <d v="2026-04-10T00:00:00"/>
-        <d v="2026-04-15T00:00:00"/>
-        <d v="2026-04-22T00:00:00"/>
-        <d v="2026-04-24T00:00:00"/>
-        <d v="2026-04-27T00:00:00"/>
-        <d v="2026-05-06T00:00:00"/>
-        <d v="2026-05-10T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-25T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-04-21T00:00:00"/>
-        <d v="2026-04-02T00:00:00"/>
-        <d v="2026-04-07T00:00:00"/>
-        <d v="2026-04-09T00:00:00"/>
-        <d v="2026-04-14T00:00:00"/>
-        <d v="2026-04-18T00:00:00"/>
-        <d v="2026-05-08T00:00:00"/>
-        <d v="2026-04-28T00:00:00"/>
-        <d v="2026-04-30T00:00:00"/>
-        <d v="2026-06-05T00:00:00"/>
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-23T00:00:00"/>
-        <d v="2026-05-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="7"/>
-        <n v="9"/>
-        <n v="12"/>
-        <n v="31"/>
-        <n v="11"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="5"/>
-        <n v="7"/>
-        <n v="10"/>
-        <n v="23"/>
-        <n v="9"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
-        <m/>
-        <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A4:N29" sheet="项目管理"/>
-  </cacheSource>
-  <cacheFields count="14">
-    <cacheField name="任务" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="一、底座与设计基线"/>
-        <s v="【若依底座接入与品牌裁剪】"/>
-        <s v="【首页驾驶舱基线】"/>
-        <s v="【详细设计文档体系】"/>
-        <s v="【完整数据库SQL与ER图】"/>
-        <s v="【需求跟踪矩阵初始化】"/>
-        <s v="二、配置主链恢复"/>
-        <s v="【业务域字典治理】"/>
-        <s v="【场景中心】"/>
-        <s v="【费用中心】"/>
-        <s v="【变量中心】"/>
-        <s v="【规则中心】"/>
-        <s v="【阶梯费率与依据变量】"/>
-        <s v="三、发布与治理恢复"/>
-        <s v="【发布中心】"/>
-        <s v="【版本差异与费用级视图】"/>
-        <s v="【引用校验与删除保护】"/>
-        <s v="【发布审计与回滚】"/>
-        <s v="四、运行链与性能治理"/>
-        <s v="【试算中心】"/>
-        <s v="【正式核算与批量任务】"/>
-        <s v="【结果台账与追溯】"/>
-        <s v="【百万级性能优化】"/>
-        <s v="【监控告警与通知】"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="备注" numFmtId="0">
-      <sharedItems containsBlank="1" count="25">
-        <m/>
-        <s v="建立产品重构新基线"/>
-        <s v="完成独立仓库、品牌文案、导航精简"/>
-        <s v="首页切换为企业级成本核算驾驶舱"/>
-        <s v="补齐详细设计、缓存规范、验证规范、首页裁剪设计"/>
-        <s v="形成完整建表语句、ER图、页面原型"/>
-        <s v="将模板转为当前项目进展、测试、计划台账"/>
-        <s v="按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进"/>
-        <s v="独立系统字典并接入业务域下拉和筛选"/>
-        <s v="恢复场景台账、表单、筛选、治理入口"/>
-        <s v="恢复费用主数据、场景联动、影响因素摘要"/>
-        <s v="恢复字典型、接口型、公式型变量工作台"/>
-        <s v="实现费用主线规则台账与条件编辑"/>
-        <s v="显式阶梯依据变量、区间规则、命中解释"/>
-        <s v="恢复场景发布、版本快照和费用级差异视图"/>
-        <s v="恢复发布说明、校验、版本台账、生效切换"/>
-        <s v="支持场景总览差异和费用级差异筛选"/>
-        <s v="恢复变量、费用、规则删除前实时预检查"/>
-        <s v="补齐版本详情、回滚、发布审计链路"/>
-        <s v="恢复试算、正式核算、批量任务与百万级性能治理"/>
-        <s v="恢复试算、执行步骤时间线、单价来源解释"/>
-        <s v="恢复按发布快照执行的单笔与批量核算"/>
-        <s v="恢复独立结果台账、规则命中与阶梯解释"/>
-        <s v="批量分片、异步执行、索引与缓存优化"/>
-        <s v="恢复任务告警、失败订阅和通知治理"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="负责人" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <m/>
-        <s v="GitFhw"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
-        <m/>
-        <s v="已完成 ❇️"/>
-        <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-05-25T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-03-31T00:00:00"/>
-        <d v="2026-04-01T00:00:00"/>
-        <d v="2026-04-03T00:00:00"/>
-        <d v="2026-04-08T00:00:00"/>
-        <d v="2026-04-10T00:00:00"/>
-        <d v="2026-04-15T00:00:00"/>
-        <d v="2026-04-22T00:00:00"/>
-        <d v="2026-04-24T00:00:00"/>
-        <d v="2026-04-27T00:00:00"/>
-        <d v="2026-05-06T00:00:00"/>
-        <d v="2026-05-10T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-25T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="预计结束时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-06-05T00:00:00" count="16">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-        <d v="2026-04-21T00:00:00"/>
-        <d v="2026-04-02T00:00:00"/>
-        <d v="2026-04-07T00:00:00"/>
-        <d v="2026-04-09T00:00:00"/>
-        <d v="2026-04-14T00:00:00"/>
-        <d v="2026-04-18T00:00:00"/>
-        <d v="2026-05-08T00:00:00"/>
-        <d v="2026-04-28T00:00:00"/>
-        <d v="2026-04-30T00:00:00"/>
-        <d v="2026-06-05T00:00:00"/>
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-20T00:00:00"/>
-        <d v="2026-05-23T00:00:00"/>
-        <d v="2026-05-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时预估" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_自然日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="31" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="7"/>
-        <n v="9"/>
-        <n v="12"/>
-        <n v="31"/>
-        <n v="11"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="工时_x000a_工作日" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="23" count="8">
-        <m/>
-        <n v="1"/>
-        <n v="3"/>
-        <n v="5"/>
-        <n v="7"/>
-        <n v="10"/>
-        <n v="23"/>
-        <n v="9"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
-        <m/>
-        <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_开始时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="实际_x000a_结束时间" numFmtId="14">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" containsDate="1" minDate="2026-03-30T00:00:00" maxDate="2026-03-30T00:00:00" count="2">
-        <m/>
-        <d v="2026-03-30T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="测试人" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="开始时间" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNonDate="0" count="1">
-        <m/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
-  <location ref="B24:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="26">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="25">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="9"/>
-        <item h="1" m="1" x="10"/>
-        <item h="1" m="1" x="11"/>
-        <item h="1" m="1" x="12"/>
-        <item h="1" m="1" x="13"/>
-        <item h="1" m="1" x="14"/>
-        <item h="1" m="1" x="15"/>
-        <item h="1" m="1" x="16"/>
-        <item h="1" m="1" x="17"/>
-        <item h="1" m="1" x="18"/>
-        <item h="1" m="1" x="19"/>
-        <item h="1" m="1" x="20"/>
-        <item h="1" m="1" x="21"/>
-        <item h="1" m="1" x="22"/>
-        <item h="1" m="1" x="23"/>
-        <item h="1" m="1" x="7"/>
-        <item h="1" x="1"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" m="1" x="8"/>
-        <item h="1" m="1" x="5"/>
-        <item h="1" m="1" x="6"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="1">
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="计数项:任务" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table2" cacheId="1" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
-  <location ref="B12:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="26">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-  </pivotFields>
-  <dataFields count="1">
-    <dataField name="计数项:任务" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table3" cacheId="2" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
-  <location ref="E24:F26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="26">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="25">
-        <item h="1" x="0"/>
-        <item h="1" m="1" x="9"/>
-        <item h="1" m="1" x="10"/>
-        <item h="1" m="1" x="11"/>
-        <item h="1" m="1" x="12"/>
-        <item h="1" m="1" x="13"/>
-        <item h="1" m="1" x="14"/>
-        <item h="1" m="1" x="15"/>
-        <item h="1" m="1" x="16"/>
-        <item h="1" m="1" x="17"/>
-        <item h="1" m="1" x="18"/>
-        <item h="1" m="1" x="19"/>
-        <item h="1" m="1" x="20"/>
-        <item h="1" m="1" x="21"/>
-        <item h="1" m="1" x="22"/>
-        <item h="1" m="1" x="23"/>
-        <item h="1" m="1" x="7"/>
-        <item h="1" x="1"/>
-        <item h="1" m="1" x="4"/>
-        <item h="1" m="1" x="8"/>
-        <item h="1" m="1" x="5"/>
-        <item h="1" m="1" x="6"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="3"/>
-  </colFields>
-  <colItems count="1">
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="计数项:任务" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot Table4" cacheId="3" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" createdVersion="3" useAutoFormatting="1" compact="0" compactData="0" showDrill="1">
-  <location ref="E12:F13" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="26">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="任务数量统计" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="总工时预估" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -3872,7 +3882,45 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
+  </bookViews>
+  <sheets>
+    <sheet name="项目管理" sheetId="2" r:id="rId1"/>
+    <sheet name="项目进展分析" sheetId="3" r:id="rId2"/>
+    <sheet name="项目甘特图" sheetId="4" r:id="rId3"/>
+    <sheet name="使用说明" sheetId="5" r:id="rId4"/>
+    <sheet name="节假日一览表" sheetId="6" r:id="rId5"/>
+    <sheet name="测试问题及整改记录" sheetId="7" r:id="rId6"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="2" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId10"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6112,8 +6160,10 @@
       <c r="C12" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="119" t="s">
-        <v>42</v>
+      <c r="D12" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E12" s="104">
         <v>46112</v>
@@ -6125,7 +6175,7 @@
       <c r="H12" s="106"/>
       <c r="I12" s="106"/>
       <c r="J12" s="107">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="K12" s="104"/>
       <c r="L12" s="104"/>
@@ -6210,8 +6260,10 @@
       <c r="C13" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="119" t="s">
-        <v>45</v>
+      <c r="D13" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E13" s="104">
         <v>46112</v>
@@ -6227,7 +6279,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="104"/>
       <c r="L13" s="104"/>
@@ -6312,8 +6364,10 @@
       <c r="C14" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="119" t="s">
-        <v>45</v>
+      <c r="D14" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E14" s="104">
         <v>46113</v>
@@ -6329,7 +6383,7 @@
         <v>5</v>
       </c>
       <c r="J14" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="104"/>
       <c r="L14" s="104"/>
@@ -6414,8 +6468,10 @@
       <c r="C15" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="119" t="s">
-        <v>45</v>
+      <c r="D15" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E15" s="104">
         <v>46115</v>
@@ -6431,7 +6487,7 @@
         <v>5</v>
       </c>
       <c r="J15" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="104"/>
       <c r="L15" s="104"/>
@@ -6516,8 +6572,10 @@
       <c r="C16" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="119" t="s">
-        <v>29</v>
+      <c r="D16" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E16" s="104">
         <v>46120</v>
@@ -6533,7 +6591,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="104"/>
       <c r="L16" s="104"/>
@@ -6618,8 +6676,10 @@
       <c r="C17" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="119" t="s">
-        <v>45</v>
+      <c r="D17" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E17" s="104">
         <v>46122</v>
@@ -6635,7 +6695,7 @@
         <v>7</v>
       </c>
       <c r="J17" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="104"/>
       <c r="L17" s="104"/>
@@ -6720,8 +6780,10 @@
       <c r="C18" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="119" t="s">
-        <v>45</v>
+      <c r="D18" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E18" s="104">
         <v>46127</v>
@@ -6737,7 +6799,7 @@
         <v>5</v>
       </c>
       <c r="J18" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="104"/>
       <c r="L18" s="104"/>
@@ -6822,8 +6884,10 @@
       <c r="C19" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="119" t="s">
-        <v>45</v>
+      <c r="D19" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E19" s="104">
         <v>46134</v>
@@ -6835,7 +6899,7 @@
       <c r="H19" s="106"/>
       <c r="I19" s="106"/>
       <c r="J19" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="104"/>
@@ -6920,8 +6984,10 @@
       <c r="C20" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="119" t="s">
-        <v>45</v>
+      <c r="D20" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E20" s="104">
         <v>46134</v>
@@ -6937,7 +7003,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="104"/>
       <c r="L20" s="104"/>
@@ -7022,8 +7088,10 @@
       <c r="C21" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="119" t="s">
-        <v>45</v>
+      <c r="D21" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E21" s="104">
         <v>46134</v>
@@ -7039,7 +7107,7 @@
         <v>7</v>
       </c>
       <c r="J21" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="104"/>
       <c r="L21" s="104"/>
@@ -7124,8 +7192,10 @@
       <c r="C22" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="119" t="s">
-        <v>45</v>
+      <c r="D22" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E22" s="104">
         <v>46136</v>
@@ -7141,7 +7211,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="104"/>
       <c r="L22" s="104"/>
@@ -7226,8 +7296,10 @@
       <c r="C23" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="119" t="s">
-        <v>45</v>
+      <c r="D23" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E23" s="104">
         <v>46139</v>
@@ -7243,7 +7315,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="104"/>
       <c r="L23" s="104"/>
@@ -7328,8 +7400,10 @@
       <c r="C24" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="119" t="s">
-        <v>45</v>
+      <c r="D24" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
       </c>
       <c r="E24" s="104">
         <v>46148</v>
@@ -7345,7 +7419,7 @@
         <v>23</v>
       </c>
       <c r="J24" s="107">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K24" s="104"/>
       <c r="L24" s="104"/>
@@ -7430,8 +7504,10 @@
       <c r="C25" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="119" t="s">
-        <v>45</v>
+      <c r="D25" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
       </c>
       <c r="E25" s="104">
         <v>46148</v>
@@ -7447,7 +7523,7 @@
         <v>5</v>
       </c>
       <c r="J25" s="107">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="K25" s="104"/>
       <c r="L25" s="104"/>
@@ -7532,8 +7608,10 @@
       <c r="C26" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="119" t="s">
-        <v>45</v>
+      <c r="D26" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E26" s="104">
         <v>46152</v>
@@ -7549,7 +7627,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="104"/>
       <c r="L26" s="104"/>
@@ -7634,8 +7712,10 @@
       <c r="C27" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="119" t="s">
-        <v>45</v>
+      <c r="D27" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
       </c>
       <c r="E27" s="104">
         <v>46157</v>
@@ -7651,7 +7731,7 @@
         <v>7</v>
       </c>
       <c r="J27" s="107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="104"/>
       <c r="L27" s="104"/>
@@ -7736,8 +7816,10 @@
       <c r="C28" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="115" t="s">
-        <v>45</v>
+      <c r="D28" s="115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
       </c>
       <c r="E28" s="116">
         <v>46162</v>
@@ -7753,7 +7835,7 @@
         <v>9</v>
       </c>
       <c r="J28" s="126">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="K28" s="116"/>
       <c r="L28" s="116"/>
@@ -7892,8 +7974,10 @@
       <c r="C29" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="119" t="s">
-        <v>45</v>
+      <c r="D29" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
       </c>
       <c r="E29" s="104">
         <v>46167</v>
@@ -7909,7 +7993,7 @@
         <v>10</v>
       </c>
       <c r="J29" s="107">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="K29" s="104"/>
       <c r="L29" s="104"/>
@@ -7985,16 +8069,38 @@
       <c r="CD29" s="15"/>
     </row>
     <row r="30" spans="1:136">
-      <c r="A30" s="19"/>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="104"/>
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五、公式实验室与表达式资产化</t>
+        </is>
+      </c>
+      <c r="B30" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">恢复公式工作台、公式编码和表达式资产治理</t>
+        </is>
+      </c>
+      <c r="C30" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="D30" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
+      </c>
+      <c r="E30" s="104">
+        <v>46111</v>
+      </c>
+      <c r="F30" s="104">
+        <v>46125</v>
+      </c>
       <c r="G30" s="105"/>
       <c r="H30" s="106"/>
       <c r="I30" s="106"/>
-      <c r="J30" s="107"/>
+      <c r="J30" s="107">
+        <v>0.72</v>
+      </c>
       <c r="K30" s="104"/>
       <c r="L30" s="104"/>
       <c r="M30" s="104"/>
@@ -8069,16 +8175,38 @@
       <c r="CD30" s="15"/>
     </row>
     <row r="31" spans="1:136">
-      <c r="A31" s="19"/>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【公式实验室工作台】</t>
+        </is>
+      </c>
+      <c r="B31" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">支持业务人员点选变量、条件、模板生成中文公式与标准表达式</t>
+        </is>
+      </c>
+      <c r="C31" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="D31" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成 ❇️</t>
+        </is>
+      </c>
+      <c r="E31" s="104">
+        <v>46111</v>
+      </c>
+      <c r="F31" s="104">
+        <v>46112</v>
+      </c>
       <c r="G31" s="105"/>
       <c r="H31" s="106"/>
       <c r="I31" s="106"/>
-      <c r="J31" s="107"/>
+      <c r="J31" s="107">
+        <v>1</v>
+      </c>
       <c r="K31" s="104"/>
       <c r="L31" s="104"/>
       <c r="M31" s="104"/>
@@ -8153,16 +8281,38 @@
       <c r="CD31" s="15"/>
     </row>
     <row r="32" spans="1:136">
-      <c r="A32" s="19"/>
-      <c r="B32" s="127"/>
-      <c r="C32" s="127"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【公式编码接入变量/规则/发布/运行】</t>
+        </is>
+      </c>
+      <c r="B32" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量、规则、发布快照、运行链支持公式编码优先执行</t>
+        </is>
+      </c>
+      <c r="C32" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="D32" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
+      </c>
+      <c r="E32" s="104">
+        <v>46111</v>
+      </c>
+      <c r="F32" s="104">
+        <v>46116</v>
+      </c>
       <c r="G32" s="105"/>
       <c r="H32" s="106"/>
       <c r="I32" s="106"/>
-      <c r="J32" s="107"/>
+      <c r="J32" s="107">
+        <v>0.8</v>
+      </c>
       <c r="K32" s="104"/>
       <c r="L32" s="104"/>
       <c r="M32" s="104"/>
@@ -8237,16 +8387,38 @@
       <c r="CD32" s="15"/>
     </row>
     <row r="33" spans="1:82">
-      <c r="A33" s="19"/>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【工作台点选配置持久化】</t>
+        </is>
+      </c>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">补齐 builder 配置保存与二次编辑还原</t>
+        </is>
+      </c>
+      <c r="C33" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="D33" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
+      </c>
+      <c r="E33" s="104">
+        <v>46112</v>
+      </c>
+      <c r="F33" s="104">
+        <v>46120</v>
+      </c>
       <c r="G33" s="105"/>
       <c r="H33" s="106"/>
       <c r="I33" s="106"/>
-      <c r="J33" s="107"/>
+      <c r="J33" s="107">
+        <v>0.35</v>
+      </c>
       <c r="K33" s="104"/>
       <c r="L33" s="104"/>
       <c r="M33" s="104"/>
@@ -8321,16 +8493,38 @@
       <c r="CD33" s="15"/>
     </row>
     <row r="34" spans="1:82">
-      <c r="A34" s="19"/>
-      <c r="B34" s="127"/>
-      <c r="C34" s="127"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="104"/>
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【公式版本管理与模板库】</t>
+        </is>
+      </c>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">补齐公式版本台账、模板库和长期演进治理</t>
+        </is>
+      </c>
+      <c r="C34" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="D34" s="119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 🚀</t>
+        </is>
+      </c>
+      <c r="E34" s="104">
+        <v>46113</v>
+      </c>
+      <c r="F34" s="104">
+        <v>46125</v>
+      </c>
       <c r="G34" s="105"/>
       <c r="H34" s="106"/>
       <c r="I34" s="106"/>
-      <c r="J34" s="107"/>
+      <c r="J34" s="107">
+        <v>0.25</v>
+      </c>
       <c r="K34" s="104"/>
       <c r="L34" s="104"/>
       <c r="M34" s="104"/>
@@ -22231,7 +22425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -37877,7 +38071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -38296,7 +38490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -39031,7 +39225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -43520,12 +43714,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="13.2" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -43734,6 +43928,996 @@
       </c>
       <c r="L5" s="13">
         <v>46111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>46111</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全局体验治理</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全局场景控制</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">缺少可选全局场景上下文，跨页面频繁重复按场景筛选，建议支持用户选中一个场景后其他页面默认按该场景过滤，未选时维持各页面自身分页查询。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">设计优化</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分完成：公式实验室、试算中心、正式核算已支持记住最近场景，其他中心页面待继续接入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>46111</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">场景中心</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">适用组织选择</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">适用组织建议改为系统部门/组织树下拉，避免手输组织编码，与企业组织口径保持一致。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优化</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已登记，待结合系统部门接口和场景模型收口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>46111</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">场景中心</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发布治理摘要</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">场景中心当前仍需补齐更完整的发布资格、最近校验、最近告警和试算提醒表达，并去掉开发过程文案。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优化</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分完成：场景中心与发布中心已补一轮发布治理摘要，仍需结合真实业务数据继续产品化联调。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>46111</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">费用中心</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">计价单位语义</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">计价单位当前更多停留在主数据字段，尚未充分影响计量变量选择提示、规则配置语义和结果解释，需要继续产品化。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">设计缺口</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已登记，待结合费用、规则、结果解释链统一补强。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>46111</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量中心</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字典类型口径</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字典变量的字典类型仍需统一支持系统字典/核算字典下拉选择；第三方变量则继续按来源系统和字段映射建模，不走手填口径。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优化</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已登记，后续与变量中心产品化整改一起处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>46111</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规则中心</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">组合费率与按组变量</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">复杂计费场景下仍缺少按组变量、费率矩阵或组合命中能力，容易出现规则爆炸，需参考业务维护体验继续抽象。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">设计缺口</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已登记，后续在线程三后续深化与公式/矩阵能力中处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>46111</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试算中心</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">动态输入模板</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试算与正式核算输入模板尚未完全按已配置变量和命名空间自动生成，业务仍容易误解场景输入口径。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">设计缺口</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成：试算中心和正式核算已按发布快照、变量配置与命名空间路径自动生成输入模板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>46111</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全页面</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卡片与文案产品化</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多个页面卡片和提示仍需持续清理开发过程文案，统一成企业级成本核算平台的正式产品表达。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优化</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成首轮整改：主要成本页面已替换线程/步骤类文案，后续仍需逐页联调微调。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>46111</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量中心</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第三方接入变量执行链</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第三方接入变量虽已形成正式配置模型，但真实执行链仍为轻量实现，未接真实第三方调用、密钥托管、同步任务、失败重试和告警。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，建议在线程二/五/六联动收口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>46111</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量中心</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">页面能力与数据接入治理</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量中心虽已补导入、复制、共享模板，但距离独立数据接入与导入中心仍有差距，详设能力尚未完全闭环。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，待后续数据接入中心能力补齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>46111</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量中心</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">共享影响因素模板</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">共享影响因素模板当前为内置模板库，尚未形成正式模板台账、发布和审计能力。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，当前线程先保持内置模板策略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>46111</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规则中心</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式构建器</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规则中心当前公式构建器仍为轻量助手，复杂公式依然偏依赖手工表达式维护。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，后续继续与公式实验室复用收口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>46111</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规则中心</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阶梯命中预演</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阶梯命中预演未独立落地，业务仍需借助试算或运行链验证命中档位。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，计划在线程五联调增强中补齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>46111</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">试算中心</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">批量试算</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">批量试算仍缺失，线程五尚未达到完整运行链验收标准。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，待线程五后续收口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>46111</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">运行链</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输入模板命名空间</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">运行链输入模板未按变量配置与命名空间生成，与 V/C/I/F/T 上下文口径仍存在偏差。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成：运行链输入模板已统一按变量元数据、dataPath 和发布快照生成，风险转为关闭记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>46111</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">告警治理</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通知中心与自动恢复</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">告警中心未接外部通知渠道与自动化恢复，只能台账查看和人工处理。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，计划在线程六持续完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>46111</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">性能治理</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分布式与大数据量治理</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">运行链当前仍为单机线程池与轻量 Redis 缓存，未完成分布式调度、锁控制和大数据量压测闭环。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，计划在线程六持续完善。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>46111</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式实验室</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式版本管理与模板库</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式实验室当前未落独立版本管理与模板库，难以支撑长期演进、历史回看与跨场景复用。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，建议归属线程八到线程九之间补齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>46111</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式实验室</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式编码全链收口</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量、规则、运行链尚未全链强制只按 formulaCode 执行，仍保留原始表达式兼容兜底。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，建议归属线程八继续收口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>46111</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式实验室</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作台配置持久化</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作台点选配置当前未持久化，二次编辑不能完整恢复点选过程。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风险</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已同步 docs/风险清单，建议线程七继续整改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>46111</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公式实验室</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变量下拉数据</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当前用户反馈公式实验室存在“变量下拉没数据”问题，需要结合场景选择和数据加载链路尽快回归复核。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">缺陷</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成：已修复新建/编辑公式时场景丢失导致变量下拉为空的问题，并补齐场景记忆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitFhw</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>46111</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发布中心</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发布前检查与生成版本</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发布前检查与生成版本按钮在真实数据下仍需继续复核提示完整性和稳定性，避免业务看不懂或误判。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">待验证</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已登记为持续验证项，后续结合发布联调继续回归。</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/成本核算平台需求跟踪矩阵.xlsx
+++ b/成本核算平台需求跟踪矩阵.xlsx
@@ -29,7 +29,7 @@
 <cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
   <cp:lastModifiedBy>范皓为</cp:lastModifiedBy>
   <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-30T06:31:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-30T09:22:18Z</dcterms:modified>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-04-02T00:54:48Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -166,7 +166,7 @@
 </file>
 
 <file path=xl\pivotCache\pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46114.3709837963" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
@@ -240,7 +240,7 @@
         <m/>
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
+        <s v="未开始 ⏳" u="1"/>
         <s v="开发完成👌" u="1"/>
         <s v="已延期 💥" u="1"/>
         <s v="进行中 🔛" u="1"/>
@@ -333,11 +333,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.45" maxValue="1" count="6">
         <m/>
         <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
+        <n v="0.85"/>
+        <n v="0.75"/>
+        <n v="0.45"/>
+        <n v="0.55"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
@@ -367,7 +369,7 @@
 </file>
 
 <file path=xl\pivotCache\pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46114.3709837963" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
@@ -437,11 +439,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
+      <sharedItems containsBlank="1" count="3">
         <m/>
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计开始时间" numFmtId="0">
@@ -514,11 +515,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.45" maxValue="1" count="6">
         <m/>
         <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
+        <n v="0.85"/>
+        <n v="0.75"/>
+        <n v="0.45"/>
+        <n v="0.55"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
@@ -548,7 +551,7 @@
 </file>
 
 <file path=xl\pivotCache\pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46114.3709837963" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
@@ -622,7 +625,7 @@
         <m/>
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
+        <s v="未开始 ⏳" u="1"/>
         <s v="开发完成👌" u="1"/>
         <s v="已延期 💥" u="1"/>
         <s v="进行中 🔛" u="1"/>
@@ -715,11 +718,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.45" maxValue="1" count="6">
         <m/>
         <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
+        <n v="0.85"/>
+        <n v="0.75"/>
+        <n v="0.45"/>
+        <n v="0.55"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
@@ -749,7 +754,7 @@
 </file>
 
 <file path=xl\pivotCache\pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46111.7233564815" refreshedBy="26242" recordCount="25">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" refreshOnLoad="1" saveData="0" createdVersion="3" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46114.3709837963" refreshedBy="26242" recordCount="25">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:N29" sheet="项目管理"/>
   </cacheSource>
@@ -819,11 +824,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="状态" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
+      <sharedItems containsBlank="1" count="3">
         <m/>
         <s v="已完成 ❇️"/>
         <s v="进行中 🚀"/>
-        <s v="未开始 ⏳"/>
       </sharedItems>
     </cacheField>
     <cacheField name="预计开始时间" numFmtId="0">
@@ -896,11 +900,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="完成度_x000a_ %" numFmtId="10">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="1" count="4">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.45" maxValue="1" count="6">
         <m/>
         <n v="1"/>
-        <n v="0.15"/>
-        <n v="0"/>
+        <n v="0.85"/>
+        <n v="0.75"/>
+        <n v="0.45"/>
+        <n v="0.55"/>
       </sharedItems>
     </cacheField>
     <cacheField name="实际_x000a_开始时间" numFmtId="14">
@@ -990,7 +996,7 @@
         <item h="1" m="1" x="5"/>
         <item h="1" m="1" x="6"/>
         <item h="1" x="2"/>
-        <item h="1" x="3"/>
+        <item h="1" m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1149,7 +1155,7 @@
         <item h="1" m="1" x="5"/>
         <item h="1" m="1" x="6"/>
         <item h="1" x="2"/>
-        <item h="1" x="3"/>
+        <item h="1" m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1268,7 +1274,7 @@
 </file>
 
 <file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="261">
   <si>
     <t>成本核算平台</t>
   </si>
@@ -1401,16 +1407,10 @@
     <t>按业务域 -&gt; 场景 -&gt; 费用 -&gt; 变量 -&gt; 规则 -&gt; 阶梯推进</t>
   </si>
   <si>
-    <t>进行中 🚀</t>
-  </si>
-  <si>
     <t>【业务域字典治理】</t>
   </si>
   <si>
     <t>独立系统字典并接入业务域下拉和筛选</t>
-  </si>
-  <si>
-    <t>未开始 ⏳</t>
   </si>
   <si>
     <t>【场景中心】</t>
@@ -1479,6 +1479,9 @@
     <t>恢复试算、正式核算、批量任务与百万级性能治理</t>
   </si>
   <si>
+    <t>进行中 🚀</t>
+  </si>
+  <si>
     <t>【试算中心】</t>
   </si>
   <si>
@@ -1509,16 +1512,34 @@
     <t>恢复任务告警、失败订阅和通知治理</t>
   </si>
   <si>
-    <t>卸船基础</t>
+    <t>五、公式实验室与表达式资产化</t>
   </si>
   <si>
-    <t>汽车集疏港</t>
+    <t>恢复公式工作台、公式编码和表达式资产治理</t>
   </si>
   <si>
-    <t>火车零工</t>
+    <t>【公式实验室工作台】</t>
   </si>
   <si>
-    <t>总共</t>
+    <t>支持业务人员点选变量、条件、模板生成中文公式与标准表达式</t>
+  </si>
+  <si>
+    <t>【公式编码接入变量/规则/发布/运行】</t>
+  </si>
+  <si>
+    <t>变量、规则、发布快照、运行链支持公式编码优先执行</t>
+  </si>
+  <si>
+    <t>【工作台点选配置持久化】</t>
+  </si>
+  <si>
+    <t>补齐 builder 配置保存与二次编辑还原</t>
+  </si>
+  <si>
+    <t>【公式版本管理与模板库】</t>
+  </si>
+  <si>
+    <t>补齐公式版本台账、模板库和长期演进治理</t>
   </si>
   <si>
     <t>看板分析</t>
@@ -1889,6 +1910,225 @@
   </si>
   <si>
     <t>已按当前项目基线回填进展、甘特计划和测试问题记录</t>
+  </si>
+  <si>
+    <t>全局体验治理</t>
+  </si>
+  <si>
+    <t>全局场景控制</t>
+  </si>
+  <si>
+    <t>缺少可选全局场景上下文，跨页面频繁重复按场景筛选，建议支持用户选中一个场景后其他页面默认按该场景过滤，未选时维持各页面自身分页查询。</t>
+  </si>
+  <si>
+    <t>设计优化</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>部分完成：公式实验室、试算中心、正式核算已支持记住最近场景，其他中心页面待继续接入。</t>
+  </si>
+  <si>
+    <t>适用组织选择</t>
+  </si>
+  <si>
+    <t>适用组织建议改为系统部门/组织树下拉，避免手输组织编码，与企业组织口径保持一致。</t>
+  </si>
+  <si>
+    <t>已登记，待结合系统部门接口和场景模型收口。</t>
+  </si>
+  <si>
+    <t>发布治理摘要</t>
+  </si>
+  <si>
+    <t>场景中心当前仍需补齐更完整的发布资格、最近校验、最近告警和试算提醒表达，并去掉开发过程文案。</t>
+  </si>
+  <si>
+    <t>部分完成：场景中心与发布中心已补一轮发布治理摘要，仍需结合真实业务数据继续产品化联调。</t>
+  </si>
+  <si>
+    <t>计价单位语义</t>
+  </si>
+  <si>
+    <t>计价单位当前更多停留在主数据字段，尚未充分影响计量变量选择提示、规则配置语义和结果解释，需要继续产品化。</t>
+  </si>
+  <si>
+    <t>已登记，待结合费用、规则、结果解释链统一补强。</t>
+  </si>
+  <si>
+    <t>字典类型口径</t>
+  </si>
+  <si>
+    <t>字典变量的字典类型仍需统一支持系统字典/核算字典下拉选择；第三方变量则继续按来源系统和字段映射建模，不走手填口径。</t>
+  </si>
+  <si>
+    <t>已登记，后续与变量中心产品化整改一起处理。</t>
+  </si>
+  <si>
+    <t>组合费率与按组变量</t>
+  </si>
+  <si>
+    <t>复杂计费场景下仍缺少按组变量、费率矩阵或组合命中能力，容易出现规则爆炸，需参考业务维护体验继续抽象。</t>
+  </si>
+  <si>
+    <t>已登记，后续在线程三后续深化与公式/矩阵能力中处理。</t>
+  </si>
+  <si>
+    <t>动态输入模板</t>
+  </si>
+  <si>
+    <t>试算与正式核算输入模板尚未完全按已配置变量和命名空间自动生成，业务仍容易误解场景输入口径。</t>
+  </si>
+  <si>
+    <t>已完成：试算中心和正式核算已按发布快照、变量配置与命名空间路径自动生成输入模板。</t>
+  </si>
+  <si>
+    <t>全页面</t>
+  </si>
+  <si>
+    <t>卡片与文案产品化</t>
+  </si>
+  <si>
+    <t>多个页面卡片和提示仍需持续清理开发过程文案，统一成企业级成本核算平台的正式产品表达。</t>
+  </si>
+  <si>
+    <t>已完成首轮整改：主要成本页面已替换线程/步骤类文案，后续仍需逐页联调微调。</t>
+  </si>
+  <si>
+    <t>第三方接入变量执行链</t>
+  </si>
+  <si>
+    <t>第三方接入变量虽已形成正式配置模型，但真实执行链仍为轻量实现，未接真实第三方调用、密钥托管、同步任务、失败重试和告警。</t>
+  </si>
+  <si>
+    <t>风险</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，建议在线程二/五/六联动收口。</t>
+  </si>
+  <si>
+    <t>页面能力与数据接入治理</t>
+  </si>
+  <si>
+    <t>变量中心虽已补导入、复制、共享模板，但距离独立数据接入与导入中心仍有差距，详设能力尚未完全闭环。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，待后续数据接入中心能力补齐。</t>
+  </si>
+  <si>
+    <t>共享影响因素模板</t>
+  </si>
+  <si>
+    <t>共享影响因素模板当前为内置模板库，尚未形成正式模板台账、发布和审计能力。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，当前线程先保持内置模板策略。</t>
+  </si>
+  <si>
+    <t>公式构建器</t>
+  </si>
+  <si>
+    <t>规则中心当前公式构建器仍为轻量助手，复杂公式依然偏依赖手工表达式维护。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，后续继续与公式实验室复用收口。</t>
+  </si>
+  <si>
+    <t>阶梯命中预演</t>
+  </si>
+  <si>
+    <t>阶梯命中预演未独立落地，业务仍需借助试算或运行链验证命中档位。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，计划在线程五联调增强中补齐。</t>
+  </si>
+  <si>
+    <t>批量试算</t>
+  </si>
+  <si>
+    <t>批量试算仍缺失，线程五尚未达到完整运行链验收标准。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，待线程五后续收口。</t>
+  </si>
+  <si>
+    <t>输入模板命名空间</t>
+  </si>
+  <si>
+    <t>运行链输入模板未按变量配置与命名空间生成，与 V/C/I/F/T 上下文口径仍存在偏差。</t>
+  </si>
+  <si>
+    <t>已完成：运行链输入模板已统一按变量元数据、dataPath 和发布快照生成，风险转为关闭记录。</t>
+  </si>
+  <si>
+    <t>告警治理</t>
+  </si>
+  <si>
+    <t>通知中心与自动恢复</t>
+  </si>
+  <si>
+    <t>告警中心未接外部通知渠道与自动化恢复，只能台账查看和人工处理。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，计划在线程六持续完善。</t>
+  </si>
+  <si>
+    <t>分布式与大数据量治理</t>
+  </si>
+  <si>
+    <t>运行链当前仍为单机线程池与轻量 Redis 缓存，未完成分布式调度、锁控制和大数据量压测闭环。</t>
+  </si>
+  <si>
+    <t>公式实验室</t>
+  </si>
+  <si>
+    <t>公式版本管理与模板库</t>
+  </si>
+  <si>
+    <t>公式实验室当前未落独立版本管理与模板库，难以支撑长期演进、历史回看与跨场景复用。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，建议归属线程八到线程九之间补齐。</t>
+  </si>
+  <si>
+    <t>公式编码全链收口</t>
+  </si>
+  <si>
+    <t>变量、规则、运行链尚未全链强制只按 formulaCode 执行，仍保留原始表达式兼容兜底。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，建议归属线程八继续收口。</t>
+  </si>
+  <si>
+    <t>工作台配置持久化</t>
+  </si>
+  <si>
+    <t>工作台点选配置当前未持久化，二次编辑不能完整恢复点选过程。</t>
+  </si>
+  <si>
+    <t>已同步 docs/风险清单，建议线程七继续整改。</t>
+  </si>
+  <si>
+    <t>变量下拉数据</t>
+  </si>
+  <si>
+    <t>当前用户反馈公式实验室存在“变量下拉没数据”问题，需要结合场景选择和数据加载链路尽快回归复核。</t>
+  </si>
+  <si>
+    <t>已完成：已修复新建/编辑公式时场景丢失导致变量下拉为空的问题，并补齐场景记忆。</t>
+  </si>
+  <si>
+    <t>发布前检查与生成版本</t>
+  </si>
+  <si>
+    <t>发布前检查与生成版本按钮在真实数据下仍需继续复核提示完整性和稳定性，避免业务看不懂或误判。</t>
+  </si>
+  <si>
+    <t>待验证</t>
+  </si>
+  <si>
+    <t>已登记为持续验证项，后续结合发布联调继续回归。</t>
   </si>
 </sst>
 </file>
@@ -2314,6 +2554,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="9.75"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9.75"/>
       <color rgb="FF1F2329"/>
       <name val="Calibri"/>
@@ -2328,13 +2575,6 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="9.75"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="9.75"/>
       <color theme="10"/>
@@ -6160,10 +6400,8 @@
       <c r="C12" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D12" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E12" s="104">
         <v>46112</v>
@@ -6252,18 +6490,16 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:136">
       <c r="A13" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="102" t="s">
         <v>43</v>
-      </c>
-      <c r="B13" s="102" t="s">
-        <v>44</v>
       </c>
       <c r="C13" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D13" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E13" s="104">
         <v>46112</v>
@@ -6356,18 +6592,16 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:136">
       <c r="A14" s="121" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B14" s="102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D14" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E14" s="104">
         <v>46113</v>
@@ -6460,18 +6694,16 @@
     </row>
     <row r="15" ht="27" customHeight="1" spans="1:136">
       <c r="A15" s="121" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D15" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E15" s="104">
         <v>46115</v>
@@ -6564,18 +6796,16 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:136">
       <c r="A16" s="102" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="102" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D16" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E16" s="104">
         <v>46120</v>
@@ -6668,18 +6898,16 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:136">
       <c r="A17" s="102" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" s="102" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D17" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E17" s="104">
         <v>46122</v>
@@ -6772,18 +7000,16 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:136">
       <c r="A18" s="102" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="102" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D18" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E18" s="104">
         <v>46127</v>
@@ -6876,18 +7102,16 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:136">
       <c r="A19" s="102" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="102" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D19" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E19" s="104">
         <v>46134</v>
@@ -6976,18 +7200,16 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:136">
       <c r="A20" s="102" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="102" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D20" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E20" s="104">
         <v>46134</v>
@@ -7080,18 +7302,16 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:136">
       <c r="A21" s="102" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B21" s="102" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D21" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E21" s="104">
         <v>46134</v>
@@ -7184,18 +7404,16 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:136">
       <c r="A22" s="102" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="102" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C22" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D22" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E22" s="104">
         <v>46136</v>
@@ -7288,18 +7506,16 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:136">
       <c r="A23" s="102" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B23" s="102" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C23" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D23" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E23" s="104">
         <v>46139</v>
@@ -7392,18 +7608,16 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:136">
       <c r="A24" s="102" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B24" s="102" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="D24" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E24" s="104">
         <v>46148</v>
@@ -7496,18 +7710,16 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:136">
       <c r="A25" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="102" t="s">
         <v>68</v>
-      </c>
-      <c r="B25" s="102" t="s">
-        <v>69</v>
       </c>
       <c r="C25" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="D25" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E25" s="104">
         <v>46148</v>
@@ -7600,18 +7812,16 @@
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:136">
       <c r="A26" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="102" t="s">
         <v>70</v>
-      </c>
-      <c r="B26" s="102" t="s">
-        <v>71</v>
       </c>
       <c r="C26" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D26" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E26" s="104">
         <v>46152</v>
@@ -7704,18 +7914,16 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:136">
       <c r="A27" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="102" t="s">
         <v>72</v>
-      </c>
-      <c r="B27" s="102" t="s">
-        <v>73</v>
       </c>
       <c r="C27" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="D27" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E27" s="104">
         <v>46157</v>
@@ -7808,18 +8016,16 @@
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:136">
       <c r="A28" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="114" t="s">
         <v>74</v>
-      </c>
-      <c r="B28" s="114" t="s">
-        <v>75</v>
       </c>
       <c r="C28" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="D28" s="115" t="s">
+        <v>66</v>
       </c>
       <c r="E28" s="116">
         <v>46162</v>
@@ -7966,18 +8172,16 @@
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:136">
       <c r="A29" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="127" t="s">
         <v>76</v>
-      </c>
-      <c r="B29" s="127" t="s">
-        <v>77</v>
       </c>
       <c r="C29" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="D29" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E29" s="104">
         <v>46167</v>
@@ -8069,25 +8273,17 @@
       <c r="CD29" s="15"/>
     </row>
     <row r="30" spans="1:136">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">五、公式实验室与表达式资产化</t>
-        </is>
-      </c>
-      <c r="B30" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">恢复公式工作台、公式编码和表达式资产治理</t>
-        </is>
-      </c>
-      <c r="C30" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
-      </c>
-      <c r="D30" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="A30" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="127" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E30" s="104">
         <v>46111</v>
@@ -8175,25 +8371,17 @@
       <c r="CD30" s="15"/>
     </row>
     <row r="31" spans="1:136">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【公式实验室工作台】</t>
-        </is>
-      </c>
-      <c r="B31" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">支持业务人员点选变量、条件、模板生成中文公式与标准表达式</t>
-        </is>
-      </c>
-      <c r="C31" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
-      </c>
-      <c r="D31" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成 ❇️</t>
-        </is>
+      <c r="A31" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="127" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="119" t="s">
+        <v>29</v>
       </c>
       <c r="E31" s="104">
         <v>46111</v>
@@ -8281,25 +8469,17 @@
       <c r="CD31" s="15"/>
     </row>
     <row r="32" spans="1:136">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【公式编码接入变量/规则/发布/运行】</t>
-        </is>
-      </c>
-      <c r="B32" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量、规则、发布快照、运行链支持公式编码优先执行</t>
-        </is>
-      </c>
-      <c r="C32" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
-      </c>
-      <c r="D32" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="A32" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="127" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E32" s="104">
         <v>46111</v>
@@ -8387,25 +8567,17 @@
       <c r="CD32" s="15"/>
     </row>
     <row r="33" spans="1:82">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【工作台点选配置持久化】</t>
-        </is>
-      </c>
-      <c r="B33" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">补齐 builder 配置保存与二次编辑还原</t>
-        </is>
-      </c>
-      <c r="C33" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
-      </c>
-      <c r="D33" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="A33" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E33" s="104">
         <v>46112</v>
@@ -8493,25 +8665,17 @@
       <c r="CD33" s="15"/>
     </row>
     <row r="34" spans="1:82">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【公式版本管理与模板库】</t>
-        </is>
-      </c>
-      <c r="B34" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">补齐公式版本台账、模板库和长期演进治理</t>
-        </is>
-      </c>
-      <c r="C34" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
-      </c>
-      <c r="D34" s="119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">进行中 🚀</t>
-        </is>
+      <c r="A34" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="127" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="119" t="s">
+        <v>66</v>
       </c>
       <c r="E34" s="104">
         <v>46113</v>
@@ -8604,16 +8768,10 @@
       <c r="C35" s="127"/>
       <c r="D35" s="119"/>
       <c r="E35" s="104"/>
-      <c r="F35" s="104" t="s">
-        <v>78</v>
-      </c>
+      <c r="F35" s="104"/>
       <c r="G35" s="105"/>
-      <c r="H35" s="106">
-        <v>130</v>
-      </c>
-      <c r="I35" s="106">
-        <v>130</v>
-      </c>
+      <c r="H35" s="106"/>
+      <c r="I35" s="106"/>
       <c r="J35" s="107"/>
       <c r="K35" s="104"/>
       <c r="L35" s="104"/>
@@ -8694,16 +8852,10 @@
       <c r="C36" s="127"/>
       <c r="D36" s="119"/>
       <c r="E36" s="104"/>
-      <c r="F36" s="104" t="s">
-        <v>79</v>
-      </c>
+      <c r="F36" s="104"/>
       <c r="G36" s="105"/>
-      <c r="H36" s="106">
-        <v>41</v>
-      </c>
-      <c r="I36" s="106">
-        <v>41</v>
-      </c>
+      <c r="H36" s="106"/>
+      <c r="I36" s="106"/>
       <c r="J36" s="107"/>
       <c r="K36" s="104"/>
       <c r="L36" s="104"/>
@@ -8784,20 +8936,11 @@
       <c r="C37" s="127"/>
       <c r="D37" s="119"/>
       <c r="E37" s="104"/>
-      <c r="F37" s="104" t="s">
-        <v>80</v>
-      </c>
+      <c r="F37" s="104"/>
       <c r="G37" s="105"/>
-      <c r="H37" s="106">
-        <v>52</v>
-      </c>
-      <c r="I37" s="106">
-        <v>35</v>
-      </c>
-      <c r="J37" s="107">
-        <f>(I37/H37)</f>
-        <v>0.673076923076923</v>
-      </c>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="107"/>
       <c r="K37" s="104"/>
       <c r="L37" s="104"/>
       <c r="M37" s="104"/>
@@ -8877,22 +9020,11 @@
       <c r="C38" s="127"/>
       <c r="D38" s="119"/>
       <c r="E38" s="104"/>
-      <c r="F38" s="104" t="s">
-        <v>81</v>
-      </c>
+      <c r="F38" s="104"/>
       <c r="G38" s="105"/>
-      <c r="H38" s="106">
-        <f>SUM(H35:H37)</f>
-        <v>223</v>
-      </c>
-      <c r="I38" s="106">
-        <f>SUM(I35:I37)</f>
-        <v>206</v>
-      </c>
-      <c r="J38" s="107">
-        <f>I38/H38</f>
-        <v>0.923766816143498</v>
-      </c>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="107"/>
       <c r="K38" s="104"/>
       <c r="L38" s="104"/>
       <c r="M38" s="104"/>
@@ -22369,7 +22501,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{feb41b57-5429-4ab1-baaa-366519f0a351}</x14:id>
+          <x14:id>{6d002d69-2b20-406b-beab-19da24ef0109}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22405,7 +22537,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{feb41b57-5429-4ab1-baaa-366519f0a351}">
+          <x14:cfRule type="dataBar" id="{6d002d69-2b20-406b-beab-19da24ef0109}">
             <x14:dataBar minLength="0" maxLength="100" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22523,7 +22655,7 @@
     <row r="2" ht="33" customHeight="1" spans="1:73">
       <c r="A2" s="29"/>
       <c r="B2" s="30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -22748,14 +22880,14 @@
       <c r="A5" s="15"/>
       <c r="B5" s="31"/>
       <c r="C5" s="32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
       <c r="G5" s="33"/>
       <c r="J5" s="34" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
@@ -22830,7 +22962,7 @@
       <c r="F6" s="32"/>
       <c r="G6" s="33"/>
       <c r="J6" s="35" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K6" s="15"/>
       <c r="L6" s="36"/>
@@ -23118,7 +23250,7 @@
     <row r="10" ht="37" customHeight="1" spans="1:73">
       <c r="A10" s="15"/>
       <c r="B10" s="37" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="37"/>
@@ -23192,12 +23324,12 @@
     <row r="11" ht="28" customHeight="1" spans="1:73">
       <c r="A11" s="15"/>
       <c r="B11" s="38" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="15"/>
       <c r="E11" s="38" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
@@ -23268,14 +23400,14 @@
     <row r="12" spans="1:73">
       <c r="A12" s="15"/>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
@@ -23350,7 +23482,6 @@
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13"/>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
@@ -23994,7 +24125,7 @@
     <row r="22" ht="36" customHeight="1" spans="1:73">
       <c r="A22" s="15"/>
       <c r="B22" s="37" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
@@ -24071,12 +24202,12 @@
     <row r="23" ht="26" customHeight="1" spans="1:73">
       <c r="A23" s="15"/>
       <c r="B23" s="38" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="15"/>
       <c r="E23" s="38" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F23" s="38"/>
       <c r="G23" s="38"/>
@@ -24153,7 +24284,7 @@
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
@@ -24227,10 +24358,10 @@
     <row r="25" spans="1:73">
       <c r="A25" s="15"/>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
@@ -24301,7 +24432,7 @@
     <row r="26" spans="1:73">
       <c r="A26" s="15"/>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
@@ -38087,33 +38218,33 @@
         <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
         <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E1" t="s">
         <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:7">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>2</v>
@@ -38125,18 +38256,18 @@
         <v>46111</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" spans="1:7">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>2</v>
@@ -38148,18 +38279,18 @@
         <v>46111</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:7">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
         <v>2</v>
@@ -38171,18 +38302,18 @@
         <v>46111</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" spans="1:7">
       <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
         <v>106</v>
       </c>
-      <c r="B5" t="s">
-        <v>101</v>
-      </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
@@ -38194,18 +38325,18 @@
         <v>46111</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" spans="1:7">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
         <v>2</v>
@@ -38217,18 +38348,18 @@
         <v>46114</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:7">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
         <v>2</v>
@@ -38240,18 +38371,18 @@
         <v>46119</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:7">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
         <v>2</v>
@@ -38263,18 +38394,18 @@
         <v>46121</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1" spans="1:7">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
         <v>2</v>
@@ -38286,18 +38417,18 @@
         <v>46126</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1" spans="1:7">
       <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" t="s">
         <v>114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" t="s">
-        <v>109</v>
       </c>
       <c r="D10" t="s">
         <v>2</v>
@@ -38309,18 +38440,18 @@
         <v>46130</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1" spans="1:7">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
         <v>2</v>
@@ -38332,18 +38463,18 @@
         <v>46133</v>
       </c>
       <c r="G11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
         <v>2</v>
@@ -38355,18 +38486,18 @@
         <v>46140</v>
       </c>
       <c r="G12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
         <v>2</v>
@@ -38378,18 +38509,18 @@
         <v>46142</v>
       </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
         <v>2</v>
@@ -38401,18 +38532,18 @@
         <v>46154</v>
       </c>
       <c r="G14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
         <v>2</v>
@@ -38424,18 +38555,18 @@
         <v>46162</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
         <v>2</v>
@@ -38447,18 +38578,18 @@
         <v>46165</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
         <v>2</v>
@@ -38470,7 +38601,7 @@
         <v>46172</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -38504,16 +38635,16 @@
   <sheetData>
     <row r="1" ht="29" customHeight="1" spans="1:20">
       <c r="A1" s="22" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B1" s="22"/>
     </row>
     <row r="2" ht="29" customHeight="1" spans="1:20">
       <c r="A2" s="23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -38536,10 +38667,10 @@
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:20">
       <c r="A3" s="23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
@@ -38562,10 +38693,10 @@
     </row>
     <row r="4" ht="29" customHeight="1" spans="1:20">
       <c r="A4" s="23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -38588,10 +38719,10 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:20">
       <c r="A5" s="24" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -39242,18 +39373,18 @@
   <sheetData>
     <row r="1" ht="13.8" spans="1:20">
       <c r="A1" s="14" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E1" s="15"/>
       <c r="F1" s="16" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -39272,7 +39403,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B2" s="18">
         <v>45657</v>
@@ -39300,7 +39431,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B3" s="18">
         <v>45658</v>
@@ -39311,7 +39442,7 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="15" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -39330,7 +39461,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B4" s="18">
         <v>45332</v>
@@ -39341,7 +39472,7 @@
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G4" s="19"/>
       <c r="H4" s="19"/>
@@ -39360,7 +39491,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B5" s="18">
         <v>45333</v>
@@ -39371,7 +39502,7 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="20" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
@@ -39390,7 +39521,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B6" s="18">
         <v>45334</v>
@@ -39418,7 +39549,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B7" s="18">
         <v>45335</v>
@@ -39429,7 +39560,7 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="20" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G7" s="20"/>
       <c r="H7" s="20"/>
@@ -39448,7 +39579,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B8" s="18">
         <v>45336</v>
@@ -39476,7 +39607,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B9" s="18">
         <v>45337</v>
@@ -39504,7 +39635,7 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B10" s="18">
         <v>45338</v>
@@ -39530,7 +39661,7 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B11" s="18">
         <v>45339</v>
@@ -39556,7 +39687,7 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B12" s="18">
         <v>45386</v>
@@ -39582,7 +39713,7 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B13" s="18">
         <v>45387</v>
@@ -39608,7 +39739,7 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B14" s="18">
         <v>45388</v>
@@ -39634,7 +39765,7 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B15" s="18">
         <v>45413</v>
@@ -39660,7 +39791,7 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B16" s="18">
         <v>45414</v>
@@ -39686,7 +39817,7 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B17" s="18">
         <v>45415</v>
@@ -39712,7 +39843,7 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B18" s="18">
         <v>45416</v>
@@ -39738,7 +39869,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B19" s="18">
         <v>45417</v>
@@ -39764,7 +39895,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B20" s="18">
         <v>45453</v>
@@ -39790,7 +39921,7 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B21" s="18">
         <v>45550</v>
@@ -39816,7 +39947,7 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22" s="17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B22" s="18">
         <v>45551</v>
@@ -39842,7 +39973,7 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B23" s="18">
         <v>45552</v>
@@ -39868,7 +39999,7 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B24" s="18">
         <v>45566</v>
@@ -39894,7 +40025,7 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B25" s="18">
         <v>45567</v>
@@ -39920,7 +40051,7 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B26" s="18">
         <v>45568</v>
@@ -39946,7 +40077,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B27" s="18">
         <v>45569</v>
@@ -39972,7 +40103,7 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B28" s="18">
         <v>45570</v>
@@ -39998,7 +40129,7 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B29" s="18">
         <v>45571</v>
@@ -40024,7 +40155,7 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B30" s="18">
         <v>45572</v>
@@ -43719,8 +43850,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="13.2" outlineLevelRow="4"/>
+  <dimension ref="A1:X27"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -43738,46 +43869,46 @@
   <sheetData>
     <row r="1" ht="13.8" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
@@ -43798,27 +43929,27 @@
         <v>46111</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="12"/>
@@ -43842,25 +43973,25 @@
         <v>46111</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" t="s">
         <v>171</v>
       </c>
-      <c r="I3" t="s">
-        <v>166</v>
-      </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L3" s="13">
         <v>46111</v>
@@ -43874,25 +44005,25 @@
         <v>46111</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I4" t="s">
         <v>171</v>
       </c>
-      <c r="I4" t="s">
-        <v>166</v>
-      </c>
       <c r="J4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L4" s="13">
         <v>46111</v>
@@ -43906,1018 +44037,670 @@
         <v>46111</v>
       </c>
       <c r="C5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J5" t="s">
         <v>177</v>
       </c>
-      <c r="D5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" t="s">
-        <v>180</v>
-      </c>
-      <c r="I5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J5" t="s">
-        <v>172</v>
-      </c>
       <c r="K5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="L5" s="13">
         <v>46111</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+    <row r="6" spans="1:24">
+      <c r="A6" t="s">
+        <v>2</v>
       </c>
       <c r="B6">
         <v>46111</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全局体验治理</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全局场景控制</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">缺少可选全局场景上下文，跨页面频繁重复按场景筛选，建议支持用户选中一个场景后其他页面默认按该场景过滤，未选时维持各页面自身分页查询。</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计优化</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
+      <c r="C6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J6" t="s">
+        <v>177</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分完成：公式实验室、试算中心、正式核算已支持记住最近场景，其他中心页面待继续接入。</t>
+          <t>已完成首轮：公式实验室、试算中心、正式核算、费用中心、变量中心、规则中心、发布中心、结果台账已支持继承最近场景，场景中心已支持设置和清除当前工作场景。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+    <row r="7" spans="1:24">
+      <c r="A7" t="s">
+        <v>2</v>
       </c>
       <c r="B7">
         <v>46111</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">场景中心</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">适用组织选择</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">适用组织建议改为系统部门/组织树下拉，避免手输组织编码，与企业组织口径保持一致。</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">优化</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已登记，待结合系统部门接口和场景模型收口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I7" t="s">
+        <v>192</v>
+      </c>
+      <c r="J7" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" t="s">
+        <v>2</v>
       </c>
       <c r="B8">
         <v>46111</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">场景中心</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布治理摘要</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">场景中心当前仍需补齐更完整的发布资格、最近校验、最近告警和试算提醒表达，并去掉开发过程文案。</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">优化</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">部分完成：场景中心与发布中心已补一轮发布治理摘要，仍需结合真实业务数据继续产品化联调。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" t="s">
+        <v>2</v>
       </c>
       <c r="B9">
         <v>46111</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">费用中心</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">计价单位语义</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">计价单位当前更多停留在主数据字段，尚未充分影响计量变量选择提示、规则配置语义和结果解释，需要继续产品化。</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计缺口</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J9" t="s">
+        <v>177</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">已登记，待结合费用、规则、结果解释链统一补强。</t>
+          <t>已完成：费用中心、规则中心、结果台账和运行解释链已补齐单位业务语义，计价单位已影响计量提示、计价解释和结果展示。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+    <row r="10" spans="1:24">
+      <c r="A10" t="s">
+        <v>2</v>
       </c>
       <c r="B10">
         <v>46111</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量中心</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">字典类型口径</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">字典变量的字典类型仍需统一支持系统字典/核算字典下拉选择；第三方变量则继续按来源系统和字段映射建模，不走手填口径。</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">优化</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已登记，后续与变量中心产品化整改一起处理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E10" t="s">
+        <v>204</v>
+      </c>
+      <c r="H10" t="s">
+        <v>185</v>
+      </c>
+      <c r="I10" t="s">
+        <v>192</v>
+      </c>
+      <c r="J10" t="s">
+        <v>177</v>
+      </c>
+      <c r="K10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" t="s">
+        <v>2</v>
       </c>
       <c r="B11">
         <v>46111</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">规则中心</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">组合费率与按组变量</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">复杂计费场景下仍缺少按组变量、费率矩阵或组合命中能力，容易出现规则爆炸，需参考业务维护体验继续抽象。</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计缺口</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已登记，后续在线程三后续深化与公式/矩阵能力中处理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" t="s">
+        <v>207</v>
+      </c>
+      <c r="H11" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" t="s">
+        <v>2</v>
       </c>
       <c r="B12">
         <v>46111</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">试算中心</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">动态输入模板</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">试算与正式核算输入模板尚未完全按已配置变量和命名空间自动生成，业务仍容易误解场景输入口径。</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计缺口</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成：试算中心和正式核算已按发布快照、变量配置与命名空间路径自动生成输入模板。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" t="s">
+        <v>210</v>
+      </c>
+      <c r="H12" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" t="s">
+        <v>171</v>
+      </c>
+      <c r="J12" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" t="s">
+        <v>2</v>
       </c>
       <c r="B13">
         <v>46111</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">全页面</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">卡片与文案产品化</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">多个页面卡片和提示仍需持续清理开发过程文案，统一成企业级成本核算平台的正式产品表达。</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">优化</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成首轮整改：主要成本页面已替换线程/步骤类文案，后续仍需逐页联调微调。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" t="s">
+        <v>213</v>
+      </c>
+      <c r="E13" t="s">
+        <v>214</v>
+      </c>
+      <c r="H13" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" t="s">
+        <v>2</v>
       </c>
       <c r="B14">
         <v>46111</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量中心</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第三方接入变量执行链</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第三方接入变量虽已形成正式配置模型，但真实执行链仍为轻量实现，未接真实第三方调用、密钥托管、同步任务、失败重试和告警。</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，建议在线程二/五/六联动收口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" t="s">
+        <v>217</v>
+      </c>
+      <c r="H14" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" t="s">
+        <v>171</v>
+      </c>
+      <c r="J14" t="s">
+        <v>177</v>
+      </c>
+      <c r="K14" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" t="s">
+        <v>2</v>
       </c>
       <c r="B15">
         <v>46111</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量中心</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">页面能力与数据接入治理</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量中心虽已补导入、复制、共享模板，但距离独立数据接入与导入中心仍有差距，详设能力尚未完全闭环。</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，待后续数据接入中心能力补齐。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" t="s">
+        <v>218</v>
+      </c>
+      <c r="I15" t="s">
+        <v>192</v>
+      </c>
+      <c r="J15" t="s">
+        <v>177</v>
+      </c>
+      <c r="K15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16" t="s">
+        <v>2</v>
       </c>
       <c r="B16">
         <v>46111</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量中心</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">共享影响因素模板</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">共享影响因素模板当前为内置模板库，尚未形成正式模板台账、发布和审计能力。</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，当前线程先保持内置模板策略。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" t="s">
+        <v>223</v>
+      </c>
+      <c r="E16" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" t="s">
+        <v>218</v>
+      </c>
+      <c r="I16" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" t="s">
+        <v>177</v>
+      </c>
+      <c r="K16" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>2</v>
       </c>
       <c r="B17">
         <v>46111</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">规则中心</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式构建器</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">规则中心当前公式构建器仍为轻量助手，复杂公式依然偏依赖手工表达式维护。</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，后续继续与公式实验室复用收口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" t="s">
+        <v>218</v>
+      </c>
+      <c r="I17" t="s">
+        <v>192</v>
+      </c>
+      <c r="J17" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>2</v>
       </c>
       <c r="B18">
         <v>46111</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">规则中心</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">阶梯命中预演</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">阶梯命中预演未独立落地，业务仍需借助试算或运行链验证命中档位。</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，计划在线程五联调增强中补齐。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18" t="s">
+        <v>230</v>
+      </c>
+      <c r="H18" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" t="s">
+        <v>177</v>
+      </c>
+      <c r="K18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>2</v>
       </c>
       <c r="B19">
         <v>46111</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">试算中心</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">批量试算</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">批量试算仍缺失，线程五尚未达到完整运行链验收标准。</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，待线程五后续收口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E19" t="s">
+        <v>233</v>
+      </c>
+      <c r="H19" t="s">
+        <v>218</v>
+      </c>
+      <c r="I19" t="s">
+        <v>192</v>
+      </c>
+      <c r="J19" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>2</v>
       </c>
       <c r="B20">
         <v>46111</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">运行链</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入模板命名空间</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">运行链输入模板未按变量配置与命名空间生成，与 V/C/I/F/T 上下文口径仍存在偏差。</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成：运行链输入模板已统一按变量元数据、dataPath 和发布快照生成，风险转为关闭记录。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" t="s">
+        <v>236</v>
+      </c>
+      <c r="H20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I20" t="s">
+        <v>171</v>
+      </c>
+      <c r="J20" t="s">
+        <v>177</v>
+      </c>
+      <c r="K20" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>2</v>
       </c>
       <c r="B21">
         <v>46111</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">告警治理</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通知中心与自动恢复</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">告警中心未接外部通知渠道与自动化恢复，只能台账查看和人工处理。</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，计划在线程六持续完善。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" t="s">
+        <v>240</v>
+      </c>
+      <c r="H21" t="s">
+        <v>218</v>
+      </c>
+      <c r="I21" t="s">
+        <v>192</v>
+      </c>
+      <c r="J21" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>2</v>
       </c>
       <c r="B22">
         <v>46111</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">性能治理</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">分布式与大数据量治理</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">运行链当前仍为单机线程池与轻量 Redis 缓存，未完成分布式调度、锁控制和大数据量压测闭环。</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，计划在线程六持续完善。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" t="s">
+        <v>243</v>
+      </c>
+      <c r="H22" t="s">
+        <v>218</v>
+      </c>
+      <c r="I22" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" t="s">
+        <v>177</v>
+      </c>
+      <c r="K22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>2</v>
       </c>
       <c r="B23">
         <v>46111</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式实验室</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式版本管理与模板库</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式实验室当前未落独立版本管理与模板库，难以支撑长期演进、历史回看与跨场景复用。</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，建议归属线程八到线程九之间补齐。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C23" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" t="s">
+        <v>246</v>
+      </c>
+      <c r="H23" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" t="s">
+        <v>192</v>
+      </c>
+      <c r="J23" t="s">
+        <v>177</v>
+      </c>
+      <c r="K23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>2</v>
       </c>
       <c r="B24">
         <v>46111</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式实验室</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式编码全链收口</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量、规则、运行链尚未全链强制只按 formulaCode 执行，仍保留原始表达式兼容兜底。</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，建议归属线程八继续收口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C24" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" t="s">
+        <v>249</v>
+      </c>
+      <c r="H24" t="s">
+        <v>218</v>
+      </c>
+      <c r="I24" t="s">
+        <v>171</v>
+      </c>
+      <c r="J24" t="s">
+        <v>177</v>
+      </c>
+      <c r="K24" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>2</v>
       </c>
       <c r="B25">
         <v>46111</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式实验室</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">工作台配置持久化</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">工作台点选配置当前未持久化，二次编辑不能完整恢复点选过程。</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风险</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已同步 docs/风险清单，建议线程七继续整改。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C25" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" t="s">
+        <v>252</v>
+      </c>
+      <c r="H25" t="s">
+        <v>218</v>
+      </c>
+      <c r="I25" t="s">
+        <v>192</v>
+      </c>
+      <c r="J25" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>2</v>
       </c>
       <c r="B26">
         <v>46111</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">公式实验室</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">变量下拉数据</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">当前用户反馈公式实验室存在“变量下拉没数据”问题，需要结合场景选择和数据加载链路尽快回归复核。</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">缺陷</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已完成：已修复新建/编辑公式时场景丢失导致变量下拉为空的问题，并补齐场景记忆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GitFhw</t>
-        </is>
+      <c r="C26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" t="s">
+        <v>255</v>
+      </c>
+      <c r="H26" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" t="s">
+        <v>171</v>
+      </c>
+      <c r="J26" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>2</v>
       </c>
       <c r="B27">
         <v>46111</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布中心</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布前检查与生成版本</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">发布前检查与生成版本按钮在真实数据下仍需继续复核提示完整性和稳定性，避免业务看不懂或误判。</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">待验证</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codex</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已登记为持续验证项，后续结合发布联调继续回归。</t>
-        </is>
+      <c r="C27" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" t="s">
+        <v>257</v>
+      </c>
+      <c r="E27" t="s">
+        <v>258</v>
+      </c>
+      <c r="H27" t="s">
+        <v>259</v>
+      </c>
+      <c r="I27" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/成本核算平台需求跟踪矩阵.xlsx
+++ b/成本核算平台需求跟踪矩阵.xlsx
@@ -1274,7 +1274,7 @@
 </file>
 
 <file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t>成本核算平台</t>
   </si>
@@ -2129,6 +2129,54 @@
   </si>
   <si>
     <t>已登记为持续验证项，后续结合发布联调继续回归。</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>????????????????????????????????????????????????????????????????????</t>
+  </si>
+  <si>
+    <t>????????P0???????????????????????????</t>
+  </si>
+  <si>
+    <t>????????????/??????????????????????????????????????</t>
+  </si>
+  <si>
+    <t>????</t>
+  </si>
+  <si>
+    <t>??????</t>
+  </si>
+  <si>
+    <t>?????????????????????? WARN ?????????????????????????</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>???????????????????????????????????????????????</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>????????</t>
+  </si>
+  <si>
+    <t>?????????????????????????????????????????????</t>
+  </si>
+  <si>
+    <t>?????????????????????????????????????????????????????????</t>
+  </si>
+  <si>
+    <t>?????????</t>
+  </si>
+  <si>
+    <t>??????????? JSON ?????????????????????????? JSON ????</t>
+  </si>
+  <si>
+    <t>???????P0???????????????????????????</t>
   </si>
 </sst>
 </file>
@@ -43850,7 +43898,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -44081,15 +44129,13 @@
         <v>191</v>
       </c>
       <c r="I6" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="J6" t="s">
         <v>177</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>已完成首轮：公式实验室、试算中心、正式核算、费用中心、变量中心、规则中心、发布中心、结果台账已支持继承最近场景，场景中心已支持设置和清除当前工作场景。</t>
-        </is>
+      <c r="K6" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -44462,13 +44508,13 @@
         <v>218</v>
       </c>
       <c r="I19" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="J19" t="s">
         <v>177</v>
       </c>
       <c r="K19" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -44700,7 +44746,94 @@
         <v>177</v>
       </c>
       <c r="K27" t="s">
-        <v>260</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>46111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" t="s">
+        <v>267</v>
+      </c>
+      <c r="H28" t="s">
+        <v>268</v>
+      </c>
+      <c r="I28" t="s">
+        <v>261</v>
+      </c>
+      <c r="J28" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>46111</v>
+      </c>
+      <c r="C29" t="s">
+        <v>270</v>
+      </c>
+      <c r="D29" t="s">
+        <v>271</v>
+      </c>
+      <c r="E29" t="s">
+        <v>272</v>
+      </c>
+      <c r="H29" t="s">
+        <v>270</v>
+      </c>
+      <c r="I29" t="s">
+        <v>261</v>
+      </c>
+      <c r="J29" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>46111</v>
+      </c>
+      <c r="C30" t="s">
+        <v>265</v>
+      </c>
+      <c r="D30" t="s">
+        <v>274</v>
+      </c>
+      <c r="E30" t="s">
+        <v>275</v>
+      </c>
+      <c r="H30" t="s">
+        <v>268</v>
+      </c>
+      <c r="I30" t="s">
+        <v>261</v>
+      </c>
+      <c r="J30" t="s">
+        <v>177</v>
+      </c>
+      <c r="K30" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
